--- a/youtube stories/batch 3/Batch 3 - Production Sheet.xlsx
+++ b/youtube stories/batch 3/Batch 3 - Production Sheet.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -175,6 +175,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -542,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -798,6 +801,18 @@
       <c r="B21" s="14" t="inlineStr">
         <is>
           <t>Reel VO poori story EK BAAR mein banti hai (Rudra, eleven_v4, stability 0.45, speed 1.05 + purana tighten). VO mein NAHI: 'bole/boli', motive line (sirf SUSPECT card par), 'ab suniye sabke bayaan', jo photo mein dikhe (jaise 'haath laal'), galat-ishara line, saboot, 'full video/link bio' line. Saboot ke time ek jagah-set line (saboot ka naam nahi): jaise 'Drawing room mein sab kuch waisa hi tha... Shivam ne har cheez par nazar daali.' End hamesha: 3 sec chup -&gt; PAKAD_LIYA_HI + CTA_HI + SIGNATURE_HI (purani files, dobara nahi banti). Bayaan mein emotion tag ([annoyed] [nervous] [calm]...), har suspect ko koi tag - killer alag na lage. Reel 55-60 sec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Images</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Image Prompts sheet: HARA = purani image (nayi mat banao) – 72 alag images reuse. Baaki 68 nayi banani hain (BG_ wale long video 16:9 ke liye).</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3567,7 @@
       <c r="I14" s="16" t="inlineStr"/>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>P_A021_GLASS</t>
+          <t>P_KAANCH_TUKDE_CUT</t>
         </is>
       </c>
       <c r="K14" s="16" t="inlineStr">
@@ -3940,7 +3955,7 @@
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>A021_RAHUL</t>
+          <t>C10-008_KARAN</t>
         </is>
       </c>
       <c r="K20" s="16" t="inlineStr"/>
@@ -4006,7 +4021,7 @@
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>A021_PRIYA</t>
+          <t>G_W_ORANGE_KURTI_CUT</t>
         </is>
       </c>
       <c r="K21" s="16" t="inlineStr"/>
@@ -4073,7 +4088,7 @@
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>A021_JOSHI</t>
+          <t>C009_JOSHI</t>
         </is>
       </c>
       <c r="K22" s="16" t="inlineStr"/>
@@ -4140,7 +4155,7 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>A021_SUMAN</t>
+          <t>G_W_MAROON_SAREE_CUT</t>
         </is>
       </c>
       <c r="K23" s="16" t="inlineStr"/>
@@ -4206,7 +4221,7 @@
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>A021_NARESH</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr"/>
@@ -4277,7 +4292,7 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>A021_BABLU</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="K25" s="16" t="inlineStr"/>
@@ -4344,7 +4359,7 @@
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>A021_SINGHANIA</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="K26" s="16" t="inlineStr"/>
@@ -4410,7 +4425,7 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>A021_ADITI</t>
+          <t>C004_SNEHA</t>
         </is>
       </c>
       <c r="K27" s="16" t="inlineStr"/>
@@ -4471,7 +4486,7 @@
       <c r="I28" s="16" t="inlineStr"/>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>A021_RAHUL</t>
+          <t>C10-008_KARAN</t>
         </is>
       </c>
       <c r="K28" s="16" t="inlineStr">
@@ -5167,7 +5182,7 @@
       <c r="I39" s="16" t="inlineStr"/>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>P_A022_BILL</t>
+          <t>P_REGISTER_TORN</t>
         </is>
       </c>
       <c r="K39" s="16" t="inlineStr">
@@ -5433,7 +5448,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>A022_REDDY</t>
+          <t>C08-007_KAPOOR</t>
         </is>
       </c>
       <c r="K43" s="16" t="inlineStr"/>
@@ -5499,7 +5514,7 @@
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>A022_SWATI</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="K44" s="16" t="inlineStr"/>
@@ -5565,7 +5580,7 @@
       </c>
       <c r="J45" s="17" t="inlineStr">
         <is>
-          <t>A022_DSOUZA</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="K45" s="17" t="inlineStr"/>
@@ -5636,7 +5651,7 @@
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>A022_AYYAPPAN</t>
+          <t>G_M_APRON_CUT</t>
         </is>
       </c>
       <c r="K46" s="16" t="inlineStr"/>
@@ -5703,7 +5718,7 @@
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>A022_LATA</t>
+          <t>G_V_WOMAN_SAREE_CUT</t>
         </is>
       </c>
       <c r="K47" s="16" t="inlineStr"/>
@@ -5836,7 +5851,7 @@
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>A022_KIRAN</t>
+          <t>C04-010_ARJUN</t>
         </is>
       </c>
       <c r="K49" s="16" t="inlineStr"/>
@@ -5903,7 +5918,7 @@
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>A022_MURTHY</t>
+          <t>G_M_OLD_GLASSES_CUT</t>
         </is>
       </c>
       <c r="K50" s="16" t="inlineStr"/>
@@ -5969,7 +5984,7 @@
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>A022_MEENA</t>
+          <t>C005_NEHA</t>
         </is>
       </c>
       <c r="K51" s="16" t="inlineStr"/>
@@ -6604,7 +6619,7 @@
       <c r="I61" s="16" t="inlineStr"/>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>P_A023_TROPHY</t>
+          <t>P_TROPHY</t>
         </is>
       </c>
       <c r="K61" s="16" t="inlineStr">
@@ -7124,7 +7139,7 @@
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>A023_MATHEW</t>
+          <t>G_UMPIRE_CUT</t>
         </is>
       </c>
       <c r="K69" s="16" t="inlineStr"/>
@@ -7257,7 +7272,7 @@
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>A023_VINAYAK</t>
+          <t>G_V_MAN_BLUE_CUT</t>
         </is>
       </c>
       <c r="K71" s="16" t="inlineStr"/>
@@ -7390,7 +7405,7 @@
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>A023_SOHAM</t>
+          <t>G_CR_VIKRAM_CUT</t>
         </is>
       </c>
       <c r="K73" s="16" t="inlineStr"/>
@@ -7526,7 +7541,7 @@
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>A023_KAPOOR</t>
+          <t>G_W_PINK_SUIT_CUT</t>
         </is>
       </c>
       <c r="K75" s="16" t="inlineStr"/>
@@ -7592,7 +7607,7 @@
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>A023_SAINA</t>
+          <t>C008_NEHA</t>
         </is>
       </c>
       <c r="K76" s="16" t="inlineStr"/>
@@ -8288,7 +8303,7 @@
       <c r="I87" s="16" t="inlineStr"/>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>P_A024_CHAI</t>
+          <t>P_DO_CHAI_UP</t>
         </is>
       </c>
       <c r="K87" s="16" t="inlineStr">
@@ -8410,7 +8425,7 @@
       <c r="I89" s="16" t="inlineStr"/>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>P_A024_DRAWER</t>
+          <t>P_ALMARI_KHULI</t>
         </is>
       </c>
       <c r="K89" s="16" t="inlineStr">
@@ -8471,7 +8486,7 @@
       <c r="I90" s="16" t="inlineStr"/>
       <c r="J90" s="16" t="inlineStr">
         <is>
-          <t>P_A024_SPECS</t>
+          <t>P_BROKEN_GLASSES_CUT</t>
         </is>
       </c>
       <c r="K90" s="16" t="inlineStr">
@@ -8615,7 +8630,7 @@
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
-          <t>A024_URMILA</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="K92" s="16" t="inlineStr"/>
@@ -8682,7 +8697,7 @@
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>A024_AMAN</t>
+          <t>G_M_GREY_HOODIE_CUT</t>
         </is>
       </c>
       <c r="K93" s="16" t="inlineStr"/>
@@ -8748,7 +8763,7 @@
       </c>
       <c r="J94" s="16" t="inlineStr">
         <is>
-          <t>A024_KRITIKA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="K94" s="16" t="inlineStr"/>
@@ -8815,7 +8830,7 @@
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>A024_TIWARI</t>
+          <t>C004_PADOSI</t>
         </is>
       </c>
       <c r="K95" s="16" t="inlineStr"/>
@@ -8881,7 +8896,7 @@
       </c>
       <c r="J96" s="16" t="inlineStr">
         <is>
-          <t>A024_MUKESH</t>
+          <t>G_V_MAN_BLUE_CUT</t>
         </is>
       </c>
       <c r="K96" s="16" t="inlineStr"/>
@@ -8947,7 +8962,7 @@
       </c>
       <c r="J97" s="17" t="inlineStr">
         <is>
-          <t>A024_SANJAY</t>
+          <t>G_M_YELLOW_KURTA_CUT</t>
         </is>
       </c>
       <c r="K97" s="17" t="inlineStr"/>
@@ -9001,7 +9016,7 @@
       </c>
       <c r="G98" s="16" t="inlineStr">
         <is>
-          <t>कामवाली शांता। पैसों का लिफ़ाफ़ा इसी ने देखा था। बोलीं... मैं कपड़े सुखा रही थी, धूप में कपड़े जल्दी सूखते हैं।</t>
+          <t>कामवाली शांति। पैसों का लिफ़ाफ़ा इसी ने देखा था। बोलीं... मैं कपड़े सुखा रही थी, धूप में कपड़े जल्दी सूखते हैं।</t>
         </is>
       </c>
       <c r="H98" s="16" t="inlineStr">
@@ -9012,13 +9027,13 @@
       <c r="I98" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 7/8
-Kaamwali Shanta
+Kaamwali Shanti
 (lifaafa isi ne dekha tha)</t>
         </is>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>A024_SHANTA</t>
+          <t>G_SHANTI</t>
         </is>
       </c>
       <c r="K98" s="16" t="inlineStr"/>
@@ -9084,7 +9099,7 @@
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>A024_FAROOQ</t>
+          <t>G_M_LIGHTMAN_CUT</t>
         </is>
       </c>
       <c r="K99" s="16" t="inlineStr"/>
@@ -9134,18 +9149,18 @@
       </c>
       <c r="G100" s="16" t="inlineStr">
         <is>
-          <t>पैसों का लिफ़ाफ़ा... शांता जी ने ही देखा था न?</t>
+          <t>पैसों का लिफ़ाफ़ा... शांति जी ने ही देखा था न?</t>
         </is>
       </c>
       <c r="H100" s="16" t="inlineStr">
         <is>
-          <t>Paison ka lifaafa... Shanta ji ne hi dekha tha na?</t>
+          <t>Paison ka lifaafa... Shanti ji ne hi dekha tha na?</t>
         </is>
       </c>
       <c r="I100" s="16" t="inlineStr"/>
       <c r="J100" s="16" t="inlineStr">
         <is>
-          <t>A024_SHANTA</t>
+          <t>G_SHANTI</t>
         </is>
       </c>
       <c r="K100" s="16" t="inlineStr">
@@ -9902,7 +9917,7 @@
       <c r="I112" s="16" t="inlineStr"/>
       <c r="J112" s="16" t="inlineStr">
         <is>
-          <t>P_A025_BOOT</t>
+          <t>P_MUD_MARKS</t>
         </is>
       </c>
       <c r="K112" s="16" t="inlineStr">
@@ -10107,7 +10122,7 @@
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>A025_ROHIT</t>
+          <t>C001_ROHIT</t>
         </is>
       </c>
       <c r="K115" s="16" t="inlineStr"/>
@@ -10173,7 +10188,7 @@
       </c>
       <c r="J116" s="17" t="inlineStr">
         <is>
-          <t>A025_VIVEK</t>
+          <t>G_M_BROWN_JACKET_CUT</t>
         </is>
       </c>
       <c r="K116" s="17" t="inlineStr"/>
@@ -10244,7 +10259,7 @@
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>A025_NAZIYA</t>
+          <t>C004_SNEHA</t>
         </is>
       </c>
       <c r="K117" s="16" t="inlineStr"/>
@@ -10376,7 +10391,7 @@
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>A025_ZOYA</t>
+          <t>C001_ANJALI</t>
         </is>
       </c>
       <c r="K119" s="16" t="inlineStr"/>
@@ -10443,7 +10458,7 @@
       </c>
       <c r="J120" s="16" t="inlineStr">
         <is>
-          <t>A025_SEN</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="K120" s="16" t="inlineStr"/>
@@ -10510,7 +10525,7 @@
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
-          <t>A025_PAPPU</t>
+          <t>G_M_BLUE_JACKET_A_CUT</t>
         </is>
       </c>
       <c r="K121" s="16" t="inlineStr"/>
@@ -10576,7 +10591,7 @@
       </c>
       <c r="J122" s="16" t="inlineStr">
         <is>
-          <t>A025_SAHIL</t>
+          <t>C18-007_SAHIL</t>
         </is>
       </c>
       <c r="K122" s="16" t="inlineStr"/>
@@ -10626,7 +10641,7 @@
       </c>
       <c r="G123" s="16" t="inlineStr">
         <is>
-          <t>नौकरानी रज़िया। बोलीं... मैं घर पर नहीं थी, अपनी बहन के घर गई थी।</t>
+          <t>नौकरानी कमला। बोलीं... मैं घर पर नहीं थी, अपनी बहन के घर गई थी।</t>
         </is>
       </c>
       <c r="H123" s="16" t="inlineStr">
@@ -10637,12 +10652,12 @@
       <c r="I123" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 9/9
-Naukrani Raziya</t>
+Naukrani Kamla</t>
         </is>
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
-          <t>A025_RAZIYA</t>
+          <t>G_KAMLA</t>
         </is>
       </c>
       <c r="K123" s="16" t="inlineStr"/>
@@ -10703,7 +10718,7 @@
       <c r="I124" s="16" t="inlineStr"/>
       <c r="J124" s="16" t="inlineStr">
         <is>
-          <t>A025_ROHIT</t>
+          <t>C001_ROHIT</t>
         </is>
       </c>
       <c r="K124" s="16" t="inlineStr">
@@ -11277,7 +11292,7 @@
       <c r="I133" s="16" t="inlineStr"/>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>P_A026_TEA</t>
+          <t>P_CHAI_TRAY</t>
         </is>
       </c>
       <c r="K133" s="16" t="inlineStr">
@@ -11460,7 +11475,7 @@
       <c r="I136" s="16" t="inlineStr"/>
       <c r="J136" s="16" t="inlineStr">
         <is>
-          <t>P_A026_BOX</t>
+          <t>P_DONATION_BOX_CUT</t>
         </is>
       </c>
       <c r="K136" s="16" t="inlineStr">
@@ -11665,7 +11680,7 @@
       </c>
       <c r="J139" s="16" t="inlineStr">
         <is>
-          <t>A026_ANSHUL</t>
+          <t>C006_RAJAT</t>
         </is>
       </c>
       <c r="K139" s="16" t="inlineStr"/>
@@ -11731,7 +11746,7 @@
       </c>
       <c r="J140" s="16" t="inlineStr">
         <is>
-          <t>A026_NEHA</t>
+          <t>C008_NEHA</t>
         </is>
       </c>
       <c r="K140" s="16" t="inlineStr"/>
@@ -11797,7 +11812,7 @@
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>A026_PARTH</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="K141" s="16" t="inlineStr"/>
@@ -11930,7 +11945,7 @@
       </c>
       <c r="J143" s="16" t="inlineStr">
         <is>
-          <t>A026_KALE</t>
+          <t>G_M_OLD_GLASSES_CUT</t>
         </is>
       </c>
       <c r="K143" s="16" t="inlineStr"/>
@@ -11996,7 +12011,7 @@
       </c>
       <c r="J144" s="16" t="inlineStr">
         <is>
-          <t>A026_RIYA</t>
+          <t>C002_RIYA_CUT</t>
         </is>
       </c>
       <c r="K144" s="16" t="inlineStr"/>
@@ -12063,7 +12078,7 @@
       </c>
       <c r="J145" s="16" t="inlineStr">
         <is>
-          <t>A026_MEHTA</t>
+          <t>C16-001_DRMEHTA</t>
         </is>
       </c>
       <c r="K145" s="16" t="inlineStr"/>
@@ -12196,7 +12211,7 @@
       </c>
       <c r="J147" s="17" t="inlineStr">
         <is>
-          <t>A026_VIKRAM</t>
+          <t>C007_VIKRAM</t>
         </is>
       </c>
       <c r="K147" s="17" t="inlineStr"/>
@@ -12896,7 +12911,7 @@
       <c r="I158" s="16" t="inlineStr"/>
       <c r="J158" s="16" t="inlineStr">
         <is>
-          <t>P_A027_REGISTER</t>
+          <t>P_VISITOR_REGISTER</t>
         </is>
       </c>
       <c r="K158" s="16" t="inlineStr">
@@ -13079,7 +13094,7 @@
       <c r="I161" s="16" t="inlineStr"/>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>P_A027_CCTV</t>
+          <t>P_CCTV_MONITOR</t>
         </is>
       </c>
       <c r="K161" s="16" t="inlineStr">
@@ -13223,7 +13238,7 @@
       </c>
       <c r="J163" s="16" t="inlineStr">
         <is>
-          <t>A027_POOJA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="K163" s="16" t="inlineStr"/>
@@ -13290,7 +13305,7 @@
       </c>
       <c r="J164" s="16" t="inlineStr">
         <is>
-          <t>A027_HARIHAR</t>
+          <t>G_M_GUARD_CUT</t>
         </is>
       </c>
       <c r="K164" s="16" t="inlineStr"/>
@@ -13356,7 +13371,7 @@
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>A027_FAIZAN</t>
+          <t>C18-003_PRATEEK</t>
         </is>
       </c>
       <c r="K165" s="16" t="inlineStr"/>
@@ -13422,7 +13437,7 @@
       </c>
       <c r="J166" s="17" t="inlineStr">
         <is>
-          <t>A027_MALHOTRA</t>
+          <t>C17-001_SETH</t>
         </is>
       </c>
       <c r="K166" s="17" t="inlineStr"/>
@@ -13493,7 +13508,7 @@
       </c>
       <c r="J167" s="16" t="inlineStr">
         <is>
-          <t>A027_SUJATA</t>
+          <t>G_V_WOMAN_SAREE_CUT</t>
         </is>
       </c>
       <c r="K167" s="16" t="inlineStr"/>
@@ -13559,7 +13574,7 @@
       </c>
       <c r="J168" s="16" t="inlineStr">
         <is>
-          <t>A027_PRAKASH</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="K168" s="16" t="inlineStr"/>
@@ -13626,7 +13641,7 @@
       </c>
       <c r="J169" s="16" t="inlineStr">
         <is>
-          <t>A027_ANITA</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="K169" s="16" t="inlineStr"/>
@@ -13692,7 +13707,7 @@
       </c>
       <c r="J170" s="16" t="inlineStr">
         <is>
-          <t>A027_RAGHUNATH</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="K170" s="16" t="inlineStr"/>
@@ -13759,7 +13774,7 @@
       </c>
       <c r="J171" s="16" t="inlineStr">
         <is>
-          <t>A027_ABHIJIT</t>
+          <t>C002_KUNAL</t>
         </is>
       </c>
       <c r="K171" s="16" t="inlineStr"/>
@@ -13809,7 +13824,7 @@
       </c>
       <c r="G172" s="16" t="inlineStr">
         <is>
-          <t>सफ़ाईवाला गोपी। बोले... मैं अमृतसर में जलियाँवाला बाग़ गया था।</t>
+          <t>सफ़ाईवाला रामू। बोले... मैं अमृतसर में जलियाँवाला बाग़ गया था।</t>
         </is>
       </c>
       <c r="H172" s="16" t="inlineStr">
@@ -13820,12 +13835,12 @@
       <c r="I172" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 10/10
-Safaiwala Gopi</t>
+Safaiwala Ramu</t>
         </is>
       </c>
       <c r="J172" s="16" t="inlineStr">
         <is>
-          <t>A027_GOPI</t>
+          <t>G_RAMU</t>
         </is>
       </c>
       <c r="K172" s="16" t="inlineStr"/>
@@ -13886,7 +13901,7 @@
       <c r="I173" s="16" t="inlineStr"/>
       <c r="J173" s="16" t="inlineStr">
         <is>
-          <t>A027_HARIHAR</t>
+          <t>G_M_GUARD_CUT</t>
         </is>
       </c>
       <c r="K173" s="16" t="inlineStr">
@@ -14582,7 +14597,7 @@
       <c r="I184" s="16" t="inlineStr"/>
       <c r="J184" s="16" t="inlineStr">
         <is>
-          <t>P_A028_STETHO</t>
+          <t>P_STETHOSCOPE</t>
         </is>
       </c>
       <c r="K184" s="16" t="inlineStr">
@@ -14848,7 +14863,7 @@
       </c>
       <c r="J188" s="16" t="inlineStr">
         <is>
-          <t>A028_JASSI</t>
+          <t>C005_VICKY</t>
         </is>
       </c>
       <c r="K188" s="16" t="inlineStr"/>
@@ -14915,7 +14930,7 @@
       </c>
       <c r="J189" s="16" t="inlineStr">
         <is>
-          <t>A028_BAJWA</t>
+          <t>C16-001_DRMEHTA</t>
         </is>
       </c>
       <c r="K189" s="16" t="inlineStr"/>
@@ -15316,7 +15331,7 @@
       </c>
       <c r="J195" s="16" t="inlineStr">
         <is>
-          <t>A028_ANU</t>
+          <t>C001_ANJALI</t>
         </is>
       </c>
       <c r="K195" s="16" t="inlineStr"/>
@@ -15768,7 +15783,7 @@
       <c r="I202" s="16" t="inlineStr"/>
       <c r="J202" s="16" t="inlineStr">
         <is>
-          <t>A029_V_GUPTA</t>
+          <t>C04-008_GUPTA_SLUMPED</t>
         </is>
       </c>
       <c r="K202" s="16" t="inlineStr"/>
@@ -15833,7 +15848,7 @@
       </c>
       <c r="J203" s="16" t="inlineStr">
         <is>
-          <t>A029_V_GUPTA</t>
+          <t>C04-008_GUPTA_SLUMPED</t>
         </is>
       </c>
       <c r="K203" s="16" t="inlineStr"/>
@@ -16012,7 +16027,7 @@
       <c r="I206" s="16" t="inlineStr"/>
       <c r="J206" s="16" t="inlineStr">
         <is>
-          <t>P_A029_SAFE</t>
+          <t>P_TIJORI</t>
         </is>
       </c>
       <c r="K206" s="16" t="inlineStr">
@@ -16134,7 +16149,7 @@
       <c r="I208" s="16" t="inlineStr"/>
       <c r="J208" s="16" t="inlineStr">
         <is>
-          <t>P_A029_GLASS</t>
+          <t>P_THAALI_LASSI</t>
         </is>
       </c>
       <c r="K208" s="16" t="inlineStr">
@@ -16195,7 +16210,7 @@
       <c r="I209" s="16" t="inlineStr"/>
       <c r="J209" s="16" t="inlineStr">
         <is>
-          <t>P_A029_CHASHMA</t>
+          <t>P_BROKEN_GLASSES_CUT</t>
         </is>
       </c>
       <c r="K209" s="16" t="inlineStr">
@@ -16338,7 +16353,7 @@
       </c>
       <c r="J211" s="17" t="inlineStr">
         <is>
-          <t>A029_RAMDAYAL</t>
+          <t>C006_GUPTA</t>
         </is>
       </c>
       <c r="K211" s="17" t="inlineStr"/>
@@ -16409,7 +16424,7 @@
       </c>
       <c r="J212" s="16" t="inlineStr">
         <is>
-          <t>A029_ASHOK</t>
+          <t>C004_AMIT</t>
         </is>
       </c>
       <c r="K212" s="16" t="inlineStr"/>
@@ -16475,7 +16490,7 @@
       </c>
       <c r="J213" s="16" t="inlineStr">
         <is>
-          <t>A029_KAMINI</t>
+          <t>C004_SNEHA</t>
         </is>
       </c>
       <c r="K213" s="16" t="inlineStr"/>
@@ -16542,7 +16557,7 @@
       </c>
       <c r="J214" s="16" t="inlineStr">
         <is>
-          <t>A029_RAJU</t>
+          <t>C003_BHATIJA</t>
         </is>
       </c>
       <c r="K214" s="16" t="inlineStr"/>
@@ -16609,7 +16624,7 @@
       </c>
       <c r="J215" s="16" t="inlineStr">
         <is>
-          <t>A029_SHERU</t>
+          <t>G_V_MAN_BLUE_CUT</t>
         </is>
       </c>
       <c r="K215" s="16" t="inlineStr"/>
@@ -16675,7 +16690,7 @@
       </c>
       <c r="J216" s="16" t="inlineStr">
         <is>
-          <t>A029_GOMTI</t>
+          <t>C004_MAA</t>
         </is>
       </c>
       <c r="K216" s="16" t="inlineStr"/>
@@ -16742,7 +16757,7 @@
       </c>
       <c r="J217" s="16" t="inlineStr">
         <is>
-          <t>A029_PATEL</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="K217" s="16" t="inlineStr"/>
@@ -16792,7 +16807,7 @@
       </c>
       <c r="G218" s="16" t="inlineStr">
         <is>
-          <t>नौकर छेदी। बोले... मैं बाज़ार में कानपुर के ठग्गू के लड्डू ले रहा था।</t>
+          <t>नौकर भोला। बोले... मैं बाज़ार में कानपुर के ठग्गू के लड्डू ले रहा था।</t>
         </is>
       </c>
       <c r="H218" s="16" t="inlineStr">
@@ -16803,12 +16818,12 @@
       <c r="I218" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 8/9
-Naukar Chhedi</t>
+Naukar Bhola</t>
         </is>
       </c>
       <c r="J218" s="16" t="inlineStr">
         <is>
-          <t>A029_CHHEDI</t>
+          <t>G_BHOLA</t>
         </is>
       </c>
       <c r="K218" s="16" t="inlineStr"/>
@@ -16874,7 +16889,7 @@
       </c>
       <c r="J219" s="16" t="inlineStr">
         <is>
-          <t>A029_ANWAR</t>
+          <t>C010_MAHESH</t>
         </is>
       </c>
       <c r="K219" s="16" t="inlineStr"/>
@@ -16935,7 +16950,7 @@
       <c r="I220" s="16" t="inlineStr"/>
       <c r="J220" s="16" t="inlineStr">
         <is>
-          <t>A029_SHERU</t>
+          <t>G_V_MAN_BLUE_CUT</t>
         </is>
       </c>
       <c r="K220" s="16" t="inlineStr">
@@ -17692,7 +17707,7 @@
       <c r="I232" s="16" t="inlineStr"/>
       <c r="J232" s="16" t="inlineStr">
         <is>
-          <t>P_A030_FLASK</t>
+          <t>P_STEEL_THERMOS</t>
         </is>
       </c>
       <c r="K232" s="16" t="inlineStr">
@@ -17897,7 +17912,7 @@
       </c>
       <c r="J235" s="16" t="inlineStr">
         <is>
-          <t>A030_TANMAY</t>
+          <t>G_M_GREY_HOODIE_CUT</t>
         </is>
       </c>
       <c r="K235" s="16" t="inlineStr"/>
@@ -17963,7 +17978,7 @@
       </c>
       <c r="J236" s="16" t="inlineStr">
         <is>
-          <t>A030_GARGI</t>
+          <t>C005_NEHA</t>
         </is>
       </c>
       <c r="K236" s="16" t="inlineStr"/>
@@ -18029,7 +18044,7 @@
       </c>
       <c r="J237" s="16" t="inlineStr">
         <is>
-          <t>A030_BISHT</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="K237" s="16" t="inlineStr"/>
@@ -18096,7 +18111,7 @@
       </c>
       <c r="J238" s="16" t="inlineStr">
         <is>
-          <t>A030_SURABHI</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="K238" s="16" t="inlineStr"/>
@@ -18146,7 +18161,7 @@
       </c>
       <c r="G239" s="16" t="inlineStr">
         <is>
-          <t>गाइड पूरन। दूरबीन बेचने का शक। बोले... मैं टूरिस्ट को ध्रुव तारा दिखा रहा था, जो उत्तर दिशा में दिखता है।</t>
+          <t>गाइड हरिया। दूरबीन बेचने का शक। बोले... मैं टूरिस्ट को ध्रुव तारा दिखा रहा था, जो उत्तर दिशा में दिखता है।</t>
         </is>
       </c>
       <c r="H239" s="16" t="inlineStr">
@@ -18157,13 +18172,13 @@
       <c r="I239" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 5/10
-Guide Pooran
+Guide Hariya
 (doorbeen bechne ka shak)</t>
         </is>
       </c>
       <c r="J239" s="16" t="inlineStr">
         <is>
-          <t>A030_POORAN</t>
+          <t>G_HARIYA</t>
         </is>
       </c>
       <c r="K239" s="16" t="inlineStr"/>
@@ -18230,7 +18245,7 @@
       </c>
       <c r="J240" s="16" t="inlineStr">
         <is>
-          <t>A030_HEMLATA</t>
+          <t>G_W_MAROON_SAREE_CUT</t>
         </is>
       </c>
       <c r="K240" s="16" t="inlineStr"/>
@@ -18296,7 +18311,7 @@
       </c>
       <c r="J241" s="16" t="inlineStr">
         <is>
-          <t>A030_HRITHIK</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="K241" s="16" t="inlineStr"/>
@@ -18363,7 +18378,7 @@
       </c>
       <c r="J242" s="16" t="inlineStr">
         <is>
-          <t>A030_NAVEEN</t>
+          <t>C10-004_DEEPAK</t>
         </is>
       </c>
       <c r="K242" s="16" t="inlineStr"/>
@@ -18413,7 +18428,7 @@
       </c>
       <c r="G243" s="16" t="inlineStr">
         <is>
-          <t>चौकीदार हरी। बोले... मैं गेट पर था, बच्चों को बता रहा था, बुध सूरज के सबसे पास वाला ग्रह है।</t>
+          <t>चौकीदार बहादुर। बोले... मैं गेट पर था, बच्चों को बता रहा था, बुध सूरज के सबसे पास वाला ग्रह है।</t>
         </is>
       </c>
       <c r="H243" s="16" t="inlineStr">
@@ -18424,12 +18439,12 @@
       <c r="I243" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 9/10
-Chowkidar Hari</t>
+Chowkidar Bahadur</t>
         </is>
       </c>
       <c r="J243" s="16" t="inlineStr">
         <is>
-          <t>A030_HARI</t>
+          <t>G_BAHADUR</t>
         </is>
       </c>
       <c r="K243" s="16" t="inlineStr"/>
@@ -18495,7 +18510,7 @@
       </c>
       <c r="J244" s="17" t="inlineStr">
         <is>
-          <t>A030_KUNDAN</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="K244" s="17" t="inlineStr"/>
@@ -18560,7 +18575,7 @@
       <c r="I245" s="16" t="inlineStr"/>
       <c r="J245" s="16" t="inlineStr">
         <is>
-          <t>A030_TANMAY</t>
+          <t>G_M_GREY_HOODIE_CUT</t>
         </is>
       </c>
       <c r="K245" s="16" t="inlineStr">
@@ -20807,7 +20822,7 @@
       <c r="G24" s="16" t="inlineStr"/>
       <c r="H24" s="16" t="inlineStr">
         <is>
-          <t>P_A021_GLASS</t>
+          <t>P_KAANCH_TUKDE_CUT</t>
         </is>
       </c>
       <c r="I24" s="16" t="inlineStr">
@@ -21257,7 +21272,7 @@
       </c>
       <c r="H30" s="16" t="inlineStr">
         <is>
-          <t>A021_RAHUL</t>
+          <t>C10-008_KARAN</t>
         </is>
       </c>
       <c r="I30" s="16" t="inlineStr">
@@ -21340,7 +21355,7 @@
       </c>
       <c r="H31" s="16" t="inlineStr">
         <is>
-          <t>A021_RAHUL</t>
+          <t>C10-008_KARAN</t>
         </is>
       </c>
       <c r="I31" s="16" t="inlineStr">
@@ -21413,7 +21428,7 @@
       </c>
       <c r="H32" s="16" t="inlineStr">
         <is>
-          <t>A021_RAHUL</t>
+          <t>C10-008_KARAN</t>
         </is>
       </c>
       <c r="I32" s="16" t="inlineStr">
@@ -21486,7 +21501,7 @@
       </c>
       <c r="H33" s="16" t="inlineStr">
         <is>
-          <t>A021_RAHUL</t>
+          <t>C10-008_KARAN</t>
         </is>
       </c>
       <c r="I33" s="16" t="inlineStr">
@@ -21559,7 +21574,7 @@
       </c>
       <c r="H34" s="16" t="inlineStr">
         <is>
-          <t>A021_PRIYA</t>
+          <t>G_W_ORANGE_KURTI_CUT</t>
         </is>
       </c>
       <c r="I34" s="16" t="inlineStr">
@@ -21641,7 +21656,7 @@
       </c>
       <c r="H35" s="16" t="inlineStr">
         <is>
-          <t>A021_PRIYA</t>
+          <t>G_W_ORANGE_KURTI_CUT</t>
         </is>
       </c>
       <c r="I35" s="16" t="inlineStr">
@@ -21714,7 +21729,7 @@
       </c>
       <c r="H36" s="16" t="inlineStr">
         <is>
-          <t>A021_PRIYA</t>
+          <t>G_W_ORANGE_KURTI_CUT</t>
         </is>
       </c>
       <c r="I36" s="16" t="inlineStr">
@@ -21787,7 +21802,7 @@
       </c>
       <c r="H37" s="16" t="inlineStr">
         <is>
-          <t>A021_JOSHI</t>
+          <t>C009_JOSHI</t>
         </is>
       </c>
       <c r="I37" s="16" t="inlineStr">
@@ -21870,7 +21885,7 @@
       </c>
       <c r="H38" s="16" t="inlineStr">
         <is>
-          <t>A021_JOSHI</t>
+          <t>C009_JOSHI</t>
         </is>
       </c>
       <c r="I38" s="16" t="inlineStr">
@@ -21943,7 +21958,7 @@
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>A021_JOSHI</t>
+          <t>C009_JOSHI</t>
         </is>
       </c>
       <c r="I39" s="16" t="inlineStr">
@@ -22016,7 +22031,7 @@
       </c>
       <c r="H40" s="16" t="inlineStr">
         <is>
-          <t>A021_SUMAN</t>
+          <t>G_W_MAROON_SAREE_CUT</t>
         </is>
       </c>
       <c r="I40" s="16" t="inlineStr">
@@ -22099,7 +22114,7 @@
       </c>
       <c r="H41" s="16" t="inlineStr">
         <is>
-          <t>A021_SUMAN</t>
+          <t>G_W_MAROON_SAREE_CUT</t>
         </is>
       </c>
       <c r="I41" s="16" t="inlineStr">
@@ -22172,7 +22187,7 @@
       </c>
       <c r="H42" s="16" t="inlineStr">
         <is>
-          <t>A021_SUMAN</t>
+          <t>G_W_MAROON_SAREE_CUT</t>
         </is>
       </c>
       <c r="I42" s="16" t="inlineStr">
@@ -22245,7 +22260,7 @@
       </c>
       <c r="H43" s="16" t="inlineStr">
         <is>
-          <t>A021_NARESH</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I43" s="16" t="inlineStr">
@@ -22327,7 +22342,7 @@
       </c>
       <c r="H44" s="16" t="inlineStr">
         <is>
-          <t>A021_NARESH</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I44" s="16" t="inlineStr">
@@ -22400,7 +22415,7 @@
       </c>
       <c r="H45" s="16" t="inlineStr">
         <is>
-          <t>A021_NARESH</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I45" s="16" t="inlineStr">
@@ -22473,7 +22488,7 @@
       </c>
       <c r="H46" s="16" t="inlineStr">
         <is>
-          <t>A021_BABLU</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="I46" s="16" t="inlineStr">
@@ -22556,7 +22571,7 @@
       </c>
       <c r="H47" s="16" t="inlineStr">
         <is>
-          <t>A021_BABLU</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="I47" s="16" t="inlineStr">
@@ -22629,7 +22644,7 @@
       </c>
       <c r="H48" s="16" t="inlineStr">
         <is>
-          <t>A021_BABLU</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="I48" s="16" t="inlineStr">
@@ -22702,7 +22717,7 @@
       </c>
       <c r="H49" s="16" t="inlineStr">
         <is>
-          <t>A021_SINGHANIA</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I49" s="16" t="inlineStr">
@@ -22785,7 +22800,7 @@
       </c>
       <c r="H50" s="16" t="inlineStr">
         <is>
-          <t>A021_SINGHANIA</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I50" s="16" t="inlineStr">
@@ -22858,7 +22873,7 @@
       </c>
       <c r="H51" s="16" t="inlineStr">
         <is>
-          <t>A021_SINGHANIA</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I51" s="16" t="inlineStr">
@@ -22931,7 +22946,7 @@
       </c>
       <c r="H52" s="16" t="inlineStr">
         <is>
-          <t>A021_ADITI</t>
+          <t>C004_SNEHA</t>
         </is>
       </c>
       <c r="I52" s="16" t="inlineStr">
@@ -23013,7 +23028,7 @@
       </c>
       <c r="H53" s="16" t="inlineStr">
         <is>
-          <t>A021_ADITI</t>
+          <t>C004_SNEHA</t>
         </is>
       </c>
       <c r="I53" s="16" t="inlineStr">
@@ -23086,7 +23101,7 @@
       </c>
       <c r="H54" s="16" t="inlineStr">
         <is>
-          <t>A021_RAHUL</t>
+          <t>C10-008_KARAN</t>
         </is>
       </c>
       <c r="I54" s="16" t="inlineStr">
@@ -24265,7 +24280,7 @@
       <c r="G70" s="16" t="inlineStr"/>
       <c r="H70" s="16" t="inlineStr">
         <is>
-          <t>P_A022_BILL</t>
+          <t>P_REGISTER_TORN</t>
         </is>
       </c>
       <c r="I70" s="16" t="inlineStr">
@@ -24569,7 +24584,7 @@
       </c>
       <c r="H74" s="16" t="inlineStr">
         <is>
-          <t>A022_REDDY</t>
+          <t>C08-007_KAPOOR</t>
         </is>
       </c>
       <c r="I74" s="16" t="inlineStr">
@@ -24652,7 +24667,7 @@
       </c>
       <c r="H75" s="16" t="inlineStr">
         <is>
-          <t>A022_REDDY</t>
+          <t>C08-007_KAPOOR</t>
         </is>
       </c>
       <c r="I75" s="16" t="inlineStr">
@@ -24725,7 +24740,7 @@
       </c>
       <c r="H76" s="16" t="inlineStr">
         <is>
-          <t>A022_REDDY</t>
+          <t>C08-007_KAPOOR</t>
         </is>
       </c>
       <c r="I76" s="16" t="inlineStr">
@@ -24798,7 +24813,7 @@
       </c>
       <c r="H77" s="16" t="inlineStr">
         <is>
-          <t>A022_SWATI</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="I77" s="16" t="inlineStr">
@@ -24880,7 +24895,7 @@
       </c>
       <c r="H78" s="16" t="inlineStr">
         <is>
-          <t>A022_SWATI</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="I78" s="16" t="inlineStr">
@@ -24953,7 +24968,7 @@
       </c>
       <c r="H79" s="16" t="inlineStr">
         <is>
-          <t>A022_SWATI</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="I79" s="16" t="inlineStr">
@@ -25026,7 +25041,7 @@
       </c>
       <c r="H80" s="16" t="inlineStr">
         <is>
-          <t>A022_DSOUZA</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I80" s="16" t="inlineStr">
@@ -25108,7 +25123,7 @@
       </c>
       <c r="H81" s="16" t="inlineStr">
         <is>
-          <t>A022_DSOUZA</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I81" s="16" t="inlineStr">
@@ -25181,7 +25196,7 @@
       </c>
       <c r="H82" s="16" t="inlineStr">
         <is>
-          <t>A022_DSOUZA</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I82" s="16" t="inlineStr">
@@ -25254,7 +25269,7 @@
       </c>
       <c r="H83" s="16" t="inlineStr">
         <is>
-          <t>A022_AYYAPPAN</t>
+          <t>G_M_APRON_CUT</t>
         </is>
       </c>
       <c r="I83" s="16" t="inlineStr">
@@ -25337,7 +25352,7 @@
       </c>
       <c r="H84" s="16" t="inlineStr">
         <is>
-          <t>A022_AYYAPPAN</t>
+          <t>G_M_APRON_CUT</t>
         </is>
       </c>
       <c r="I84" s="16" t="inlineStr">
@@ -25410,7 +25425,7 @@
       </c>
       <c r="H85" s="16" t="inlineStr">
         <is>
-          <t>A022_AYYAPPAN</t>
+          <t>G_M_APRON_CUT</t>
         </is>
       </c>
       <c r="I85" s="16" t="inlineStr">
@@ -25483,7 +25498,7 @@
       </c>
       <c r="H86" s="16" t="inlineStr">
         <is>
-          <t>A022_LATA</t>
+          <t>G_V_WOMAN_SAREE_CUT</t>
         </is>
       </c>
       <c r="I86" s="16" t="inlineStr">
@@ -25566,7 +25581,7 @@
       </c>
       <c r="H87" s="16" t="inlineStr">
         <is>
-          <t>A022_LATA</t>
+          <t>G_V_WOMAN_SAREE_CUT</t>
         </is>
       </c>
       <c r="I87" s="16" t="inlineStr">
@@ -25639,7 +25654,7 @@
       </c>
       <c r="H88" s="16" t="inlineStr">
         <is>
-          <t>A022_LATA</t>
+          <t>G_V_WOMAN_SAREE_CUT</t>
         </is>
       </c>
       <c r="I88" s="16" t="inlineStr">
@@ -25941,7 +25956,7 @@
       </c>
       <c r="H92" s="16" t="inlineStr">
         <is>
-          <t>A022_KIRAN</t>
+          <t>C04-010_ARJUN</t>
         </is>
       </c>
       <c r="I92" s="16" t="inlineStr">
@@ -26023,7 +26038,7 @@
       </c>
       <c r="H93" s="16" t="inlineStr">
         <is>
-          <t>A022_KIRAN</t>
+          <t>C04-010_ARJUN</t>
         </is>
       </c>
       <c r="I93" s="16" t="inlineStr">
@@ -26096,7 +26111,7 @@
       </c>
       <c r="H94" s="16" t="inlineStr">
         <is>
-          <t>A022_MURTHY</t>
+          <t>G_M_OLD_GLASSES_CUT</t>
         </is>
       </c>
       <c r="I94" s="16" t="inlineStr">
@@ -26179,7 +26194,7 @@
       </c>
       <c r="H95" s="16" t="inlineStr">
         <is>
-          <t>A022_MURTHY</t>
+          <t>G_M_OLD_GLASSES_CUT</t>
         </is>
       </c>
       <c r="I95" s="16" t="inlineStr">
@@ -26252,7 +26267,7 @@
       </c>
       <c r="H96" s="16" t="inlineStr">
         <is>
-          <t>A022_MURTHY</t>
+          <t>G_M_OLD_GLASSES_CUT</t>
         </is>
       </c>
       <c r="I96" s="16" t="inlineStr">
@@ -26325,7 +26340,7 @@
       </c>
       <c r="H97" s="16" t="inlineStr">
         <is>
-          <t>A022_MEENA</t>
+          <t>C005_NEHA</t>
         </is>
       </c>
       <c r="I97" s="16" t="inlineStr">
@@ -26407,7 +26422,7 @@
       </c>
       <c r="H98" s="16" t="inlineStr">
         <is>
-          <t>A022_MEENA</t>
+          <t>C005_NEHA</t>
         </is>
       </c>
       <c r="I98" s="16" t="inlineStr">
@@ -26480,7 +26495,7 @@
       </c>
       <c r="H99" s="16" t="inlineStr">
         <is>
-          <t>A022_MEENA</t>
+          <t>C005_NEHA</t>
         </is>
       </c>
       <c r="I99" s="16" t="inlineStr">
@@ -27586,7 +27601,7 @@
       <c r="G114" s="16" t="inlineStr"/>
       <c r="H114" s="16" t="inlineStr">
         <is>
-          <t>P_A023_TROPHY</t>
+          <t>P_TROPHY</t>
         </is>
       </c>
       <c r="I114" s="16" t="inlineStr">
@@ -28493,7 +28508,7 @@
       </c>
       <c r="H126" s="16" t="inlineStr">
         <is>
-          <t>A023_MATHEW</t>
+          <t>G_UMPIRE_CUT</t>
         </is>
       </c>
       <c r="I126" s="16" t="inlineStr">
@@ -28575,7 +28590,7 @@
       </c>
       <c r="H127" s="16" t="inlineStr">
         <is>
-          <t>A023_MATHEW</t>
+          <t>G_UMPIRE_CUT</t>
         </is>
       </c>
       <c r="I127" s="16" t="inlineStr">
@@ -28876,7 +28891,7 @@
       </c>
       <c r="H131" s="16" t="inlineStr">
         <is>
-          <t>A023_VINAYAK</t>
+          <t>G_V_MAN_BLUE_CUT</t>
         </is>
       </c>
       <c r="I131" s="16" t="inlineStr">
@@ -28959,7 +28974,7 @@
       </c>
       <c r="H132" s="16" t="inlineStr">
         <is>
-          <t>A023_VINAYAK</t>
+          <t>G_V_MAN_BLUE_CUT</t>
         </is>
       </c>
       <c r="I132" s="16" t="inlineStr">
@@ -29032,7 +29047,7 @@
       </c>
       <c r="H133" s="16" t="inlineStr">
         <is>
-          <t>A023_VINAYAK</t>
+          <t>G_V_MAN_BLUE_CUT</t>
         </is>
       </c>
       <c r="I133" s="16" t="inlineStr">
@@ -29333,7 +29348,7 @@
       </c>
       <c r="H137" s="16" t="inlineStr">
         <is>
-          <t>A023_SOHAM</t>
+          <t>G_CR_VIKRAM_CUT</t>
         </is>
       </c>
       <c r="I137" s="16" t="inlineStr">
@@ -29416,7 +29431,7 @@
       </c>
       <c r="H138" s="16" t="inlineStr">
         <is>
-          <t>A023_SOHAM</t>
+          <t>G_CR_VIKRAM_CUT</t>
         </is>
       </c>
       <c r="I138" s="16" t="inlineStr">
@@ -29489,7 +29504,7 @@
       </c>
       <c r="H139" s="16" t="inlineStr">
         <is>
-          <t>A023_SOHAM</t>
+          <t>G_CR_VIKRAM_CUT</t>
         </is>
       </c>
       <c r="I139" s="16" t="inlineStr">
@@ -29790,7 +29805,7 @@
       </c>
       <c r="H143" s="16" t="inlineStr">
         <is>
-          <t>A023_KAPOOR</t>
+          <t>G_W_PINK_SUIT_CUT</t>
         </is>
       </c>
       <c r="I143" s="16" t="inlineStr">
@@ -29872,7 +29887,7 @@
       </c>
       <c r="H144" s="16" t="inlineStr">
         <is>
-          <t>A023_KAPOOR</t>
+          <t>G_W_PINK_SUIT_CUT</t>
         </is>
       </c>
       <c r="I144" s="16" t="inlineStr">
@@ -29945,7 +29960,7 @@
       </c>
       <c r="H145" s="16" t="inlineStr">
         <is>
-          <t>A023_SAINA</t>
+          <t>C008_NEHA</t>
         </is>
       </c>
       <c r="I145" s="16" t="inlineStr">
@@ -30027,7 +30042,7 @@
       </c>
       <c r="H146" s="16" t="inlineStr">
         <is>
-          <t>A023_SAINA</t>
+          <t>C008_NEHA</t>
         </is>
       </c>
       <c r="I146" s="16" t="inlineStr">
@@ -31206,7 +31221,7 @@
       <c r="G162" s="16" t="inlineStr"/>
       <c r="H162" s="16" t="inlineStr">
         <is>
-          <t>P_A024_CHAI</t>
+          <t>P_DO_CHAI_UP</t>
         </is>
       </c>
       <c r="I162" s="16" t="inlineStr">
@@ -31352,7 +31367,7 @@
       <c r="G164" s="16" t="inlineStr"/>
       <c r="H164" s="16" t="inlineStr">
         <is>
-          <t>P_A024_DRAWER</t>
+          <t>P_ALMARI_KHULI</t>
         </is>
       </c>
       <c r="I164" s="16" t="inlineStr">
@@ -31425,7 +31440,7 @@
       <c r="G165" s="16" t="inlineStr"/>
       <c r="H165" s="16" t="inlineStr">
         <is>
-          <t>P_A024_SPECS</t>
+          <t>P_BROKEN_GLASSES_CUT</t>
         </is>
       </c>
       <c r="I165" s="16" t="inlineStr">
@@ -31583,7 +31598,7 @@
       </c>
       <c r="H167" s="16" t="inlineStr">
         <is>
-          <t>A024_URMILA</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="I167" s="16" t="inlineStr">
@@ -31666,7 +31681,7 @@
       </c>
       <c r="H168" s="16" t="inlineStr">
         <is>
-          <t>A024_URMILA</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="I168" s="16" t="inlineStr">
@@ -31739,7 +31754,7 @@
       </c>
       <c r="H169" s="16" t="inlineStr">
         <is>
-          <t>A024_URMILA</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="I169" s="16" t="inlineStr">
@@ -31812,7 +31827,7 @@
       </c>
       <c r="H170" s="16" t="inlineStr">
         <is>
-          <t>A024_AMAN</t>
+          <t>G_M_GREY_HOODIE_CUT</t>
         </is>
       </c>
       <c r="I170" s="16" t="inlineStr">
@@ -31895,7 +31910,7 @@
       </c>
       <c r="H171" s="16" t="inlineStr">
         <is>
-          <t>A024_AMAN</t>
+          <t>G_M_GREY_HOODIE_CUT</t>
         </is>
       </c>
       <c r="I171" s="16" t="inlineStr">
@@ -31968,7 +31983,7 @@
       </c>
       <c r="H172" s="16" t="inlineStr">
         <is>
-          <t>A024_AMAN</t>
+          <t>G_M_GREY_HOODIE_CUT</t>
         </is>
       </c>
       <c r="I172" s="16" t="inlineStr">
@@ -32041,7 +32056,7 @@
       </c>
       <c r="H173" s="16" t="inlineStr">
         <is>
-          <t>A024_KRITIKA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="I173" s="16" t="inlineStr">
@@ -32123,7 +32138,7 @@
       </c>
       <c r="H174" s="16" t="inlineStr">
         <is>
-          <t>A024_KRITIKA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="I174" s="16" t="inlineStr">
@@ -32196,7 +32211,7 @@
       </c>
       <c r="H175" s="16" t="inlineStr">
         <is>
-          <t>A024_KRITIKA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="I175" s="16" t="inlineStr">
@@ -32269,7 +32284,7 @@
       </c>
       <c r="H176" s="16" t="inlineStr">
         <is>
-          <t>A024_TIWARI</t>
+          <t>C004_PADOSI</t>
         </is>
       </c>
       <c r="I176" s="16" t="inlineStr">
@@ -32352,7 +32367,7 @@
       </c>
       <c r="H177" s="16" t="inlineStr">
         <is>
-          <t>A024_TIWARI</t>
+          <t>C004_PADOSI</t>
         </is>
       </c>
       <c r="I177" s="16" t="inlineStr">
@@ -32425,7 +32440,7 @@
       </c>
       <c r="H178" s="16" t="inlineStr">
         <is>
-          <t>A024_TIWARI</t>
+          <t>C004_PADOSI</t>
         </is>
       </c>
       <c r="I178" s="16" t="inlineStr">
@@ -32498,7 +32513,7 @@
       </c>
       <c r="H179" s="16" t="inlineStr">
         <is>
-          <t>A024_MUKESH</t>
+          <t>G_V_MAN_BLUE_CUT</t>
         </is>
       </c>
       <c r="I179" s="16" t="inlineStr">
@@ -32580,7 +32595,7 @@
       </c>
       <c r="H180" s="16" t="inlineStr">
         <is>
-          <t>A024_MUKESH</t>
+          <t>G_V_MAN_BLUE_CUT</t>
         </is>
       </c>
       <c r="I180" s="16" t="inlineStr">
@@ -32653,7 +32668,7 @@
       </c>
       <c r="H181" s="16" t="inlineStr">
         <is>
-          <t>A024_MUKESH</t>
+          <t>G_V_MAN_BLUE_CUT</t>
         </is>
       </c>
       <c r="I181" s="16" t="inlineStr">
@@ -32726,7 +32741,7 @@
       </c>
       <c r="H182" s="16" t="inlineStr">
         <is>
-          <t>A024_SANJAY</t>
+          <t>G_M_YELLOW_KURTA_CUT</t>
         </is>
       </c>
       <c r="I182" s="16" t="inlineStr">
@@ -32808,7 +32823,7 @@
       </c>
       <c r="H183" s="16" t="inlineStr">
         <is>
-          <t>A024_SANJAY</t>
+          <t>G_M_YELLOW_KURTA_CUT</t>
         </is>
       </c>
       <c r="I183" s="16" t="inlineStr">
@@ -32881,7 +32896,7 @@
       </c>
       <c r="H184" s="16" t="inlineStr">
         <is>
-          <t>A024_SANJAY</t>
+          <t>G_M_YELLOW_KURTA_CUT</t>
         </is>
       </c>
       <c r="I184" s="16" t="inlineStr">
@@ -32954,7 +32969,7 @@
       </c>
       <c r="H185" s="16" t="inlineStr">
         <is>
-          <t>A024_SHANTA</t>
+          <t>G_SHANTI</t>
         </is>
       </c>
       <c r="I185" s="16" t="inlineStr">
@@ -32980,7 +32995,7 @@
       <c r="M185" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 7/8
-Kaamwali Shanta
+Kaamwali Shanti
 (lifaafa isi ne dekha tha)</t>
         </is>
       </c>
@@ -33037,7 +33052,7 @@
       </c>
       <c r="H186" s="16" t="inlineStr">
         <is>
-          <t>A024_SHANTA</t>
+          <t>G_SHANTI</t>
         </is>
       </c>
       <c r="I186" s="16" t="inlineStr">
@@ -33110,7 +33125,7 @@
       </c>
       <c r="H187" s="16" t="inlineStr">
         <is>
-          <t>A024_SHANTA</t>
+          <t>G_SHANTI</t>
         </is>
       </c>
       <c r="I187" s="16" t="inlineStr">
@@ -33183,7 +33198,7 @@
       </c>
       <c r="H188" s="16" t="inlineStr">
         <is>
-          <t>A024_FAROOQ</t>
+          <t>G_M_LIGHTMAN_CUT</t>
         </is>
       </c>
       <c r="I188" s="16" t="inlineStr">
@@ -33265,7 +33280,7 @@
       </c>
       <c r="H189" s="16" t="inlineStr">
         <is>
-          <t>A024_FAROOQ</t>
+          <t>G_M_LIGHTMAN_CUT</t>
         </is>
       </c>
       <c r="I189" s="16" t="inlineStr">
@@ -33338,7 +33353,7 @@
       </c>
       <c r="H190" s="16" t="inlineStr">
         <is>
-          <t>A024_FAROOQ</t>
+          <t>G_M_LIGHTMAN_CUT</t>
         </is>
       </c>
       <c r="I190" s="16" t="inlineStr">
@@ -33406,12 +33421,12 @@
       </c>
       <c r="G191" s="16" t="inlineStr">
         <is>
-          <t>Paison ka lifaafa... Shanta ji</t>
+          <t>Paison ka lifaafa... Shanti ji</t>
         </is>
       </c>
       <c r="H191" s="16" t="inlineStr">
         <is>
-          <t>A024_SHANTA</t>
+          <t>G_SHANTI</t>
         </is>
       </c>
       <c r="I191" s="16" t="inlineStr">
@@ -33484,7 +33499,7 @@
       </c>
       <c r="H192" s="16" t="inlineStr">
         <is>
-          <t>A024_SHANTA</t>
+          <t>G_SHANTI</t>
         </is>
       </c>
       <c r="I192" s="16" t="inlineStr">
@@ -34667,7 +34682,7 @@
       <c r="G208" s="16" t="inlineStr"/>
       <c r="H208" s="16" t="inlineStr">
         <is>
-          <t>P_A025_BOOT</t>
+          <t>P_MUD_MARKS</t>
         </is>
       </c>
       <c r="I208" s="16" t="inlineStr">
@@ -34898,7 +34913,7 @@
       </c>
       <c r="H211" s="16" t="inlineStr">
         <is>
-          <t>A025_ROHIT</t>
+          <t>C001_ROHIT</t>
         </is>
       </c>
       <c r="I211" s="16" t="inlineStr">
@@ -34981,7 +34996,7 @@
       </c>
       <c r="H212" s="16" t="inlineStr">
         <is>
-          <t>A025_ROHIT</t>
+          <t>C001_ROHIT</t>
         </is>
       </c>
       <c r="I212" s="16" t="inlineStr">
@@ -35054,7 +35069,7 @@
       </c>
       <c r="H213" s="16" t="inlineStr">
         <is>
-          <t>A025_ROHIT</t>
+          <t>C001_ROHIT</t>
         </is>
       </c>
       <c r="I213" s="16" t="inlineStr">
@@ -35127,7 +35142,7 @@
       </c>
       <c r="H214" s="16" t="inlineStr">
         <is>
-          <t>A025_VIVEK</t>
+          <t>G_M_BROWN_JACKET_CUT</t>
         </is>
       </c>
       <c r="I214" s="16" t="inlineStr">
@@ -35209,7 +35224,7 @@
       </c>
       <c r="H215" s="16" t="inlineStr">
         <is>
-          <t>A025_VIVEK</t>
+          <t>G_M_BROWN_JACKET_CUT</t>
         </is>
       </c>
       <c r="I215" s="16" t="inlineStr">
@@ -35282,7 +35297,7 @@
       </c>
       <c r="H216" s="16" t="inlineStr">
         <is>
-          <t>A025_VIVEK</t>
+          <t>G_M_BROWN_JACKET_CUT</t>
         </is>
       </c>
       <c r="I216" s="16" t="inlineStr">
@@ -35355,7 +35370,7 @@
       </c>
       <c r="H217" s="16" t="inlineStr">
         <is>
-          <t>A025_NAZIYA</t>
+          <t>C004_SNEHA</t>
         </is>
       </c>
       <c r="I217" s="16" t="inlineStr">
@@ -35438,7 +35453,7 @@
       </c>
       <c r="H218" s="16" t="inlineStr">
         <is>
-          <t>A025_NAZIYA</t>
+          <t>C004_SNEHA</t>
         </is>
       </c>
       <c r="I218" s="16" t="inlineStr">
@@ -35511,7 +35526,7 @@
       </c>
       <c r="H219" s="16" t="inlineStr">
         <is>
-          <t>A025_NAZIYA</t>
+          <t>C004_SNEHA</t>
         </is>
       </c>
       <c r="I219" s="16" t="inlineStr">
@@ -35812,7 +35827,7 @@
       </c>
       <c r="H223" s="16" t="inlineStr">
         <is>
-          <t>A025_ZOYA</t>
+          <t>C001_ANJALI</t>
         </is>
       </c>
       <c r="I223" s="16" t="inlineStr">
@@ -35894,7 +35909,7 @@
       </c>
       <c r="H224" s="16" t="inlineStr">
         <is>
-          <t>A025_ZOYA</t>
+          <t>C001_ANJALI</t>
         </is>
       </c>
       <c r="I224" s="16" t="inlineStr">
@@ -35967,7 +35982,7 @@
       </c>
       <c r="H225" s="16" t="inlineStr">
         <is>
-          <t>A025_SEN</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="I225" s="16" t="inlineStr">
@@ -36050,7 +36065,7 @@
       </c>
       <c r="H226" s="16" t="inlineStr">
         <is>
-          <t>A025_SEN</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="I226" s="16" t="inlineStr">
@@ -36123,7 +36138,7 @@
       </c>
       <c r="H227" s="16" t="inlineStr">
         <is>
-          <t>A025_PAPPU</t>
+          <t>G_M_BLUE_JACKET_A_CUT</t>
         </is>
       </c>
       <c r="I227" s="16" t="inlineStr">
@@ -36206,7 +36221,7 @@
       </c>
       <c r="H228" s="16" t="inlineStr">
         <is>
-          <t>A025_PAPPU</t>
+          <t>G_M_BLUE_JACKET_A_CUT</t>
         </is>
       </c>
       <c r="I228" s="16" t="inlineStr">
@@ -36279,7 +36294,7 @@
       </c>
       <c r="H229" s="16" t="inlineStr">
         <is>
-          <t>A025_PAPPU</t>
+          <t>G_M_BLUE_JACKET_A_CUT</t>
         </is>
       </c>
       <c r="I229" s="16" t="inlineStr">
@@ -36352,7 +36367,7 @@
       </c>
       <c r="H230" s="16" t="inlineStr">
         <is>
-          <t>A025_SAHIL</t>
+          <t>C18-007_SAHIL</t>
         </is>
       </c>
       <c r="I230" s="16" t="inlineStr">
@@ -36434,7 +36449,7 @@
       </c>
       <c r="H231" s="16" t="inlineStr">
         <is>
-          <t>A025_SAHIL</t>
+          <t>C18-007_SAHIL</t>
         </is>
       </c>
       <c r="I231" s="16" t="inlineStr">
@@ -36507,7 +36522,7 @@
       </c>
       <c r="H232" s="16" t="inlineStr">
         <is>
-          <t>A025_RAZIYA</t>
+          <t>G_KAMLA</t>
         </is>
       </c>
       <c r="I232" s="16" t="inlineStr">
@@ -36533,7 +36548,7 @@
       <c r="M232" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 9/9
-Naukrani Raziya</t>
+Naukrani Kamla</t>
         </is>
       </c>
       <c r="N232" s="16" t="inlineStr">
@@ -36589,7 +36604,7 @@
       </c>
       <c r="H233" s="16" t="inlineStr">
         <is>
-          <t>A025_RAZIYA</t>
+          <t>G_KAMLA</t>
         </is>
       </c>
       <c r="I233" s="16" t="inlineStr">
@@ -36662,7 +36677,7 @@
       </c>
       <c r="H234" s="16" t="inlineStr">
         <is>
-          <t>A025_ROHIT</t>
+          <t>C001_ROHIT</t>
         </is>
       </c>
       <c r="I234" s="16" t="inlineStr">
@@ -37626,7 +37641,7 @@
       <c r="G247" s="16" t="inlineStr"/>
       <c r="H247" s="16" t="inlineStr">
         <is>
-          <t>P_A026_TEA</t>
+          <t>P_CHAI_TRAY</t>
         </is>
       </c>
       <c r="I247" s="16" t="inlineStr">
@@ -37845,7 +37860,7 @@
       <c r="G250" s="16" t="inlineStr"/>
       <c r="H250" s="16" t="inlineStr">
         <is>
-          <t>P_A026_BOX</t>
+          <t>P_DONATION_BOX_CUT</t>
         </is>
       </c>
       <c r="I250" s="16" t="inlineStr">
@@ -38076,7 +38091,7 @@
       </c>
       <c r="H253" s="16" t="inlineStr">
         <is>
-          <t>A026_ANSHUL</t>
+          <t>C006_RAJAT</t>
         </is>
       </c>
       <c r="I253" s="16" t="inlineStr">
@@ -38159,7 +38174,7 @@
       </c>
       <c r="H254" s="16" t="inlineStr">
         <is>
-          <t>A026_ANSHUL</t>
+          <t>C006_RAJAT</t>
         </is>
       </c>
       <c r="I254" s="16" t="inlineStr">
@@ -38232,7 +38247,7 @@
       </c>
       <c r="H255" s="16" t="inlineStr">
         <is>
-          <t>A026_ANSHUL</t>
+          <t>C006_RAJAT</t>
         </is>
       </c>
       <c r="I255" s="16" t="inlineStr">
@@ -38305,7 +38320,7 @@
       </c>
       <c r="H256" s="16" t="inlineStr">
         <is>
-          <t>A026_NEHA</t>
+          <t>C008_NEHA</t>
         </is>
       </c>
       <c r="I256" s="16" t="inlineStr">
@@ -38387,7 +38402,7 @@
       </c>
       <c r="H257" s="16" t="inlineStr">
         <is>
-          <t>A026_NEHA</t>
+          <t>C008_NEHA</t>
         </is>
       </c>
       <c r="I257" s="16" t="inlineStr">
@@ -38460,7 +38475,7 @@
       </c>
       <c r="H258" s="16" t="inlineStr">
         <is>
-          <t>A026_NEHA</t>
+          <t>C008_NEHA</t>
         </is>
       </c>
       <c r="I258" s="16" t="inlineStr">
@@ -38533,7 +38548,7 @@
       </c>
       <c r="H259" s="16" t="inlineStr">
         <is>
-          <t>A026_PARTH</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I259" s="16" t="inlineStr">
@@ -38615,7 +38630,7 @@
       </c>
       <c r="H260" s="16" t="inlineStr">
         <is>
-          <t>A026_PARTH</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I260" s="16" t="inlineStr">
@@ -38917,7 +38932,7 @@
       </c>
       <c r="H264" s="16" t="inlineStr">
         <is>
-          <t>A026_KALE</t>
+          <t>G_M_OLD_GLASSES_CUT</t>
         </is>
       </c>
       <c r="I264" s="16" t="inlineStr">
@@ -38999,7 +39014,7 @@
       </c>
       <c r="H265" s="16" t="inlineStr">
         <is>
-          <t>A026_KALE</t>
+          <t>G_M_OLD_GLASSES_CUT</t>
         </is>
       </c>
       <c r="I265" s="16" t="inlineStr">
@@ -39072,7 +39087,7 @@
       </c>
       <c r="H266" s="16" t="inlineStr">
         <is>
-          <t>A026_RIYA</t>
+          <t>C002_RIYA_CUT</t>
         </is>
       </c>
       <c r="I266" s="16" t="inlineStr">
@@ -39154,7 +39169,7 @@
       </c>
       <c r="H267" s="16" t="inlineStr">
         <is>
-          <t>A026_RIYA</t>
+          <t>C002_RIYA_CUT</t>
         </is>
       </c>
       <c r="I267" s="16" t="inlineStr">
@@ -39227,7 +39242,7 @@
       </c>
       <c r="H268" s="16" t="inlineStr">
         <is>
-          <t>A026_RIYA</t>
+          <t>C002_RIYA_CUT</t>
         </is>
       </c>
       <c r="I268" s="16" t="inlineStr">
@@ -39300,7 +39315,7 @@
       </c>
       <c r="H269" s="16" t="inlineStr">
         <is>
-          <t>A026_MEHTA</t>
+          <t>C16-001_DRMEHTA</t>
         </is>
       </c>
       <c r="I269" s="16" t="inlineStr">
@@ -39383,7 +39398,7 @@
       </c>
       <c r="H270" s="16" t="inlineStr">
         <is>
-          <t>A026_MEHTA</t>
+          <t>C16-001_DRMEHTA</t>
         </is>
       </c>
       <c r="I270" s="16" t="inlineStr">
@@ -39456,7 +39471,7 @@
       </c>
       <c r="H271" s="16" t="inlineStr">
         <is>
-          <t>A026_MEHTA</t>
+          <t>C16-001_DRMEHTA</t>
         </is>
       </c>
       <c r="I271" s="16" t="inlineStr">
@@ -39758,7 +39773,7 @@
       </c>
       <c r="H275" s="16" t="inlineStr">
         <is>
-          <t>A026_VIKRAM</t>
+          <t>C007_VIKRAM</t>
         </is>
       </c>
       <c r="I275" s="16" t="inlineStr">
@@ -39840,7 +39855,7 @@
       </c>
       <c r="H276" s="16" t="inlineStr">
         <is>
-          <t>A026_VIKRAM</t>
+          <t>C007_VIKRAM</t>
         </is>
       </c>
       <c r="I276" s="16" t="inlineStr">
@@ -39913,7 +39928,7 @@
       </c>
       <c r="H277" s="16" t="inlineStr">
         <is>
-          <t>A026_VIKRAM</t>
+          <t>C007_VIKRAM</t>
         </is>
       </c>
       <c r="I277" s="16" t="inlineStr">
@@ -41165,7 +41180,7 @@
       <c r="G294" s="16" t="inlineStr"/>
       <c r="H294" s="16" t="inlineStr">
         <is>
-          <t>P_A027_REGISTER</t>
+          <t>P_VISITOR_REGISTER</t>
         </is>
       </c>
       <c r="I294" s="16" t="inlineStr">
@@ -41384,7 +41399,7 @@
       <c r="G297" s="16" t="inlineStr"/>
       <c r="H297" s="16" t="inlineStr">
         <is>
-          <t>P_A027_CCTV</t>
+          <t>P_CCTV_MONITOR</t>
         </is>
       </c>
       <c r="I297" s="16" t="inlineStr">
@@ -41542,7 +41557,7 @@
       </c>
       <c r="H299" s="16" t="inlineStr">
         <is>
-          <t>A027_POOJA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="I299" s="16" t="inlineStr">
@@ -41625,7 +41640,7 @@
       </c>
       <c r="H300" s="16" t="inlineStr">
         <is>
-          <t>A027_POOJA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="I300" s="16" t="inlineStr">
@@ -41698,7 +41713,7 @@
       </c>
       <c r="H301" s="16" t="inlineStr">
         <is>
-          <t>A027_POOJA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="I301" s="16" t="inlineStr">
@@ -41771,7 +41786,7 @@
       </c>
       <c r="H302" s="16" t="inlineStr">
         <is>
-          <t>A027_HARIHAR</t>
+          <t>G_M_GUARD_CUT</t>
         </is>
       </c>
       <c r="I302" s="16" t="inlineStr">
@@ -41854,7 +41869,7 @@
       </c>
       <c r="H303" s="16" t="inlineStr">
         <is>
-          <t>A027_HARIHAR</t>
+          <t>G_M_GUARD_CUT</t>
         </is>
       </c>
       <c r="I303" s="16" t="inlineStr">
@@ -41927,7 +41942,7 @@
       </c>
       <c r="H304" s="16" t="inlineStr">
         <is>
-          <t>A027_FAIZAN</t>
+          <t>C18-003_PRATEEK</t>
         </is>
       </c>
       <c r="I304" s="16" t="inlineStr">
@@ -42009,7 +42024,7 @@
       </c>
       <c r="H305" s="16" t="inlineStr">
         <is>
-          <t>A027_FAIZAN</t>
+          <t>C18-003_PRATEEK</t>
         </is>
       </c>
       <c r="I305" s="16" t="inlineStr">
@@ -42082,7 +42097,7 @@
       </c>
       <c r="H306" s="16" t="inlineStr">
         <is>
-          <t>A027_FAIZAN</t>
+          <t>C18-003_PRATEEK</t>
         </is>
       </c>
       <c r="I306" s="16" t="inlineStr">
@@ -42155,7 +42170,7 @@
       </c>
       <c r="H307" s="16" t="inlineStr">
         <is>
-          <t>A027_MALHOTRA</t>
+          <t>C17-001_SETH</t>
         </is>
       </c>
       <c r="I307" s="16" t="inlineStr">
@@ -42237,7 +42252,7 @@
       </c>
       <c r="H308" s="16" t="inlineStr">
         <is>
-          <t>A027_MALHOTRA</t>
+          <t>C17-001_SETH</t>
         </is>
       </c>
       <c r="I308" s="16" t="inlineStr">
@@ -42310,7 +42325,7 @@
       </c>
       <c r="H309" s="16" t="inlineStr">
         <is>
-          <t>A027_MALHOTRA</t>
+          <t>C17-001_SETH</t>
         </is>
       </c>
       <c r="I309" s="16" t="inlineStr">
@@ -42383,7 +42398,7 @@
       </c>
       <c r="H310" s="16" t="inlineStr">
         <is>
-          <t>A027_SUJATA</t>
+          <t>G_V_WOMAN_SAREE_CUT</t>
         </is>
       </c>
       <c r="I310" s="16" t="inlineStr">
@@ -42466,7 +42481,7 @@
       </c>
       <c r="H311" s="16" t="inlineStr">
         <is>
-          <t>A027_SUJATA</t>
+          <t>G_V_WOMAN_SAREE_CUT</t>
         </is>
       </c>
       <c r="I311" s="16" t="inlineStr">
@@ -42539,7 +42554,7 @@
       </c>
       <c r="H312" s="16" t="inlineStr">
         <is>
-          <t>A027_SUJATA</t>
+          <t>G_V_WOMAN_SAREE_CUT</t>
         </is>
       </c>
       <c r="I312" s="16" t="inlineStr">
@@ -42612,7 +42627,7 @@
       </c>
       <c r="H313" s="16" t="inlineStr">
         <is>
-          <t>A027_PRAKASH</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I313" s="16" t="inlineStr">
@@ -42694,7 +42709,7 @@
       </c>
       <c r="H314" s="16" t="inlineStr">
         <is>
-          <t>A027_PRAKASH</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I314" s="16" t="inlineStr">
@@ -42767,7 +42782,7 @@
       </c>
       <c r="H315" s="16" t="inlineStr">
         <is>
-          <t>A027_PRAKASH</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I315" s="16" t="inlineStr">
@@ -42840,7 +42855,7 @@
       </c>
       <c r="H316" s="16" t="inlineStr">
         <is>
-          <t>A027_ANITA</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="I316" s="16" t="inlineStr">
@@ -42923,7 +42938,7 @@
       </c>
       <c r="H317" s="16" t="inlineStr">
         <is>
-          <t>A027_ANITA</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="I317" s="16" t="inlineStr">
@@ -42996,7 +43011,7 @@
       </c>
       <c r="H318" s="16" t="inlineStr">
         <is>
-          <t>A027_ANITA</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="I318" s="16" t="inlineStr">
@@ -43069,7 +43084,7 @@
       </c>
       <c r="H319" s="16" t="inlineStr">
         <is>
-          <t>A027_RAGHUNATH</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="I319" s="16" t="inlineStr">
@@ -43151,7 +43166,7 @@
       </c>
       <c r="H320" s="16" t="inlineStr">
         <is>
-          <t>A027_RAGHUNATH</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="I320" s="16" t="inlineStr">
@@ -43224,7 +43239,7 @@
       </c>
       <c r="H321" s="16" t="inlineStr">
         <is>
-          <t>A027_RAGHUNATH</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="I321" s="16" t="inlineStr">
@@ -43297,7 +43312,7 @@
       </c>
       <c r="H322" s="16" t="inlineStr">
         <is>
-          <t>A027_ABHIJIT</t>
+          <t>C002_KUNAL</t>
         </is>
       </c>
       <c r="I322" s="16" t="inlineStr">
@@ -43380,7 +43395,7 @@
       </c>
       <c r="H323" s="16" t="inlineStr">
         <is>
-          <t>A027_ABHIJIT</t>
+          <t>C002_KUNAL</t>
         </is>
       </c>
       <c r="I323" s="16" t="inlineStr">
@@ -43453,7 +43468,7 @@
       </c>
       <c r="H324" s="16" t="inlineStr">
         <is>
-          <t>A027_ABHIJIT</t>
+          <t>C002_KUNAL</t>
         </is>
       </c>
       <c r="I324" s="16" t="inlineStr">
@@ -43526,7 +43541,7 @@
       </c>
       <c r="H325" s="16" t="inlineStr">
         <is>
-          <t>A027_GOPI</t>
+          <t>G_RAMU</t>
         </is>
       </c>
       <c r="I325" s="16" t="inlineStr">
@@ -43552,7 +43567,7 @@
       <c r="M325" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 10/10
-Safaiwala Gopi</t>
+Safaiwala Ramu</t>
         </is>
       </c>
       <c r="N325" s="16" t="inlineStr">
@@ -43608,7 +43623,7 @@
       </c>
       <c r="H326" s="16" t="inlineStr">
         <is>
-          <t>A027_GOPI</t>
+          <t>G_RAMU</t>
         </is>
       </c>
       <c r="I326" s="16" t="inlineStr">
@@ -43681,7 +43696,7 @@
       </c>
       <c r="H327" s="16" t="inlineStr">
         <is>
-          <t>A027_HARIHAR</t>
+          <t>G_M_GUARD_CUT</t>
         </is>
       </c>
       <c r="I327" s="16" t="inlineStr">
@@ -44860,7 +44875,7 @@
       <c r="G343" s="16" t="inlineStr"/>
       <c r="H343" s="16" t="inlineStr">
         <is>
-          <t>P_A028_STETHO</t>
+          <t>P_STETHOSCOPE</t>
         </is>
       </c>
       <c r="I343" s="16" t="inlineStr">
@@ -45164,7 +45179,7 @@
       </c>
       <c r="H347" s="16" t="inlineStr">
         <is>
-          <t>A028_JASSI</t>
+          <t>C005_VICKY</t>
         </is>
       </c>
       <c r="I347" s="16" t="inlineStr">
@@ -45247,7 +45262,7 @@
       </c>
       <c r="H348" s="16" t="inlineStr">
         <is>
-          <t>A028_JASSI</t>
+          <t>C005_VICKY</t>
         </is>
       </c>
       <c r="I348" s="16" t="inlineStr">
@@ -45320,7 +45335,7 @@
       </c>
       <c r="H349" s="16" t="inlineStr">
         <is>
-          <t>A028_JASSI</t>
+          <t>C005_VICKY</t>
         </is>
       </c>
       <c r="I349" s="16" t="inlineStr">
@@ -45393,7 +45408,7 @@
       </c>
       <c r="H350" s="16" t="inlineStr">
         <is>
-          <t>A028_JASSI</t>
+          <t>C005_VICKY</t>
         </is>
       </c>
       <c r="I350" s="16" t="inlineStr">
@@ -45466,7 +45481,7 @@
       </c>
       <c r="H351" s="16" t="inlineStr">
         <is>
-          <t>A028_BAJWA</t>
+          <t>C16-001_DRMEHTA</t>
         </is>
       </c>
       <c r="I351" s="16" t="inlineStr">
@@ -45549,7 +45564,7 @@
       </c>
       <c r="H352" s="16" t="inlineStr">
         <is>
-          <t>A028_BAJWA</t>
+          <t>C16-001_DRMEHTA</t>
         </is>
       </c>
       <c r="I352" s="16" t="inlineStr">
@@ -45622,7 +45637,7 @@
       </c>
       <c r="H353" s="16" t="inlineStr">
         <is>
-          <t>A028_BAJWA</t>
+          <t>C16-001_DRMEHTA</t>
         </is>
       </c>
       <c r="I353" s="16" t="inlineStr">
@@ -46982,7 +46997,7 @@
       </c>
       <c r="H371" s="16" t="inlineStr">
         <is>
-          <t>A028_ANU</t>
+          <t>C001_ANJALI</t>
         </is>
       </c>
       <c r="I371" s="16" t="inlineStr">
@@ -47064,7 +47079,7 @@
       </c>
       <c r="H372" s="16" t="inlineStr">
         <is>
-          <t>A028_ANU</t>
+          <t>C001_ANJALI</t>
         </is>
       </c>
       <c r="I372" s="16" t="inlineStr">
@@ -47137,7 +47152,7 @@
       </c>
       <c r="H373" s="16" t="inlineStr">
         <is>
-          <t>A028_ANU</t>
+          <t>C001_ANJALI</t>
         </is>
       </c>
       <c r="I373" s="16" t="inlineStr">
@@ -47886,7 +47901,7 @@
       </c>
       <c r="H383" s="16" t="inlineStr">
         <is>
-          <t>A029_V_GUPTA</t>
+          <t>C04-008_GUPTA_SLUMPED</t>
         </is>
       </c>
       <c r="I383" s="16" t="inlineStr">
@@ -47959,7 +47974,7 @@
       </c>
       <c r="H384" s="16" t="inlineStr">
         <is>
-          <t>A029_V_GUPTA</t>
+          <t>C04-008_GUPTA_SLUMPED</t>
         </is>
       </c>
       <c r="I384" s="16" t="inlineStr">
@@ -48028,7 +48043,7 @@
       </c>
       <c r="H385" s="16" t="inlineStr">
         <is>
-          <t>A029_V_GUPTA</t>
+          <t>C04-008_GUPTA_SLUMPED</t>
         </is>
       </c>
       <c r="I385" s="16" t="inlineStr">
@@ -48247,7 +48262,7 @@
       <c r="G388" s="16" t="inlineStr"/>
       <c r="H388" s="16" t="inlineStr">
         <is>
-          <t>P_A029_SAFE</t>
+          <t>P_TIJORI</t>
         </is>
       </c>
       <c r="I388" s="16" t="inlineStr">
@@ -48393,7 +48408,7 @@
       <c r="G390" s="16" t="inlineStr"/>
       <c r="H390" s="16" t="inlineStr">
         <is>
-          <t>P_A029_GLASS</t>
+          <t>P_THAALI_LASSI</t>
         </is>
       </c>
       <c r="I390" s="16" t="inlineStr">
@@ -48466,7 +48481,7 @@
       <c r="G391" s="16" t="inlineStr"/>
       <c r="H391" s="16" t="inlineStr">
         <is>
-          <t>P_A029_CHASHMA</t>
+          <t>P_BROKEN_GLASSES_CUT</t>
         </is>
       </c>
       <c r="I391" s="16" t="inlineStr">
@@ -48624,7 +48639,7 @@
       </c>
       <c r="H393" s="16" t="inlineStr">
         <is>
-          <t>A029_RAMDAYAL</t>
+          <t>C006_GUPTA</t>
         </is>
       </c>
       <c r="I393" s="16" t="inlineStr">
@@ -48706,7 +48721,7 @@
       </c>
       <c r="H394" s="16" t="inlineStr">
         <is>
-          <t>A029_RAMDAYAL</t>
+          <t>C006_GUPTA</t>
         </is>
       </c>
       <c r="I394" s="16" t="inlineStr">
@@ -48779,7 +48794,7 @@
       </c>
       <c r="H395" s="16" t="inlineStr">
         <is>
-          <t>A029_RAMDAYAL</t>
+          <t>C006_GUPTA</t>
         </is>
       </c>
       <c r="I395" s="16" t="inlineStr">
@@ -48852,7 +48867,7 @@
       </c>
       <c r="H396" s="16" t="inlineStr">
         <is>
-          <t>A029_RAMDAYAL</t>
+          <t>C006_GUPTA</t>
         </is>
       </c>
       <c r="I396" s="16" t="inlineStr">
@@ -48925,7 +48940,7 @@
       </c>
       <c r="H397" s="16" t="inlineStr">
         <is>
-          <t>A029_ASHOK</t>
+          <t>C004_AMIT</t>
         </is>
       </c>
       <c r="I397" s="16" t="inlineStr">
@@ -49008,7 +49023,7 @@
       </c>
       <c r="H398" s="16" t="inlineStr">
         <is>
-          <t>A029_ASHOK</t>
+          <t>C004_AMIT</t>
         </is>
       </c>
       <c r="I398" s="16" t="inlineStr">
@@ -49081,7 +49096,7 @@
       </c>
       <c r="H399" s="16" t="inlineStr">
         <is>
-          <t>A029_ASHOK</t>
+          <t>C004_AMIT</t>
         </is>
       </c>
       <c r="I399" s="16" t="inlineStr">
@@ -49154,7 +49169,7 @@
       </c>
       <c r="H400" s="16" t="inlineStr">
         <is>
-          <t>A029_KAMINI</t>
+          <t>C004_SNEHA</t>
         </is>
       </c>
       <c r="I400" s="16" t="inlineStr">
@@ -49236,7 +49251,7 @@
       </c>
       <c r="H401" s="16" t="inlineStr">
         <is>
-          <t>A029_KAMINI</t>
+          <t>C004_SNEHA</t>
         </is>
       </c>
       <c r="I401" s="16" t="inlineStr">
@@ -49309,7 +49324,7 @@
       </c>
       <c r="H402" s="16" t="inlineStr">
         <is>
-          <t>A029_KAMINI</t>
+          <t>C004_SNEHA</t>
         </is>
       </c>
       <c r="I402" s="16" t="inlineStr">
@@ -49382,7 +49397,7 @@
       </c>
       <c r="H403" s="16" t="inlineStr">
         <is>
-          <t>A029_RAJU</t>
+          <t>C003_BHATIJA</t>
         </is>
       </c>
       <c r="I403" s="16" t="inlineStr">
@@ -49465,7 +49480,7 @@
       </c>
       <c r="H404" s="16" t="inlineStr">
         <is>
-          <t>A029_RAJU</t>
+          <t>C003_BHATIJA</t>
         </is>
       </c>
       <c r="I404" s="16" t="inlineStr">
@@ -49538,7 +49553,7 @@
       </c>
       <c r="H405" s="16" t="inlineStr">
         <is>
-          <t>A029_SHERU</t>
+          <t>G_V_MAN_BLUE_CUT</t>
         </is>
       </c>
       <c r="I405" s="16" t="inlineStr">
@@ -49621,7 +49636,7 @@
       </c>
       <c r="H406" s="16" t="inlineStr">
         <is>
-          <t>A029_SHERU</t>
+          <t>G_V_MAN_BLUE_CUT</t>
         </is>
       </c>
       <c r="I406" s="16" t="inlineStr">
@@ -49694,7 +49709,7 @@
       </c>
       <c r="H407" s="16" t="inlineStr">
         <is>
-          <t>A029_GOMTI</t>
+          <t>C004_MAA</t>
         </is>
       </c>
       <c r="I407" s="16" t="inlineStr">
@@ -49776,7 +49791,7 @@
       </c>
       <c r="H408" s="16" t="inlineStr">
         <is>
-          <t>A029_GOMTI</t>
+          <t>C004_MAA</t>
         </is>
       </c>
       <c r="I408" s="16" t="inlineStr">
@@ -49849,7 +49864,7 @@
       </c>
       <c r="H409" s="16" t="inlineStr">
         <is>
-          <t>A029_PATEL</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I409" s="16" t="inlineStr">
@@ -49932,7 +49947,7 @@
       </c>
       <c r="H410" s="16" t="inlineStr">
         <is>
-          <t>A029_PATEL</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I410" s="16" t="inlineStr">
@@ -50005,7 +50020,7 @@
       </c>
       <c r="H411" s="16" t="inlineStr">
         <is>
-          <t>A029_PATEL</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I411" s="16" t="inlineStr">
@@ -50078,7 +50093,7 @@
       </c>
       <c r="H412" s="16" t="inlineStr">
         <is>
-          <t>A029_CHHEDI</t>
+          <t>G_BHOLA</t>
         </is>
       </c>
       <c r="I412" s="16" t="inlineStr">
@@ -50104,7 +50119,7 @@
       <c r="M412" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 8/9
-Naukar Chhedi</t>
+Naukar Bhola</t>
         </is>
       </c>
       <c r="N412" s="16" t="inlineStr">
@@ -50160,7 +50175,7 @@
       </c>
       <c r="H413" s="16" t="inlineStr">
         <is>
-          <t>A029_CHHEDI</t>
+          <t>G_BHOLA</t>
         </is>
       </c>
       <c r="I413" s="16" t="inlineStr">
@@ -50233,7 +50248,7 @@
       </c>
       <c r="H414" s="16" t="inlineStr">
         <is>
-          <t>A029_ANWAR</t>
+          <t>C010_MAHESH</t>
         </is>
       </c>
       <c r="I414" s="16" t="inlineStr">
@@ -50315,7 +50330,7 @@
       </c>
       <c r="H415" s="16" t="inlineStr">
         <is>
-          <t>A029_ANWAR</t>
+          <t>C010_MAHESH</t>
         </is>
       </c>
       <c r="I415" s="16" t="inlineStr">
@@ -50388,7 +50403,7 @@
       </c>
       <c r="H416" s="16" t="inlineStr">
         <is>
-          <t>A029_SHERU</t>
+          <t>G_V_MAN_BLUE_CUT</t>
         </is>
       </c>
       <c r="I416" s="16" t="inlineStr">
@@ -51571,7 +51586,7 @@
       <c r="G432" s="16" t="inlineStr"/>
       <c r="H432" s="16" t="inlineStr">
         <is>
-          <t>P_A030_FLASK</t>
+          <t>P_STEEL_THERMOS</t>
         </is>
       </c>
       <c r="I432" s="16" t="inlineStr">
@@ -51802,7 +51817,7 @@
       </c>
       <c r="H435" s="16" t="inlineStr">
         <is>
-          <t>A030_TANMAY</t>
+          <t>G_M_GREY_HOODIE_CUT</t>
         </is>
       </c>
       <c r="I435" s="16" t="inlineStr">
@@ -51885,7 +51900,7 @@
       </c>
       <c r="H436" s="16" t="inlineStr">
         <is>
-          <t>A030_TANMAY</t>
+          <t>G_M_GREY_HOODIE_CUT</t>
         </is>
       </c>
       <c r="I436" s="16" t="inlineStr">
@@ -51958,7 +51973,7 @@
       </c>
       <c r="H437" s="16" t="inlineStr">
         <is>
-          <t>A030_TANMAY</t>
+          <t>G_M_GREY_HOODIE_CUT</t>
         </is>
       </c>
       <c r="I437" s="16" t="inlineStr">
@@ -52031,7 +52046,7 @@
       </c>
       <c r="H438" s="16" t="inlineStr">
         <is>
-          <t>A030_GARGI</t>
+          <t>C005_NEHA</t>
         </is>
       </c>
       <c r="I438" s="16" t="inlineStr">
@@ -52113,7 +52128,7 @@
       </c>
       <c r="H439" s="16" t="inlineStr">
         <is>
-          <t>A030_GARGI</t>
+          <t>C005_NEHA</t>
         </is>
       </c>
       <c r="I439" s="16" t="inlineStr">
@@ -52186,7 +52201,7 @@
       </c>
       <c r="H440" s="16" t="inlineStr">
         <is>
-          <t>A030_BISHT</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="I440" s="16" t="inlineStr">
@@ -52268,7 +52283,7 @@
       </c>
       <c r="H441" s="16" t="inlineStr">
         <is>
-          <t>A030_BISHT</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="I441" s="16" t="inlineStr">
@@ -52341,7 +52356,7 @@
       </c>
       <c r="H442" s="16" t="inlineStr">
         <is>
-          <t>A030_BISHT</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="I442" s="16" t="inlineStr">
@@ -52414,7 +52429,7 @@
       </c>
       <c r="H443" s="16" t="inlineStr">
         <is>
-          <t>A030_SURABHI</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="I443" s="16" t="inlineStr">
@@ -52497,7 +52512,7 @@
       </c>
       <c r="H444" s="16" t="inlineStr">
         <is>
-          <t>A030_SURABHI</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="I444" s="16" t="inlineStr">
@@ -52570,7 +52585,7 @@
       </c>
       <c r="H445" s="16" t="inlineStr">
         <is>
-          <t>A030_SURABHI</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="I445" s="16" t="inlineStr">
@@ -52643,7 +52658,7 @@
       </c>
       <c r="H446" s="16" t="inlineStr">
         <is>
-          <t>A030_SURABHI</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="I446" s="16" t="inlineStr">
@@ -52716,7 +52731,7 @@
       </c>
       <c r="H447" s="16" t="inlineStr">
         <is>
-          <t>A030_POORAN</t>
+          <t>G_HARIYA</t>
         </is>
       </c>
       <c r="I447" s="16" t="inlineStr">
@@ -52742,7 +52757,7 @@
       <c r="M447" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 5/10
-Guide Pooran
+Guide Hariya
 (doorbeen bechne ka shak)</t>
         </is>
       </c>
@@ -52799,7 +52814,7 @@
       </c>
       <c r="H448" s="16" t="inlineStr">
         <is>
-          <t>A030_POORAN</t>
+          <t>G_HARIYA</t>
         </is>
       </c>
       <c r="I448" s="16" t="inlineStr">
@@ -52872,7 +52887,7 @@
       </c>
       <c r="H449" s="16" t="inlineStr">
         <is>
-          <t>A030_POORAN</t>
+          <t>G_HARIYA</t>
         </is>
       </c>
       <c r="I449" s="16" t="inlineStr">
@@ -52945,7 +52960,7 @@
       </c>
       <c r="H450" s="16" t="inlineStr">
         <is>
-          <t>A030_HEMLATA</t>
+          <t>G_W_MAROON_SAREE_CUT</t>
         </is>
       </c>
       <c r="I450" s="16" t="inlineStr">
@@ -53028,7 +53043,7 @@
       </c>
       <c r="H451" s="16" t="inlineStr">
         <is>
-          <t>A030_HEMLATA</t>
+          <t>G_W_MAROON_SAREE_CUT</t>
         </is>
       </c>
       <c r="I451" s="16" t="inlineStr">
@@ -53101,7 +53116,7 @@
       </c>
       <c r="H452" s="16" t="inlineStr">
         <is>
-          <t>A030_HEMLATA</t>
+          <t>G_W_MAROON_SAREE_CUT</t>
         </is>
       </c>
       <c r="I452" s="16" t="inlineStr">
@@ -53174,7 +53189,7 @@
       </c>
       <c r="H453" s="16" t="inlineStr">
         <is>
-          <t>A030_HRITHIK</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I453" s="16" t="inlineStr">
@@ -53256,7 +53271,7 @@
       </c>
       <c r="H454" s="16" t="inlineStr">
         <is>
-          <t>A030_HRITHIK</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I454" s="16" t="inlineStr">
@@ -53329,7 +53344,7 @@
       </c>
       <c r="H455" s="16" t="inlineStr">
         <is>
-          <t>A030_HRITHIK</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I455" s="16" t="inlineStr">
@@ -53402,7 +53417,7 @@
       </c>
       <c r="H456" s="16" t="inlineStr">
         <is>
-          <t>A030_NAVEEN</t>
+          <t>C10-004_DEEPAK</t>
         </is>
       </c>
       <c r="I456" s="16" t="inlineStr">
@@ -53485,7 +53500,7 @@
       </c>
       <c r="H457" s="16" t="inlineStr">
         <is>
-          <t>A030_NAVEEN</t>
+          <t>C10-004_DEEPAK</t>
         </is>
       </c>
       <c r="I457" s="16" t="inlineStr">
@@ -53558,7 +53573,7 @@
       </c>
       <c r="H458" s="16" t="inlineStr">
         <is>
-          <t>A030_NAVEEN</t>
+          <t>C10-004_DEEPAK</t>
         </is>
       </c>
       <c r="I458" s="16" t="inlineStr">
@@ -53631,7 +53646,7 @@
       </c>
       <c r="H459" s="16" t="inlineStr">
         <is>
-          <t>A030_HARI</t>
+          <t>G_BAHADUR</t>
         </is>
       </c>
       <c r="I459" s="16" t="inlineStr">
@@ -53657,7 +53672,7 @@
       <c r="M459" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 9/10
-Chowkidar Hari</t>
+Chowkidar Bahadur</t>
         </is>
       </c>
       <c r="N459" s="16" t="inlineStr">
@@ -53713,7 +53728,7 @@
       </c>
       <c r="H460" s="16" t="inlineStr">
         <is>
-          <t>A030_HARI</t>
+          <t>G_BAHADUR</t>
         </is>
       </c>
       <c r="I460" s="16" t="inlineStr">
@@ -53786,7 +53801,7 @@
       </c>
       <c r="H461" s="16" t="inlineStr">
         <is>
-          <t>A030_HARI</t>
+          <t>G_BAHADUR</t>
         </is>
       </c>
       <c r="I461" s="16" t="inlineStr">
@@ -53859,7 +53874,7 @@
       </c>
       <c r="H462" s="16" t="inlineStr">
         <is>
-          <t>A030_KUNDAN</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I462" s="16" t="inlineStr">
@@ -53941,7 +53956,7 @@
       </c>
       <c r="H463" s="16" t="inlineStr">
         <is>
-          <t>A030_KUNDAN</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I463" s="16" t="inlineStr">
@@ -54014,7 +54029,7 @@
       </c>
       <c r="H464" s="16" t="inlineStr">
         <is>
-          <t>A030_KUNDAN</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I464" s="16" t="inlineStr">
@@ -54087,7 +54102,7 @@
       </c>
       <c r="H465" s="16" t="inlineStr">
         <is>
-          <t>A030_TANMAY</t>
+          <t>G_M_GREY_HOODIE_CUT</t>
         </is>
       </c>
       <c r="I465" s="16" t="inlineStr">
@@ -56858,7 +56873,7 @@
       </c>
       <c r="H9" s="16" t="inlineStr">
         <is>
-          <t>P_A021_GLASS ... P_A021_PHOTO</t>
+          <t>P_KAANCH_TUKDE_CUT ... P_A021_PHOTO</t>
         </is>
       </c>
       <c r="I9" s="16" t="inlineStr">
@@ -56935,7 +56950,7 @@
       </c>
       <c r="H10" s="16" t="inlineStr">
         <is>
-          <t>P_A021_GLASS ... P_A021_PHOTO</t>
+          <t>P_KAANCH_TUKDE_CUT ... P_A021_PHOTO</t>
         </is>
       </c>
       <c r="I10" s="16" t="inlineStr">
@@ -57008,7 +57023,7 @@
       </c>
       <c r="H11" s="16" t="inlineStr">
         <is>
-          <t>P_A021_GLASS ... P_A021_PHOTO</t>
+          <t>P_KAANCH_TUKDE_CUT ... P_A021_PHOTO</t>
         </is>
       </c>
       <c r="I11" s="16" t="inlineStr">
@@ -57081,7 +57096,7 @@
       </c>
       <c r="H12" s="16" t="inlineStr">
         <is>
-          <t>A021_RAHUL</t>
+          <t>C10-008_KARAN</t>
         </is>
       </c>
       <c r="I12" s="16" t="inlineStr">
@@ -57164,7 +57179,7 @@
       </c>
       <c r="H13" s="16" t="inlineStr">
         <is>
-          <t>A021_RAHUL</t>
+          <t>C10-008_KARAN</t>
         </is>
       </c>
       <c r="I13" s="16" t="inlineStr">
@@ -57237,7 +57252,7 @@
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>A021_RAHUL</t>
+          <t>C10-008_KARAN</t>
         </is>
       </c>
       <c r="I14" s="16" t="inlineStr">
@@ -57310,7 +57325,7 @@
       </c>
       <c r="H15" s="16" t="inlineStr">
         <is>
-          <t>A021_JOSHI</t>
+          <t>C009_JOSHI</t>
         </is>
       </c>
       <c r="I15" s="16" t="inlineStr">
@@ -57393,7 +57408,7 @@
       </c>
       <c r="H16" s="16" t="inlineStr">
         <is>
-          <t>A021_JOSHI</t>
+          <t>C009_JOSHI</t>
         </is>
       </c>
       <c r="I16" s="16" t="inlineStr">
@@ -57466,7 +57481,7 @@
       </c>
       <c r="H17" s="16" t="inlineStr">
         <is>
-          <t>A021_NARESH</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I17" s="16" t="inlineStr">
@@ -57548,7 +57563,7 @@
       </c>
       <c r="H18" s="16" t="inlineStr">
         <is>
-          <t>A021_NARESH</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I18" s="16" t="inlineStr">
@@ -57621,7 +57636,7 @@
       </c>
       <c r="H19" s="16" t="inlineStr">
         <is>
-          <t>A021_NARESH</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I19" s="16" t="inlineStr">
@@ -57694,7 +57709,7 @@
       </c>
       <c r="H20" s="16" t="inlineStr">
         <is>
-          <t>A021_BABLU</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="I20" s="16" t="inlineStr">
@@ -57777,7 +57792,7 @@
       </c>
       <c r="H21" s="16" t="inlineStr">
         <is>
-          <t>A021_BABLU</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="I21" s="16" t="inlineStr">
@@ -57850,7 +57865,7 @@
       </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>A021_ADITI</t>
+          <t>C004_SNEHA</t>
         </is>
       </c>
       <c r="I22" s="16" t="inlineStr">
@@ -57932,7 +57947,7 @@
       </c>
       <c r="H23" s="16" t="inlineStr">
         <is>
-          <t>A021_ADITI</t>
+          <t>C004_SNEHA</t>
         </is>
       </c>
       <c r="I23" s="16" t="inlineStr">
@@ -59043,7 +59058,7 @@
       </c>
       <c r="H38" s="16" t="inlineStr">
         <is>
-          <t>A022_REDDY</t>
+          <t>C08-007_KAPOOR</t>
         </is>
       </c>
       <c r="I38" s="16" t="inlineStr">
@@ -59126,7 +59141,7 @@
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>A022_REDDY</t>
+          <t>C08-007_KAPOOR</t>
         </is>
       </c>
       <c r="I39" s="16" t="inlineStr">
@@ -59199,7 +59214,7 @@
       </c>
       <c r="H40" s="16" t="inlineStr">
         <is>
-          <t>A022_DSOUZA</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I40" s="16" t="inlineStr">
@@ -59281,7 +59296,7 @@
       </c>
       <c r="H41" s="16" t="inlineStr">
         <is>
-          <t>A022_DSOUZA</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I41" s="16" t="inlineStr">
@@ -59354,7 +59369,7 @@
       </c>
       <c r="H42" s="16" t="inlineStr">
         <is>
-          <t>A022_DSOUZA</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I42" s="16" t="inlineStr">
@@ -59427,7 +59442,7 @@
       </c>
       <c r="H43" s="16" t="inlineStr">
         <is>
-          <t>A022_LATA</t>
+          <t>G_V_WOMAN_SAREE_CUT</t>
         </is>
       </c>
       <c r="I43" s="16" t="inlineStr">
@@ -59510,7 +59525,7 @@
       </c>
       <c r="H44" s="16" t="inlineStr">
         <is>
-          <t>A022_LATA</t>
+          <t>G_V_WOMAN_SAREE_CUT</t>
         </is>
       </c>
       <c r="I44" s="16" t="inlineStr">
@@ -59739,7 +59754,7 @@
       </c>
       <c r="H47" s="16" t="inlineStr">
         <is>
-          <t>A022_MEENA</t>
+          <t>C005_NEHA</t>
         </is>
       </c>
       <c r="I47" s="16" t="inlineStr">
@@ -59821,7 +59836,7 @@
       </c>
       <c r="H48" s="16" t="inlineStr">
         <is>
-          <t>A022_MEENA</t>
+          <t>C005_NEHA</t>
         </is>
       </c>
       <c r="I48" s="16" t="inlineStr">
@@ -60709,7 +60724,7 @@
       </c>
       <c r="H60" s="16" t="inlineStr">
         <is>
-          <t>P_A027_CASE ... P_A027_CCTV</t>
+          <t>P_A027_CASE ... P_CCTV_MONITOR</t>
         </is>
       </c>
       <c r="I60" s="16" t="inlineStr">
@@ -60786,7 +60801,7 @@
       </c>
       <c r="H61" s="16" t="inlineStr">
         <is>
-          <t>P_A027_CASE ... P_A027_CCTV</t>
+          <t>P_A027_CASE ... P_CCTV_MONITOR</t>
         </is>
       </c>
       <c r="I61" s="16" t="inlineStr">
@@ -60859,7 +60874,7 @@
       </c>
       <c r="H62" s="16" t="inlineStr">
         <is>
-          <t>P_A027_CASE ... P_A027_CCTV</t>
+          <t>P_A027_CASE ... P_CCTV_MONITOR</t>
         </is>
       </c>
       <c r="I62" s="16" t="inlineStr">
@@ -60932,7 +60947,7 @@
       </c>
       <c r="H63" s="16" t="inlineStr">
         <is>
-          <t>A027_POOJA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="I63" s="16" t="inlineStr">
@@ -61015,7 +61030,7 @@
       </c>
       <c r="H64" s="16" t="inlineStr">
         <is>
-          <t>A027_POOJA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="I64" s="16" t="inlineStr">
@@ -61088,7 +61103,7 @@
       </c>
       <c r="H65" s="16" t="inlineStr">
         <is>
-          <t>A027_HARIHAR</t>
+          <t>G_M_GUARD_CUT</t>
         </is>
       </c>
       <c r="I65" s="16" t="inlineStr">
@@ -61171,7 +61186,7 @@
       </c>
       <c r="H66" s="16" t="inlineStr">
         <is>
-          <t>A027_MALHOTRA</t>
+          <t>C17-001_SETH</t>
         </is>
       </c>
       <c r="I66" s="16" t="inlineStr">
@@ -61253,7 +61268,7 @@
       </c>
       <c r="H67" s="16" t="inlineStr">
         <is>
-          <t>A027_MALHOTRA</t>
+          <t>C17-001_SETH</t>
         </is>
       </c>
       <c r="I67" s="16" t="inlineStr">
@@ -61326,7 +61341,7 @@
       </c>
       <c r="H68" s="16" t="inlineStr">
         <is>
-          <t>A027_MALHOTRA</t>
+          <t>C17-001_SETH</t>
         </is>
       </c>
       <c r="I68" s="16" t="inlineStr">
@@ -61399,7 +61414,7 @@
       </c>
       <c r="H69" s="16" t="inlineStr">
         <is>
-          <t>A027_ANITA</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="I69" s="16" t="inlineStr">
@@ -61482,7 +61497,7 @@
       </c>
       <c r="H70" s="16" t="inlineStr">
         <is>
-          <t>A027_ANITA</t>
+          <t>C007_KAVYA</t>
         </is>
       </c>
       <c r="I70" s="16" t="inlineStr">
@@ -61555,7 +61570,7 @@
       </c>
       <c r="H71" s="16" t="inlineStr">
         <is>
-          <t>A027_ABHIJIT</t>
+          <t>C002_KUNAL</t>
         </is>
       </c>
       <c r="I71" s="16" t="inlineStr">
@@ -61638,7 +61653,7 @@
       </c>
       <c r="H72" s="16" t="inlineStr">
         <is>
-          <t>A027_ABHIJIT</t>
+          <t>C002_KUNAL</t>
         </is>
       </c>
       <c r="I72" s="16" t="inlineStr">
@@ -62321,29 +62336,29 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>P_A021_GLASS</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>P_KAANCH_TUKDE_CUT</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>A021</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>Broken whisky glass on a carpet</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Broken whisky glass on a carpet. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -62456,218 +62471,218 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>A021_RAHUL</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>C10-008_KARAN</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>A021</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Beta Rahul (mill bechne par jhagda)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 30, casual shirt, sunglasses on head. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>A021_PRIYA</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>G_W_ORANGE_KURTI_CUT</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>A021</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>Beti Priya</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 27, kurti, handbag. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>A021_JOSHI</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>C009_JOSHI</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>A021</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Manager Joshi (hisaab mein gadbad)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 50, formal shirt, spectacles, files. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>A021_SUMAN</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>G_W_MAROON_SAREE_CUT</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>A021</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>Patni Suman (beema inke naam)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 52, salwar suit, dupatta on head. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>A021_NARESH</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>G_M_CAMERA_CUT</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>A021</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Bhai Naresh</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 55, kurta, camera around neck, cheerful innocent face. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>A021_BABLU</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>G_V_MAN_GREY_CUT</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>A021</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>Driver Bablu (gaadi ki chaabi)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian driver about 35, white uniform, car keys. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>A021_SINGHANIA</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>C08-004_MR_RATHI</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>A021</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Partner Singhania (mill kharidna chahta tha)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian businessman about 55, suit, gold watch, smug. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>A021_ADITI</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>C004_SNEHA</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>A021</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>Bhatiji Aditi</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian young woman about 24, jacket, phone. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -62780,29 +62795,29 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>P_A022_BILL</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>P_REGISTER_TORN</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>A022</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Torn booking register page</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Torn booking register page. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -62861,137 +62876,137 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>A022_REDDY</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>C08-007_KAPOOR</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>A022</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>Partner Reddy (resort ka bantwara)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Telugu businessman about 50, linen shirt, gold chain. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>A022_SWATI</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>C007_KAVYA</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>A022</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Beti Swati</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 26, kurti, sunglasses. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>A022_DSOUZA</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>G_V_MAN_CHECK_CUT</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>A022</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>Manager D'Souza</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Goan man about 45, floral shirt, relaxed innocent smile. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>A022_AYYAPPAN</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>G_M_APRON_CUT</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>A022</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Chef Ayyappan (chaku iski rasoi ka)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Kerala chef about 40, chef coat, knife. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>A022_LATA</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>G_V_WOMAN_SAREE_CUT</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>A022</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>Patni Lata (vasiyat inke naam)</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Telugu woman about 50, silk saree. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -63023,83 +63038,83 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>A022_KIRAN</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>C04-010_ARJUN</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>A022</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>Beta Kiran</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 30, t-shirt, backpack. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>A022_MURTHY</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>G_M_OLD_GLASSES_CUT</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>A022</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Accountant Murthy (paison ki herapheri)</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 50, spectacles, ledger. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>A022_MEENA</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>C005_NEHA</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>A022</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="19" t="inlineStr">
         <is>
           <t>Receptionist Meena</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 25, resort uniform. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -63158,29 +63173,29 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>P_A023_TROPHY</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>P_TROPHY</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>A023</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D41" s="18" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Broken trophy on the floor</t>
         </is>
       </c>
-      <c r="E41" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Broken trophy on the floor. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -63347,29 +63362,29 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>A023_MATHEW</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>G_UMPIRE_CUT</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>A023</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D48" s="19" t="inlineStr">
         <is>
           <t>Football referee Mathew</t>
         </is>
       </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian referee about 40, black referee kit, whistle. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -63401,29 +63416,29 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>A023_VINAYAK</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>G_V_MAN_BLUE_CUT</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>A023</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="19" t="inlineStr">
         <is>
           <t>Shatranj khiladi Vinayak (paise udhaar liye)</t>
         </is>
       </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 35, spectacles, chess clock. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -63455,29 +63470,29 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="inlineStr">
-        <is>
-          <t>A023_SOHAM</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>G_CR_VIKRAM_CUT</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>A023</t>
         </is>
       </c>
-      <c r="C52" s="16" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="19" t="inlineStr">
         <is>
           <t>Cricketer Soham (team se nikala)</t>
         </is>
       </c>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Young cricketer about 22, white cricket kit, bat. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -63509,56 +63524,56 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="inlineStr">
-        <is>
-          <t>A023_KAPOOR</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>G_W_PINK_SUIT_CUT</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
         <is>
           <t>A023</t>
         </is>
       </c>
-      <c r="C54" s="16" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D54" s="16" t="inlineStr">
+      <c r="D54" s="19" t="inlineStr">
         <is>
           <t>Golfer Mrs. Kapoor</t>
         </is>
       </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 50, golf cap, golf club. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t>A023_SAINA</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>C008_NEHA</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t>A023</t>
         </is>
       </c>
-      <c r="C55" s="16" t="inlineStr">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D55" s="16" t="inlineStr">
+      <c r="D55" s="19" t="inlineStr">
         <is>
           <t>Badminton khiladi Saina</t>
         </is>
       </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian young woman about 20, sports wear, racket. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -63644,29 +63659,29 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="inlineStr">
-        <is>
-          <t>P_A024_CHAI</t>
-        </is>
-      </c>
-      <c r="B59" s="18" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>P_DO_CHAI_UP</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>A024</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D59" s="18" t="inlineStr">
+      <c r="D59" s="19" t="inlineStr">
         <is>
           <t>Two tea cups on a table, one full</t>
         </is>
       </c>
-      <c r="E59" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Two tea cups on a table, one full. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E59" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -63698,272 +63713,272 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="inlineStr">
-        <is>
-          <t>P_A024_DRAWER</t>
-        </is>
-      </c>
-      <c r="B61" s="18" t="inlineStr">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>P_ALMARI_KHULI</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>A024</t>
         </is>
       </c>
-      <c r="C61" s="18" t="inlineStr">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D61" s="18" t="inlineStr">
+      <c r="D61" s="19" t="inlineStr">
         <is>
           <t>Pulled-out drawer, empty cash envelope</t>
         </is>
       </c>
-      <c r="E61" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Pulled-out drawer, empty cash envelope. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="inlineStr">
-        <is>
-          <t>P_A024_SPECS</t>
-        </is>
-      </c>
-      <c r="B62" s="18" t="inlineStr">
+      <c r="A62" s="19" t="inlineStr">
+        <is>
+          <t>P_BROKEN_GLASSES_CUT</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t>A024</t>
         </is>
       </c>
-      <c r="C62" s="18" t="inlineStr">
+      <c r="C62" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D62" s="18" t="inlineStr">
+      <c r="D62" s="19" t="inlineStr">
         <is>
           <t>Broken spectacles on the floor</t>
         </is>
       </c>
-      <c r="E62" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Broken spectacles on the floor. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>A024_URMILA</t>
-        </is>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t>C010_SUNITA</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="inlineStr">
         <is>
           <t>A024</t>
         </is>
       </c>
-      <c r="C63" s="16" t="inlineStr">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D63" s="16" t="inlineStr">
+      <c r="D63" s="19" t="inlineStr">
         <is>
           <t>Patni Urmila (beema inke naam)</t>
         </is>
       </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 50, cotton saree. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="inlineStr">
-        <is>
-          <t>A024_AMAN</t>
-        </is>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>G_M_GREY_HOODIE_CUT</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t>A024</t>
         </is>
       </c>
-      <c r="C64" s="16" t="inlineStr">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="D64" s="19" t="inlineStr">
         <is>
           <t>Beta Aman (bike ke paise maange)</t>
         </is>
       </c>
-      <c r="E64" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian teenage boy about 18, t-shirt, ice tray. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="inlineStr">
-        <is>
-          <t>A024_KRITIKA</t>
-        </is>
-      </c>
-      <c r="B65" s="16" t="inlineStr">
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>C004_BEHEN</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
         <is>
           <t>A024</t>
         </is>
       </c>
-      <c r="C65" s="16" t="inlineStr">
+      <c r="C65" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D65" s="16" t="inlineStr">
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>Tuition student Kritika</t>
         </is>
       </c>
-      <c r="E65" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian schoolgirl about 15, school uniform, notebook. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="inlineStr">
-        <is>
-          <t>A024_TIWARI</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
+        <is>
+          <t>C004_PADOSI</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="inlineStr">
         <is>
           <t>A024</t>
         </is>
       </c>
-      <c r="C66" s="16" t="inlineStr">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D66" s="19" t="inlineStr">
         <is>
           <t>Padosi Tiwari ji (deewar ko lekar jhagda)</t>
         </is>
       </c>
-      <c r="E66" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 60, kurta, watering can. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="inlineStr">
-        <is>
-          <t>A024_MUKESH</t>
-        </is>
-      </c>
-      <c r="B67" s="16" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>G_V_MAN_BLUE_CUT</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>A024</t>
         </is>
       </c>
-      <c r="C67" s="16" t="inlineStr">
+      <c r="C67" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D67" s="16" t="inlineStr">
+      <c r="D67" s="19" t="inlineStr">
         <is>
           <t>Bhai Mukesh</t>
         </is>
       </c>
-      <c r="E67" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 50, shawl. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>A024_SANJAY</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
+        <is>
+          <t>G_M_YELLOW_KURTA_CUT</t>
+        </is>
+      </c>
+      <c r="B68" s="19" t="inlineStr">
         <is>
           <t>A024</t>
         </is>
       </c>
-      <c r="C68" s="16" t="inlineStr">
+      <c r="C68" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D68" s="19" t="inlineStr">
         <is>
           <t>Kirayedaar Sanjay</t>
         </is>
       </c>
-      <c r="E68" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 35, vest and pajama, tea pan, calm face. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E68" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="inlineStr">
-        <is>
-          <t>A024_SHANTA</t>
-        </is>
-      </c>
-      <c r="B69" s="16" t="inlineStr">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>G_SHANTI</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
         <is>
           <t>A024</t>
         </is>
       </c>
-      <c r="C69" s="16" t="inlineStr">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D69" s="16" t="inlineStr">
-        <is>
-          <t>Kaamwali Shanta (lifaafa isi ne dekha tha)</t>
-        </is>
-      </c>
-      <c r="E69" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian housemaid about 40, saree. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="D69" s="19" t="inlineStr">
+        <is>
+          <t>Kaamwali Shanti (lifaafa isi ne dekha tha)</t>
+        </is>
+      </c>
+      <c r="E69" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="inlineStr">
-        <is>
-          <t>A024_FAROOQ</t>
-        </is>
-      </c>
-      <c r="B70" s="16" t="inlineStr">
+      <c r="A70" s="19" t="inlineStr">
+        <is>
+          <t>G_M_LIGHTMAN_CUT</t>
+        </is>
+      </c>
+      <c r="B70" s="19" t="inlineStr">
         <is>
           <t>A024</t>
         </is>
       </c>
-      <c r="C70" s="16" t="inlineStr">
+      <c r="C70" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="D70" s="19" t="inlineStr">
         <is>
           <t>Electrician Farooq</t>
         </is>
       </c>
-      <c r="E70" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian electrician about 40, blue shirt, tester. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E70" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -64103,29 +64118,29 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="18" t="inlineStr">
-        <is>
-          <t>P_A025_BOOT</t>
-        </is>
-      </c>
-      <c r="B76" s="18" t="inlineStr">
+      <c r="A76" s="19" t="inlineStr">
+        <is>
+          <t>P_MUD_MARKS</t>
+        </is>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
         <is>
           <t>A025</t>
         </is>
       </c>
-      <c r="C76" s="18" t="inlineStr">
+      <c r="C76" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D76" s="18" t="inlineStr">
+      <c r="D76" s="19" t="inlineStr">
         <is>
           <t>Muddy safari boots near the door</t>
         </is>
       </c>
-      <c r="E76" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Muddy safari boots near the door. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E76" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -64157,83 +64172,83 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="inlineStr">
-        <is>
-          <t>A025_ROHIT</t>
-        </is>
-      </c>
-      <c r="B78" s="16" t="inlineStr">
+      <c r="A78" s="19" t="inlineStr">
+        <is>
+          <t>C001_ROHIT</t>
+        </is>
+      </c>
+      <c r="B78" s="19" t="inlineStr">
         <is>
           <t>A025</t>
         </is>
       </c>
-      <c r="C78" s="16" t="inlineStr">
+      <c r="C78" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D78" s="16" t="inlineStr">
+      <c r="D78" s="19" t="inlineStr">
         <is>
           <t>Assistant Rohit (tasveerein churane ka shak)</t>
         </is>
       </c>
-      <c r="E78" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian young man about 26, khaki vest, binoculars. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E78" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="inlineStr">
-        <is>
-          <t>A025_VIVEK</t>
-        </is>
-      </c>
-      <c r="B79" s="16" t="inlineStr">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>G_M_BROWN_JACKET_CUT</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
         <is>
           <t>A025</t>
         </is>
       </c>
-      <c r="C79" s="16" t="inlineStr">
+      <c r="C79" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D79" s="16" t="inlineStr">
+      <c r="D79" s="19" t="inlineStr">
         <is>
           <t>Partner Vivek</t>
         </is>
       </c>
-      <c r="E79" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 45, safari hat, camera, excited innocent face. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E79" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="inlineStr">
-        <is>
-          <t>A025_NAZIYA</t>
-        </is>
-      </c>
-      <c r="B80" s="16" t="inlineStr">
+      <c r="A80" s="19" t="inlineStr">
+        <is>
+          <t>C004_SNEHA</t>
+        </is>
+      </c>
+      <c r="B80" s="19" t="inlineStr">
         <is>
           <t>A025</t>
         </is>
       </c>
-      <c r="C80" s="16" t="inlineStr">
+      <c r="C80" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D80" s="16" t="inlineStr">
+      <c r="D80" s="19" t="inlineStr">
         <is>
           <t>Patni Naziya (talaq ka case)</t>
         </is>
       </c>
-      <c r="E80" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 45, salwar suit, dupatta. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E80" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -64265,137 +64280,137 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="inlineStr">
-        <is>
-          <t>A025_ZOYA</t>
-        </is>
-      </c>
-      <c r="B82" s="16" t="inlineStr">
+      <c r="A82" s="19" t="inlineStr">
+        <is>
+          <t>C001_ANJALI</t>
+        </is>
+      </c>
+      <c r="B82" s="19" t="inlineStr">
         <is>
           <t>A025</t>
         </is>
       </c>
-      <c r="C82" s="16" t="inlineStr">
+      <c r="C82" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D82" s="16" t="inlineStr">
+      <c r="D82" s="19" t="inlineStr">
         <is>
           <t>Beti Zoya</t>
         </is>
       </c>
-      <c r="E82" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian young woman about 22, jacket, camera. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E82" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="inlineStr">
-        <is>
-          <t>A025_SEN</t>
-        </is>
-      </c>
-      <c r="B83" s="16" t="inlineStr">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>G_V_MAN_SHERWANI_CUT</t>
+        </is>
+      </c>
+      <c r="B83" s="19" t="inlineStr">
         <is>
           <t>A025</t>
         </is>
       </c>
-      <c r="C83" s="16" t="inlineStr">
+      <c r="C83" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D83" s="16" t="inlineStr">
+      <c r="D83" s="19" t="inlineStr">
         <is>
           <t>Pakshi expert Dr. Sen (puraskar ki hod)</t>
         </is>
       </c>
-      <c r="E83" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Bengali man about 55, spectacles, bird book. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E83" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="inlineStr">
-        <is>
-          <t>A025_PAPPU</t>
-        </is>
-      </c>
-      <c r="B84" s="16" t="inlineStr">
+      <c r="A84" s="19" t="inlineStr">
+        <is>
+          <t>G_M_BLUE_JACKET_A_CUT</t>
+        </is>
+      </c>
+      <c r="B84" s="19" t="inlineStr">
         <is>
           <t>A025</t>
         </is>
       </c>
-      <c r="C84" s="16" t="inlineStr">
+      <c r="C84" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D84" s="16" t="inlineStr">
+      <c r="D84" s="19" t="inlineStr">
         <is>
           <t>Driver Pappu (gaadi ki chaabi)</t>
         </is>
       </c>
-      <c r="E84" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian driver about 35, uniform, keys. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E84" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="inlineStr">
-        <is>
-          <t>A025_SAHIL</t>
-        </is>
-      </c>
-      <c r="B85" s="16" t="inlineStr">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>C18-007_SAHIL</t>
+        </is>
+      </c>
+      <c r="B85" s="19" t="inlineStr">
         <is>
           <t>A025</t>
         </is>
       </c>
-      <c r="C85" s="16" t="inlineStr">
+      <c r="C85" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D85" s="16" t="inlineStr">
+      <c r="D85" s="19" t="inlineStr">
         <is>
           <t>Bhatija Sahil</t>
         </is>
       </c>
-      <c r="E85" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian young man about 24, t-shirt, cap. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E85" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="inlineStr">
-        <is>
-          <t>A025_RAZIYA</t>
-        </is>
-      </c>
-      <c r="B86" s="16" t="inlineStr">
+      <c r="A86" s="19" t="inlineStr">
+        <is>
+          <t>G_KAMLA</t>
+        </is>
+      </c>
+      <c r="B86" s="19" t="inlineStr">
         <is>
           <t>A025</t>
         </is>
       </c>
-      <c r="C86" s="16" t="inlineStr">
+      <c r="C86" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D86" s="16" t="inlineStr">
-        <is>
-          <t>Naukrani Raziya</t>
-        </is>
-      </c>
-      <c r="E86" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian housemaid about 40, salwar suit. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="D86" s="19" t="inlineStr">
+        <is>
+          <t>Naukrani Kamla</t>
+        </is>
+      </c>
+      <c r="E86" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -64454,29 +64469,29 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="18" t="inlineStr">
-        <is>
-          <t>P_A026_TEA</t>
-        </is>
-      </c>
-      <c r="B89" s="18" t="inlineStr">
+      <c r="A89" s="19" t="inlineStr">
+        <is>
+          <t>P_CHAI_TRAY</t>
+        </is>
+      </c>
+      <c r="B89" s="19" t="inlineStr">
         <is>
           <t>A026</t>
         </is>
       </c>
-      <c r="C89" s="18" t="inlineStr">
+      <c r="C89" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D89" s="18" t="inlineStr">
+      <c r="D89" s="19" t="inlineStr">
         <is>
           <t>Butter tea cups on a low wooden table</t>
         </is>
       </c>
-      <c r="E89" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Butter tea cups on a low wooden table. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E89" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -64535,29 +64550,29 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="18" t="inlineStr">
-        <is>
-          <t>P_A026_BOX</t>
-        </is>
-      </c>
-      <c r="B92" s="18" t="inlineStr">
+      <c r="A92" s="19" t="inlineStr">
+        <is>
+          <t>P_DONATION_BOX_CUT</t>
+        </is>
+      </c>
+      <c r="B92" s="19" t="inlineStr">
         <is>
           <t>A026</t>
         </is>
       </c>
-      <c r="C92" s="18" t="inlineStr">
+      <c r="C92" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D92" s="18" t="inlineStr">
+      <c r="D92" s="19" t="inlineStr">
         <is>
           <t>Open donation box, empty</t>
         </is>
       </c>
-      <c r="E92" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Open donation box, empty. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E92" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -64589,83 +64604,83 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="16" t="inlineStr">
-        <is>
-          <t>A026_ANSHUL</t>
-        </is>
-      </c>
-      <c r="B94" s="16" t="inlineStr">
+      <c r="A94" s="19" t="inlineStr">
+        <is>
+          <t>C006_RAJAT</t>
+        </is>
+      </c>
+      <c r="B94" s="19" t="inlineStr">
         <is>
           <t>A026</t>
         </is>
       </c>
-      <c r="C94" s="16" t="inlineStr">
+      <c r="C94" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D94" s="16" t="inlineStr">
+      <c r="D94" s="19" t="inlineStr">
         <is>
           <t>Trekker Anshul (paison par jhagda)</t>
         </is>
       </c>
-      <c r="E94" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian young man about 28, trekking jacket, backpack. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E94" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="16" t="inlineStr">
-        <is>
-          <t>A026_NEHA</t>
-        </is>
-      </c>
-      <c r="B95" s="16" t="inlineStr">
+      <c r="A95" s="19" t="inlineStr">
+        <is>
+          <t>C008_NEHA</t>
+        </is>
+      </c>
+      <c r="B95" s="19" t="inlineStr">
         <is>
           <t>A026</t>
         </is>
       </c>
-      <c r="C95" s="16" t="inlineStr">
+      <c r="C95" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D95" s="16" t="inlineStr">
+      <c r="D95" s="19" t="inlineStr">
         <is>
           <t>Blogger Neha</t>
         </is>
       </c>
-      <c r="E95" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 27, raincoat, vlog camera. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="16" t="inlineStr">
-        <is>
-          <t>A026_PARTH</t>
-        </is>
-      </c>
-      <c r="B96" s="16" t="inlineStr">
+      <c r="A96" s="19" t="inlineStr">
+        <is>
+          <t>G_M_CAMERA_CUT</t>
+        </is>
+      </c>
+      <c r="B96" s="19" t="inlineStr">
         <is>
           <t>A026</t>
         </is>
       </c>
-      <c r="C96" s="16" t="inlineStr">
+      <c r="C96" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D96" s="16" t="inlineStr">
+      <c r="D96" s="19" t="inlineStr">
         <is>
           <t>Photographer Parth</t>
         </is>
       </c>
-      <c r="E96" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Gujarati man about 35, camera, cap. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E96" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -64697,83 +64712,83 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="16" t="inlineStr">
-        <is>
-          <t>A026_KALE</t>
-        </is>
-      </c>
-      <c r="B98" s="16" t="inlineStr">
+      <c r="A98" s="19" t="inlineStr">
+        <is>
+          <t>G_M_OLD_GLASSES_CUT</t>
+        </is>
+      </c>
+      <c r="B98" s="19" t="inlineStr">
         <is>
           <t>A026</t>
         </is>
       </c>
-      <c r="C98" s="16" t="inlineStr">
+      <c r="C98" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D98" s="16" t="inlineStr">
+      <c r="D98" s="19" t="inlineStr">
         <is>
           <t>Professor Kale</t>
         </is>
       </c>
-      <c r="E98" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Marathi man about 55, spectacles, notebook. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E98" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="16" t="inlineStr">
-        <is>
-          <t>A026_RIYA</t>
-        </is>
-      </c>
-      <c r="B99" s="16" t="inlineStr">
+      <c r="A99" s="19" t="inlineStr">
+        <is>
+          <t>C002_RIYA_CUT</t>
+        </is>
+      </c>
+      <c r="B99" s="19" t="inlineStr">
         <is>
           <t>A026</t>
         </is>
       </c>
-      <c r="C99" s="16" t="inlineStr">
+      <c r="C99" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D99" s="16" t="inlineStr">
+      <c r="D99" s="19" t="inlineStr">
         <is>
           <t>Honeymoon wali Riya</t>
         </is>
       </c>
-      <c r="E99" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian young woman about 26, red bangles, woollen coat. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E99" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="16" t="inlineStr">
-        <is>
-          <t>A026_MEHTA</t>
-        </is>
-      </c>
-      <c r="B100" s="16" t="inlineStr">
+      <c r="A100" s="19" t="inlineStr">
+        <is>
+          <t>C16-001_DRMEHTA</t>
+        </is>
+      </c>
+      <c r="B100" s="19" t="inlineStr">
         <is>
           <t>A026</t>
         </is>
       </c>
-      <c r="C100" s="16" t="inlineStr">
+      <c r="C100" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D100" s="16" t="inlineStr">
+      <c r="D100" s="19" t="inlineStr">
         <is>
           <t>Itihaaskaar Dr. Mehta (purani moorti kharidna chahte the)</t>
         </is>
       </c>
-      <c r="E100" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 60, kurta, magnifying glass. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E100" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -64805,29 +64820,29 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="16" t="inlineStr">
-        <is>
-          <t>A026_VIKRAM</t>
-        </is>
-      </c>
-      <c r="B102" s="16" t="inlineStr">
+      <c r="A102" s="19" t="inlineStr">
+        <is>
+          <t>C007_VIKRAM</t>
+        </is>
+      </c>
+      <c r="B102" s="19" t="inlineStr">
         <is>
           <t>A026</t>
         </is>
       </c>
-      <c r="C102" s="16" t="inlineStr">
+      <c r="C102" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D102" s="16" t="inlineStr">
+      <c r="D102" s="19" t="inlineStr">
         <is>
           <t>Guide Vikram</t>
         </is>
       </c>
-      <c r="E102" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian guide about 35, mountain jacket, woollen cap, confident. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E102" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -64913,29 +64928,29 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="18" t="inlineStr">
-        <is>
-          <t>P_A027_REGISTER</t>
-        </is>
-      </c>
-      <c r="B106" s="18" t="inlineStr">
+      <c r="A106" s="19" t="inlineStr">
+        <is>
+          <t>P_VISITOR_REGISTER</t>
+        </is>
+      </c>
+      <c r="B106" s="19" t="inlineStr">
         <is>
           <t>A027</t>
         </is>
       </c>
-      <c r="C106" s="18" t="inlineStr">
+      <c r="C106" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D106" s="18" t="inlineStr">
+      <c r="D106" s="19" t="inlineStr">
         <is>
           <t>Visitor register with a torn page</t>
         </is>
       </c>
-      <c r="E106" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Visitor register with a torn page. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E106" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -64994,299 +65009,299 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="18" t="inlineStr">
-        <is>
-          <t>P_A027_CCTV</t>
-        </is>
-      </c>
-      <c r="B109" s="18" t="inlineStr">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t>P_CCTV_MONITOR</t>
+        </is>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
         <is>
           <t>A027</t>
         </is>
       </c>
-      <c r="C109" s="18" t="inlineStr">
+      <c r="C109" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D109" s="18" t="inlineStr">
+      <c r="D109" s="19" t="inlineStr">
         <is>
           <t>CCTV monitor showing static</t>
         </is>
       </c>
-      <c r="E109" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. CCTV monitor showing static. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E109" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="16" t="inlineStr">
-        <is>
-          <t>A027_POOJA</t>
-        </is>
-      </c>
-      <c r="B110" s="16" t="inlineStr">
+      <c r="A110" s="19" t="inlineStr">
+        <is>
+          <t>C002_POOJA</t>
+        </is>
+      </c>
+      <c r="B110" s="19" t="inlineStr">
         <is>
           <t>A027</t>
         </is>
       </c>
-      <c r="C110" s="16" t="inlineStr">
+      <c r="C110" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D110" s="16" t="inlineStr">
+      <c r="D110" s="19" t="inlineStr">
         <is>
           <t>Assistant curator Pooja (promotion ruka tha)</t>
         </is>
       </c>
-      <c r="E110" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 32, saree, ID card. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E110" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="16" t="inlineStr">
-        <is>
-          <t>A027_HARIHAR</t>
-        </is>
-      </c>
-      <c r="B111" s="16" t="inlineStr">
+      <c r="A111" s="19" t="inlineStr">
+        <is>
+          <t>G_M_GUARD_CUT</t>
+        </is>
+      </c>
+      <c r="B111" s="19" t="inlineStr">
         <is>
           <t>A027</t>
         </is>
       </c>
-      <c r="C111" s="16" t="inlineStr">
+      <c r="C111" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D111" s="16" t="inlineStr">
+      <c r="D111" s="19" t="inlineStr">
         <is>
           <t>Guard Harihar (chaabiyan iske paas)</t>
         </is>
       </c>
-      <c r="E111" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Odia security guard about 50, uniform, key bunch. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E111" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="16" t="inlineStr">
-        <is>
-          <t>A027_FAIZAN</t>
-        </is>
-      </c>
-      <c r="B112" s="16" t="inlineStr">
+      <c r="A112" s="19" t="inlineStr">
+        <is>
+          <t>C18-003_PRATEEK</t>
+        </is>
+      </c>
+      <c r="B112" s="19" t="inlineStr">
         <is>
           <t>A027</t>
         </is>
       </c>
-      <c r="C112" s="16" t="inlineStr">
+      <c r="C112" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D112" s="16" t="inlineStr">
+      <c r="D112" s="19" t="inlineStr">
         <is>
           <t>Research student Faizan</t>
         </is>
       </c>
-      <c r="E112" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian young man about 25, kurta, notebook. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E112" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="16" t="inlineStr">
-        <is>
-          <t>A027_MALHOTRA</t>
-        </is>
-      </c>
-      <c r="B113" s="16" t="inlineStr">
+      <c r="A113" s="19" t="inlineStr">
+        <is>
+          <t>C17-001_SETH</t>
+        </is>
+      </c>
+      <c r="B113" s="19" t="inlineStr">
         <is>
           <t>A027</t>
         </is>
       </c>
-      <c r="C113" s="16" t="inlineStr">
+      <c r="C113" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D113" s="16" t="inlineStr">
+      <c r="D113" s="19" t="inlineStr">
         <is>
           <t>Antique dealer Malhotra</t>
         </is>
       </c>
-      <c r="E113" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 55, blazer, cane, polite smile. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E113" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="16" t="inlineStr">
-        <is>
-          <t>A027_SUJATA</t>
-        </is>
-      </c>
-      <c r="B114" s="16" t="inlineStr">
+      <c r="A114" s="19" t="inlineStr">
+        <is>
+          <t>G_V_WOMAN_SAREE_CUT</t>
+        </is>
+      </c>
+      <c r="B114" s="19" t="inlineStr">
         <is>
           <t>A027</t>
         </is>
       </c>
-      <c r="C114" s="16" t="inlineStr">
+      <c r="C114" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D114" s="16" t="inlineStr">
+      <c r="D114" s="19" t="inlineStr">
         <is>
           <t>Patni Sujata (vasiyat inke naam)</t>
         </is>
       </c>
-      <c r="E114" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Odia woman about 55, silk saree. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E114" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="16" t="inlineStr">
-        <is>
-          <t>A027_PRAKASH</t>
-        </is>
-      </c>
-      <c r="B115" s="16" t="inlineStr">
+      <c r="A115" s="19" t="inlineStr">
+        <is>
+          <t>G_V_MAN_CHECK_CUT</t>
+        </is>
+      </c>
+      <c r="B115" s="19" t="inlineStr">
         <is>
           <t>A027</t>
         </is>
       </c>
-      <c r="C115" s="16" t="inlineStr">
+      <c r="C115" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D115" s="16" t="inlineStr">
+      <c r="D115" s="19" t="inlineStr">
         <is>
           <t>Guide Prakash</t>
         </is>
       </c>
-      <c r="E115" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian tour guide about 40, cap, flag stick. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E115" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="16" t="inlineStr">
-        <is>
-          <t>A027_ANITA</t>
-        </is>
-      </c>
-      <c r="B116" s="16" t="inlineStr">
+      <c r="A116" s="19" t="inlineStr">
+        <is>
+          <t>C007_KAVYA</t>
+        </is>
+      </c>
+      <c r="B116" s="19" t="inlineStr">
         <is>
           <t>A027</t>
         </is>
       </c>
-      <c r="C116" s="16" t="inlineStr">
+      <c r="C116" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D116" s="16" t="inlineStr">
+      <c r="D116" s="19" t="inlineStr">
         <is>
           <t>Photographer Anita (tasveerein chori ka shak)</t>
         </is>
       </c>
-      <c r="E116" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 35, camera, jacket. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E116" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="16" t="inlineStr">
-        <is>
-          <t>A027_RAGHUNATH</t>
-        </is>
-      </c>
-      <c r="B117" s="16" t="inlineStr">
+      <c r="A117" s="19" t="inlineStr">
+        <is>
+          <t>G_V_MAN_GREY_CUT</t>
+        </is>
+      </c>
+      <c r="B117" s="19" t="inlineStr">
         <is>
           <t>A027</t>
         </is>
       </c>
-      <c r="C117" s="16" t="inlineStr">
+      <c r="C117" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D117" s="16" t="inlineStr">
+      <c r="D117" s="19" t="inlineStr">
         <is>
           <t>Driver Raghunath</t>
         </is>
       </c>
-      <c r="E117" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian driver about 40, uniform. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E117" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="16" t="inlineStr">
-        <is>
-          <t>A027_ABHIJIT</t>
-        </is>
-      </c>
-      <c r="B118" s="16" t="inlineStr">
+      <c r="A118" s="19" t="inlineStr">
+        <is>
+          <t>C002_KUNAL</t>
+        </is>
+      </c>
+      <c r="B118" s="19" t="inlineStr">
         <is>
           <t>A027</t>
         </is>
       </c>
-      <c r="C118" s="16" t="inlineStr">
+      <c r="C118" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D118" s="16" t="inlineStr">
+      <c r="D118" s="19" t="inlineStr">
         <is>
           <t>Beta Abhijit (paison ki tangi)</t>
         </is>
       </c>
-      <c r="E118" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 30, jeans, jacket. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E118" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="16" t="inlineStr">
-        <is>
-          <t>A027_GOPI</t>
-        </is>
-      </c>
-      <c r="B119" s="16" t="inlineStr">
+      <c r="A119" s="19" t="inlineStr">
+        <is>
+          <t>G_RAMU</t>
+        </is>
+      </c>
+      <c r="B119" s="19" t="inlineStr">
         <is>
           <t>A027</t>
         </is>
       </c>
-      <c r="C119" s="16" t="inlineStr">
+      <c r="C119" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D119" s="16" t="inlineStr">
-        <is>
-          <t>Safaiwala Gopi</t>
-        </is>
-      </c>
-      <c r="E119" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian cleaner about 45, uniform, broom. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="D119" s="19" t="inlineStr">
+        <is>
+          <t>Safaiwala Ramu</t>
+        </is>
+      </c>
+      <c r="E119" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -65399,29 +65414,29 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="18" t="inlineStr">
-        <is>
-          <t>P_A028_STETHO</t>
-        </is>
-      </c>
-      <c r="B124" s="18" t="inlineStr">
+      <c r="A124" s="19" t="inlineStr">
+        <is>
+          <t>P_STETHOSCOPE</t>
+        </is>
+      </c>
+      <c r="B124" s="19" t="inlineStr">
         <is>
           <t>A028</t>
         </is>
       </c>
-      <c r="C124" s="18" t="inlineStr">
+      <c r="C124" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D124" s="18" t="inlineStr">
+      <c r="D124" s="19" t="inlineStr">
         <is>
           <t>Stethoscope lying on the floor</t>
         </is>
       </c>
-      <c r="E124" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Stethoscope lying on the floor. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E124" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -65480,56 +65495,56 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="16" t="inlineStr">
-        <is>
-          <t>A028_JASSI</t>
-        </is>
-      </c>
-      <c r="B127" s="16" t="inlineStr">
+      <c r="A127" s="19" t="inlineStr">
+        <is>
+          <t>C005_VICKY</t>
+        </is>
+      </c>
+      <c r="B127" s="19" t="inlineStr">
         <is>
           <t>A028</t>
         </is>
       </c>
-      <c r="C127" s="16" t="inlineStr">
+      <c r="C127" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D127" s="16" t="inlineStr">
+      <c r="D127" s="19" t="inlineStr">
         <is>
           <t>Gym trainer Jassi (paise udhaar liye the)</t>
         </is>
       </c>
-      <c r="E127" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Punjabi young man about 28, gym wear, towel. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E127" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="16" t="inlineStr">
-        <is>
-          <t>A028_BAJWA</t>
-        </is>
-      </c>
-      <c r="B128" s="16" t="inlineStr">
+      <c r="A128" s="19" t="inlineStr">
+        <is>
+          <t>C16-001_DRMEHTA</t>
+        </is>
+      </c>
+      <c r="B128" s="19" t="inlineStr">
         <is>
           <t>A028</t>
         </is>
       </c>
-      <c r="C128" s="16" t="inlineStr">
+      <c r="C128" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D128" s="16" t="inlineStr">
+      <c r="D128" s="19" t="inlineStr">
         <is>
           <t>Ortho doctor Bajwa (partnership ka jhagda)</t>
         </is>
       </c>
-      <c r="E128" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Punjabi doctor about 50, white coat, X-ray film. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E128" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -65669,29 +65684,29 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="16" t="inlineStr">
-        <is>
-          <t>A028_ANU</t>
-        </is>
-      </c>
-      <c r="B134" s="16" t="inlineStr">
+      <c r="A134" s="19" t="inlineStr">
+        <is>
+          <t>C001_ANJALI</t>
+        </is>
+      </c>
+      <c r="B134" s="19" t="inlineStr">
         <is>
           <t>A028</t>
         </is>
       </c>
-      <c r="C134" s="16" t="inlineStr">
+      <c r="C134" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D134" s="16" t="inlineStr">
+      <c r="D134" s="19" t="inlineStr">
         <is>
           <t>Yoga teacher Anu</t>
         </is>
       </c>
-      <c r="E134" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 35, yoga wear. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E134" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -65723,29 +65738,29 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="16" t="inlineStr">
-        <is>
-          <t>A029_V_GUPTA</t>
-        </is>
-      </c>
-      <c r="B136" s="16" t="inlineStr">
+      <c r="A136" s="19" t="inlineStr">
+        <is>
+          <t>C04-008_GUPTA_SLUMPED</t>
+        </is>
+      </c>
+      <c r="B136" s="19" t="inlineStr">
         <is>
           <t>A029</t>
         </is>
       </c>
-      <c r="C136" s="16" t="inlineStr">
+      <c r="C136" s="19" t="inlineStr">
         <is>
           <t>Victim</t>
         </is>
       </c>
-      <c r="D136" s="16" t="inlineStr">
+      <c r="D136" s="19" t="inlineStr">
         <is>
           <t>Indian merchant Seth Ramniwas Gupta, about 65, dhoti kurta, slumped at a ledger desk, eyes closed</t>
         </is>
       </c>
-      <c r="E136" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian merchant Seth Ramniwas Gupta, about 65, dhoti kurta, slumped at a ledger desk, eyes closed. Peaceful pose, YouTube-safe: no blood, no wounds. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E136" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -65777,29 +65792,29 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="18" t="inlineStr">
-        <is>
-          <t>P_A029_SAFE</t>
-        </is>
-      </c>
-      <c r="B138" s="18" t="inlineStr">
+      <c r="A138" s="19" t="inlineStr">
+        <is>
+          <t>P_TIJORI</t>
+        </is>
+      </c>
+      <c r="B138" s="19" t="inlineStr">
         <is>
           <t>A029</t>
         </is>
       </c>
-      <c r="C138" s="18" t="inlineStr">
+      <c r="C138" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D138" s="18" t="inlineStr">
+      <c r="D138" s="19" t="inlineStr">
         <is>
           <t>Open iron safe with scattered cash bundles</t>
         </is>
       </c>
-      <c r="E138" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Open iron safe with scattered cash bundles. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E138" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -65831,299 +65846,299 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="18" t="inlineStr">
-        <is>
-          <t>P_A029_GLASS</t>
-        </is>
-      </c>
-      <c r="B140" s="18" t="inlineStr">
+      <c r="A140" s="19" t="inlineStr">
+        <is>
+          <t>P_THAALI_LASSI</t>
+        </is>
+      </c>
+      <c r="B140" s="19" t="inlineStr">
         <is>
           <t>A029</t>
         </is>
       </c>
-      <c r="C140" s="18" t="inlineStr">
+      <c r="C140" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D140" s="18" t="inlineStr">
+      <c r="D140" s="19" t="inlineStr">
         <is>
           <t>Glass of lassi, half drunk</t>
         </is>
       </c>
-      <c r="E140" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Glass of lassi, half drunk. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E140" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="18" t="inlineStr">
-        <is>
-          <t>P_A029_CHASHMA</t>
-        </is>
-      </c>
-      <c r="B141" s="18" t="inlineStr">
+      <c r="A141" s="19" t="inlineStr">
+        <is>
+          <t>P_BROKEN_GLASSES_CUT</t>
+        </is>
+      </c>
+      <c r="B141" s="19" t="inlineStr">
         <is>
           <t>A029</t>
         </is>
       </c>
-      <c r="C141" s="18" t="inlineStr">
+      <c r="C141" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D141" s="18" t="inlineStr">
+      <c r="D141" s="19" t="inlineStr">
         <is>
           <t>Broken spectacles on the gaddi</t>
         </is>
       </c>
-      <c r="E141" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Broken spectacles on the gaddi. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E141" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="16" t="inlineStr">
-        <is>
-          <t>A029_RAMDAYAL</t>
-        </is>
-      </c>
-      <c r="B142" s="16" t="inlineStr">
+      <c r="A142" s="19" t="inlineStr">
+        <is>
+          <t>C006_GUPTA</t>
+        </is>
+      </c>
+      <c r="B142" s="19" t="inlineStr">
         <is>
           <t>A029</t>
         </is>
       </c>
-      <c r="C142" s="16" t="inlineStr">
+      <c r="C142" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D142" s="16" t="inlineStr">
+      <c r="D142" s="19" t="inlineStr">
         <is>
           <t>Munim Ramdayal</t>
         </is>
       </c>
-      <c r="E142" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian munim about 55, dhoti, spectacles, cash bag, calm face. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E142" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="16" t="inlineStr">
-        <is>
-          <t>A029_ASHOK</t>
-        </is>
-      </c>
-      <c r="B143" s="16" t="inlineStr">
+      <c r="A143" s="19" t="inlineStr">
+        <is>
+          <t>C004_AMIT</t>
+        </is>
+      </c>
+      <c r="B143" s="19" t="inlineStr">
         <is>
           <t>A029</t>
         </is>
       </c>
-      <c r="C143" s="16" t="inlineStr">
+      <c r="C143" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D143" s="16" t="inlineStr">
+      <c r="D143" s="19" t="inlineStr">
         <is>
           <t>Beta Ashok (gaddi ka jhagda)</t>
         </is>
       </c>
-      <c r="E143" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 35, kurta, angry. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E143" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="16" t="inlineStr">
-        <is>
-          <t>A029_KAMINI</t>
-        </is>
-      </c>
-      <c r="B144" s="16" t="inlineStr">
+      <c r="A144" s="19" t="inlineStr">
+        <is>
+          <t>C004_SNEHA</t>
+        </is>
+      </c>
+      <c r="B144" s="19" t="inlineStr">
         <is>
           <t>A029</t>
         </is>
       </c>
-      <c r="C144" s="16" t="inlineStr">
+      <c r="C144" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D144" s="16" t="inlineStr">
+      <c r="D144" s="19" t="inlineStr">
         <is>
           <t>Bahu Kamini</t>
         </is>
       </c>
-      <c r="E144" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 32, saree. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E144" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="16" t="inlineStr">
-        <is>
-          <t>A029_RAJU</t>
-        </is>
-      </c>
-      <c r="B145" s="16" t="inlineStr">
+      <c r="A145" s="19" t="inlineStr">
+        <is>
+          <t>C003_BHATIJA</t>
+        </is>
+      </c>
+      <c r="B145" s="19" t="inlineStr">
         <is>
           <t>A029</t>
         </is>
       </c>
-      <c r="C145" s="16" t="inlineStr">
+      <c r="C145" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D145" s="16" t="inlineStr">
+      <c r="D145" s="19" t="inlineStr">
         <is>
           <t>Bhatija Raju (udhaar nahi lautaya)</t>
         </is>
       </c>
-      <c r="E145" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian young man about 26, t-shirt. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E145" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="16" t="inlineStr">
-        <is>
-          <t>A029_SHERU</t>
-        </is>
-      </c>
-      <c r="B146" s="16" t="inlineStr">
+      <c r="A146" s="19" t="inlineStr">
+        <is>
+          <t>G_V_MAN_BLUE_CUT</t>
+        </is>
+      </c>
+      <c r="B146" s="19" t="inlineStr">
         <is>
           <t>A029</t>
         </is>
       </c>
-      <c r="C146" s="16" t="inlineStr">
+      <c r="C146" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D146" s="16" t="inlineStr">
+      <c r="D146" s="19" t="inlineStr">
         <is>
           <t>Driver Sheru (tijori ke paas iske joote)</t>
         </is>
       </c>
-      <c r="E146" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian driver about 35, uniform. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E146" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="16" t="inlineStr">
-        <is>
-          <t>A029_GOMTI</t>
-        </is>
-      </c>
-      <c r="B147" s="16" t="inlineStr">
+      <c r="A147" s="19" t="inlineStr">
+        <is>
+          <t>C004_MAA</t>
+        </is>
+      </c>
+      <c r="B147" s="19" t="inlineStr">
         <is>
           <t>A029</t>
         </is>
       </c>
-      <c r="C147" s="16" t="inlineStr">
+      <c r="C147" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D147" s="16" t="inlineStr">
+      <c r="D147" s="19" t="inlineStr">
         <is>
           <t>Patni Gomti</t>
         </is>
       </c>
-      <c r="E147" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 60, saree. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E147" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="16" t="inlineStr">
-        <is>
-          <t>A029_PATEL</t>
-        </is>
-      </c>
-      <c r="B148" s="16" t="inlineStr">
+      <c r="A148" s="19" t="inlineStr">
+        <is>
+          <t>C08-004_MR_RATHI</t>
+        </is>
+      </c>
+      <c r="B148" s="19" t="inlineStr">
         <is>
           <t>A029</t>
         </is>
       </c>
-      <c r="C148" s="16" t="inlineStr">
+      <c r="C148" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D148" s="16" t="inlineStr">
+      <c r="D148" s="19" t="inlineStr">
         <is>
           <t>Vyapari Patel (sauda toota tha)</t>
         </is>
       </c>
-      <c r="E148" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Gujarati trader about 55, kurta, cap. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E148" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="16" t="inlineStr">
-        <is>
-          <t>A029_CHHEDI</t>
-        </is>
-      </c>
-      <c r="B149" s="16" t="inlineStr">
+      <c r="A149" s="19" t="inlineStr">
+        <is>
+          <t>G_BHOLA</t>
+        </is>
+      </c>
+      <c r="B149" s="19" t="inlineStr">
         <is>
           <t>A029</t>
         </is>
       </c>
-      <c r="C149" s="16" t="inlineStr">
+      <c r="C149" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D149" s="16" t="inlineStr">
-        <is>
-          <t>Naukar Chhedi</t>
-        </is>
-      </c>
-      <c r="E149" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian servant about 40, vest. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="D149" s="19" t="inlineStr">
+        <is>
+          <t>Naukar Bhola</t>
+        </is>
+      </c>
+      <c r="E149" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="16" t="inlineStr">
-        <is>
-          <t>A029_ANWAR</t>
-        </is>
-      </c>
-      <c r="B150" s="16" t="inlineStr">
+      <c r="A150" s="19" t="inlineStr">
+        <is>
+          <t>C010_MAHESH</t>
+        </is>
+      </c>
+      <c r="B150" s="19" t="inlineStr">
         <is>
           <t>A029</t>
         </is>
       </c>
-      <c r="C150" s="16" t="inlineStr">
+      <c r="C150" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D150" s="16" t="inlineStr">
+      <c r="D150" s="19" t="inlineStr">
         <is>
           <t>Kirayedaar Anwar</t>
         </is>
       </c>
-      <c r="E150" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 40, kurta, travel bag. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E150" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -66263,29 +66278,29 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="18" t="inlineStr">
-        <is>
-          <t>P_A030_FLASK</t>
-        </is>
-      </c>
-      <c r="B156" s="18" t="inlineStr">
+      <c r="A156" s="19" t="inlineStr">
+        <is>
+          <t>P_STEEL_THERMOS</t>
+        </is>
+      </c>
+      <c r="B156" s="19" t="inlineStr">
         <is>
           <t>A030</t>
         </is>
       </c>
-      <c r="C156" s="18" t="inlineStr">
+      <c r="C156" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D156" s="18" t="inlineStr">
+      <c r="D156" s="19" t="inlineStr">
         <is>
           <t>Coffee flask knocked over</t>
         </is>
       </c>
-      <c r="E156" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Coffee flask knocked over. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E156" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -66317,272 +66332,272 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="16" t="inlineStr">
-        <is>
-          <t>A030_TANMAY</t>
-        </is>
-      </c>
-      <c r="B158" s="16" t="inlineStr">
+      <c r="A158" s="19" t="inlineStr">
+        <is>
+          <t>G_M_GREY_HOODIE_CUT</t>
+        </is>
+      </c>
+      <c r="B158" s="19" t="inlineStr">
         <is>
           <t>A030</t>
         </is>
       </c>
-      <c r="C158" s="16" t="inlineStr">
+      <c r="C158" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D158" s="16" t="inlineStr">
+      <c r="D158" s="19" t="inlineStr">
         <is>
           <t>Assistant Tanmay (research chori ka shak)</t>
         </is>
       </c>
-      <c r="E158" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian young man about 26, hoodie, star chart. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E158" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="16" t="inlineStr">
-        <is>
-          <t>A030_GARGI</t>
-        </is>
-      </c>
-      <c r="B159" s="16" t="inlineStr">
+      <c r="A159" s="19" t="inlineStr">
+        <is>
+          <t>C005_NEHA</t>
+        </is>
+      </c>
+      <c r="B159" s="19" t="inlineStr">
         <is>
           <t>A030</t>
         </is>
       </c>
-      <c r="C159" s="16" t="inlineStr">
+      <c r="C159" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D159" s="16" t="inlineStr">
+      <c r="D159" s="19" t="inlineStr">
         <is>
           <t>Beti Gargi</t>
         </is>
       </c>
-      <c r="E159" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian young woman about 24, jacket, small telescope. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E159" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="16" t="inlineStr">
-        <is>
-          <t>A030_BISHT</t>
-        </is>
-      </c>
-      <c r="B160" s="16" t="inlineStr">
+      <c r="A160" s="19" t="inlineStr">
+        <is>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
+        </is>
+      </c>
+      <c r="B160" s="19" t="inlineStr">
         <is>
           <t>A030</t>
         </is>
       </c>
-      <c r="C160" s="16" t="inlineStr">
+      <c r="C160" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D160" s="16" t="inlineStr">
+      <c r="D160" s="19" t="inlineStr">
         <is>
           <t>School teacher Bisht</t>
         </is>
       </c>
-      <c r="E160" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Pahadi teacher about 45, sweater, chalk. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E160" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="16" t="inlineStr">
-        <is>
-          <t>A030_SURABHI</t>
-        </is>
-      </c>
-      <c r="B161" s="16" t="inlineStr">
+      <c r="A161" s="19" t="inlineStr">
+        <is>
+          <t>C007_KAVYA</t>
+        </is>
+      </c>
+      <c r="B161" s="19" t="inlineStr">
         <is>
           <t>A030</t>
         </is>
       </c>
-      <c r="C161" s="16" t="inlineStr">
+      <c r="C161" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D161" s="16" t="inlineStr">
+      <c r="D161" s="19" t="inlineStr">
         <is>
           <t>Engineer Surabhi (project se nikaali gayi)</t>
         </is>
       </c>
-      <c r="E161" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 30, ISRO-style jacket (no logo), laptop. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E161" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="16" t="inlineStr">
-        <is>
-          <t>A030_POORAN</t>
-        </is>
-      </c>
-      <c r="B162" s="16" t="inlineStr">
+      <c r="A162" s="19" t="inlineStr">
+        <is>
+          <t>G_HARIYA</t>
+        </is>
+      </c>
+      <c r="B162" s="19" t="inlineStr">
         <is>
           <t>A030</t>
         </is>
       </c>
-      <c r="C162" s="16" t="inlineStr">
+      <c r="C162" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D162" s="16" t="inlineStr">
-        <is>
-          <t>Guide Pooran (doorbeen bechne ka shak)</t>
-        </is>
-      </c>
-      <c r="E162" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Pahadi guide about 40, woollen cap, torch. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="D162" s="19" t="inlineStr">
+        <is>
+          <t>Guide Hariya (doorbeen bechne ka shak)</t>
+        </is>
+      </c>
+      <c r="E162" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="16" t="inlineStr">
-        <is>
-          <t>A030_HEMLATA</t>
-        </is>
-      </c>
-      <c r="B163" s="16" t="inlineStr">
+      <c r="A163" s="19" t="inlineStr">
+        <is>
+          <t>G_W_MAROON_SAREE_CUT</t>
+        </is>
+      </c>
+      <c r="B163" s="19" t="inlineStr">
         <is>
           <t>A030</t>
         </is>
       </c>
-      <c r="C163" s="16" t="inlineStr">
+      <c r="C163" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D163" s="16" t="inlineStr">
+      <c r="D163" s="19" t="inlineStr">
         <is>
           <t>Patni Hemlata (beema inke naam)</t>
         </is>
       </c>
-      <c r="E163" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 58, shawl over saree. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E163" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="16" t="inlineStr">
-        <is>
-          <t>A030_HRITHIK</t>
-        </is>
-      </c>
-      <c r="B164" s="16" t="inlineStr">
+      <c r="A164" s="19" t="inlineStr">
+        <is>
+          <t>G_M_CAMERA_CUT</t>
+        </is>
+      </c>
+      <c r="B164" s="19" t="inlineStr">
         <is>
           <t>A030</t>
         </is>
       </c>
-      <c r="C164" s="16" t="inlineStr">
+      <c r="C164" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D164" s="16" t="inlineStr">
+      <c r="D164" s="19" t="inlineStr">
         <is>
           <t>Photographer Hrithik</t>
         </is>
       </c>
-      <c r="E164" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian young man about 28, camera with long lens. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E164" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="16" t="inlineStr">
-        <is>
-          <t>A030_NAVEEN</t>
-        </is>
-      </c>
-      <c r="B165" s="16" t="inlineStr">
+      <c r="A165" s="19" t="inlineStr">
+        <is>
+          <t>C10-004_DEEPAK</t>
+        </is>
+      </c>
+      <c r="B165" s="19" t="inlineStr">
         <is>
           <t>A030</t>
         </is>
       </c>
-      <c r="C165" s="16" t="inlineStr">
+      <c r="C165" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D165" s="16" t="inlineStr">
+      <c r="D165" s="19" t="inlineStr">
         <is>
           <t>Bhatija Naveen (udhaar nahi lautaya)</t>
         </is>
       </c>
-      <c r="E165" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian man about 30, spectacles, book. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E165" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="16" t="inlineStr">
-        <is>
-          <t>A030_HARI</t>
-        </is>
-      </c>
-      <c r="B166" s="16" t="inlineStr">
+      <c r="A166" s="19" t="inlineStr">
+        <is>
+          <t>G_BAHADUR</t>
+        </is>
+      </c>
+      <c r="B166" s="19" t="inlineStr">
         <is>
           <t>A030</t>
         </is>
       </c>
-      <c r="C166" s="16" t="inlineStr">
+      <c r="C166" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D166" s="16" t="inlineStr">
-        <is>
-          <t>Chowkidar Hari</t>
-        </is>
-      </c>
-      <c r="E166" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Pahadi watchman about 55, khaki uniform, lathi. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="D166" s="19" t="inlineStr">
+        <is>
+          <t>Chowkidar Bahadur</t>
+        </is>
+      </c>
+      <c r="E166" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="16" t="inlineStr">
-        <is>
-          <t>A030_KUNDAN</t>
-        </is>
-      </c>
-      <c r="B167" s="16" t="inlineStr">
+      <c r="A167" s="19" t="inlineStr">
+        <is>
+          <t>G_V_MAN_CHECK_CUT</t>
+        </is>
+      </c>
+      <c r="B167" s="19" t="inlineStr">
         <is>
           <t>A030</t>
         </is>
       </c>
-      <c r="C167" s="16" t="inlineStr">
+      <c r="C167" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D167" s="16" t="inlineStr">
+      <c r="D167" s="19" t="inlineStr">
         <is>
           <t>Padosi Kundan</t>
         </is>
       </c>
-      <c r="E167" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Pahadi man about 50, shawl, calm dreamy face. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E167" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>

--- a/youtube stories/batch 3/Batch 3 - Production Sheet.xlsx
+++ b/youtube stories/batch 3/Batch 3 - Production Sheet.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Image Prompts sheet: HARA = purani image (nayi mat banao) – 72 alag images reuse. Baaki 68 nayi banani hain (BG_ wale long video 16:9 ke liye).</t>
+          <t>Image Prompts sheet: HARA = purani image (nayi mat banao) – 96 alag images reuse. Baaki 53 nayi banani hain (BG_ wale long video 16:9 ke liye).</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       <c r="I11" s="16" t="inlineStr"/>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>A021_V_KAMLESH</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="K11" s="16" t="inlineStr"/>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>A021_V_KAMLESH</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="K12" s="16" t="inlineStr"/>
@@ -3567,7 +3567,7 @@
       <c r="I14" s="16" t="inlineStr"/>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>P_KAANCH_TUKDE_CUT</t>
+          <t>P_KAANCH_TUKDE</t>
         </is>
       </c>
       <c r="K14" s="16" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>G_W_MAROON_SAREE_CUT</t>
+          <t>C004_MAA</t>
         </is>
       </c>
       <c r="K23" s="16" t="inlineStr"/>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>G_M_CAMERA_CUT</t>
+          <t>G_M_YELLOW_KURTA_CUT</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr"/>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_GREY_CUT</t>
+          <t>C005_VICKY_KEY_CUT</t>
         </is>
       </c>
       <c r="K25" s="16" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>C08-004_MR_RATHI</t>
+          <t>G_TTE</t>
         </is>
       </c>
       <c r="K26" s="16" t="inlineStr"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="K27" s="16" t="inlineStr"/>
@@ -4877,7 +4877,7 @@
       <c r="I34" s="16" t="inlineStr"/>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>A022_V_RAO</t>
+          <t>C002_ARYAN</t>
         </is>
       </c>
       <c r="K34" s="16" t="inlineStr"/>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>A022_V_RAO</t>
+          <t>C002_ARYAN</t>
         </is>
       </c>
       <c r="K35" s="16" t="inlineStr"/>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>C08-007_KAPOOR</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="K43" s="16" t="inlineStr"/>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>G_W_PINK_SUIT_CUT</t>
         </is>
       </c>
       <c r="K44" s="16" t="inlineStr"/>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="J45" s="17" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C007_VIKRAM</t>
         </is>
       </c>
       <c r="K45" s="17" t="inlineStr"/>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>G_M_APRON_CUT</t>
+          <t>C017_CHEF</t>
         </is>
       </c>
       <c r="K46" s="16" t="inlineStr"/>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>G_V_WOMAN_SAREE_CUT</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="K47" s="16" t="inlineStr"/>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>A022_JOHNNY</t>
+          <t>C015_MARCO</t>
         </is>
       </c>
       <c r="K48" s="16" t="inlineStr"/>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>C04-010_ARJUN</t>
+          <t>G_M_LIGHTMAN_CUT</t>
         </is>
       </c>
       <c r="K49" s="16" t="inlineStr"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>C005_NEHA</t>
+          <t>C018_SISTER</t>
         </is>
       </c>
       <c r="K51" s="16" t="inlineStr"/>
@@ -6045,7 +6045,7 @@
       <c r="I52" s="16" t="inlineStr"/>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>A022_JOHNNY</t>
+          <t>C015_MARCO</t>
         </is>
       </c>
       <c r="K52" s="16" t="inlineStr">
@@ -6436,7 +6436,7 @@
       <c r="I58" s="16" t="inlineStr"/>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>A023_V_DESHMUKH</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="K58" s="16" t="inlineStr"/>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>A023_V_DESHMUKH</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="K59" s="16" t="inlineStr"/>
@@ -6863,7 +6863,7 @@
       <c r="I65" s="16" t="inlineStr"/>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>P_A023_BOTTLE</t>
+          <t>P_BOTTLE_CUT</t>
         </is>
       </c>
       <c r="K65" s="16" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>A023_BALA</t>
+          <t>C18-003_PRATEEK</t>
         </is>
       </c>
       <c r="K68" s="16" t="inlineStr"/>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>C020_NOAH</t>
         </is>
       </c>
       <c r="K71" s="16" t="inlineStr"/>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>A023_ROY</t>
+          <t>G_CIVIL_RED_CUT</t>
         </is>
       </c>
       <c r="K72" s="16" t="inlineStr"/>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="G73" s="16" t="inlineStr">
         <is>
-          <t>क्रिकेटर सोहम। प्रेसिडेंट ने टीम से निकाला। बोले... मैं टी-ट्वेंटी मैच खेल रहा था। हर टीम को बीस ओवर।</t>
+          <t>क्रिकेटर मनोज। प्रेसिडेंट ने टीम से निकाला। बोले... मैं टी-ट्वेंटी मैच खेल रहा था। हर टीम को बीस ओवर।</t>
         </is>
       </c>
       <c r="H73" s="16" t="inlineStr">
@@ -7399,13 +7399,13 @@
       <c r="I73" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 7/10
-Cricketer Soham
+Cricketer Manoj
 (team se nikala)</t>
         </is>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>G_CR_VIKRAM_CUT</t>
+          <t>G_CR_MANOJ_CUT</t>
         </is>
       </c>
       <c r="K73" s="16" t="inlineStr"/>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="J74" s="17" t="inlineStr">
         <is>
-          <t>A023_AJINKYA</t>
+          <t>G_CIVIL_GREEN_CUT</t>
         </is>
       </c>
       <c r="K74" s="17" t="inlineStr"/>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>G_W_PINK_SUIT_CUT</t>
+          <t>A023_KAPOOR</t>
         </is>
       </c>
       <c r="K75" s="16" t="inlineStr"/>
@@ -7607,7 +7607,7 @@
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>C008_NEHA</t>
+          <t>A023_SAINA</t>
         </is>
       </c>
       <c r="K76" s="16" t="inlineStr"/>
@@ -8059,7 +8059,7 @@
       <c r="I83" s="16" t="inlineStr"/>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>A024_V_PANDEY</t>
+          <t>C04-008_GUPTA_SLUMPED</t>
         </is>
       </c>
       <c r="K83" s="16" t="inlineStr"/>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
-          <t>A024_V_PANDEY</t>
+          <t>C04-008_GUPTA_SLUMPED</t>
         </is>
       </c>
       <c r="K84" s="16" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
-          <t>C010_SUNITA</t>
+          <t>G_W_MAROON_SAREE_CUT</t>
         </is>
       </c>
       <c r="K92" s="16" t="inlineStr"/>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="J94" s="16" t="inlineStr">
         <is>
-          <t>C004_BEHEN</t>
+          <t>C002_RIYA_CUT</t>
         </is>
       </c>
       <c r="K94" s="16" t="inlineStr"/>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>C004_PADOSI</t>
+          <t>C12-010_MAHESH</t>
         </is>
       </c>
       <c r="K95" s="16" t="inlineStr"/>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="J96" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>C003_SURAJ_CUT</t>
         </is>
       </c>
       <c r="K96" s="16" t="inlineStr"/>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="J97" s="17" t="inlineStr">
         <is>
-          <t>G_M_YELLOW_KURTA_CUT</t>
+          <t>C001_ROHIT</t>
         </is>
       </c>
       <c r="K97" s="17" t="inlineStr"/>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>G_M_LIGHTMAN_CUT</t>
+          <t>G_M_BLUE_SHIRT_CUT</t>
         </is>
       </c>
       <c r="K99" s="16" t="inlineStr"/>
@@ -9551,7 +9551,7 @@
       <c r="I106" s="16" t="inlineStr"/>
       <c r="J106" s="16" t="inlineStr">
         <is>
-          <t>A025_V_KHAN</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="K106" s="16" t="inlineStr"/>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>A025_V_KHAN</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="K107" s="16" t="inlineStr"/>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>C001_ROHIT</t>
+          <t>G_CR_ROHIT_CUT</t>
         </is>
       </c>
       <c r="K115" s="16" t="inlineStr"/>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="J116" s="17" t="inlineStr">
         <is>
-          <t>G_M_BROWN_JACKET_CUT</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="K116" s="17" t="inlineStr"/>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="K117" s="16" t="inlineStr"/>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="G118" s="16" t="inlineStr">
         <is>
-          <t>गाइड भूपेंद्र। बोले... मैं राजस्थान के रणथंभौर में था, बाघ के पीछे जीप दौड़ा रहा था।</t>
+          <t>गाइड कल्लू। बोले... मैं राजस्थान के रणथंभौर में था, बाघ के पीछे जीप दौड़ा रहा था।</t>
         </is>
       </c>
       <c r="H118" s="16" t="inlineStr">
@@ -10320,12 +10320,12 @@
       <c r="I118" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 4/9
-Guide Bhupendra</t>
+Guide Kallu</t>
         </is>
       </c>
       <c r="J118" s="16" t="inlineStr">
         <is>
-          <t>A025_BHUPENDRA</t>
+          <t>G_KALLU_CUT</t>
         </is>
       </c>
       <c r="K118" s="16" t="inlineStr"/>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
-          <t>C001_ANJALI</t>
+          <t>C011_EMMA</t>
         </is>
       </c>
       <c r="K119" s="16" t="inlineStr"/>
@@ -10458,7 +10458,7 @@
       </c>
       <c r="J120" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_SHERWANI_CUT</t>
+          <t>C013_LAWYER</t>
         </is>
       </c>
       <c r="K120" s="16" t="inlineStr"/>
@@ -10718,7 +10718,7 @@
       <c r="I124" s="16" t="inlineStr"/>
       <c r="J124" s="16" t="inlineStr">
         <is>
-          <t>C001_ROHIT</t>
+          <t>G_CR_ROHIT_CUT</t>
         </is>
       </c>
       <c r="K124" s="16" t="inlineStr">
@@ -11109,7 +11109,7 @@
       <c r="I130" s="16" t="inlineStr"/>
       <c r="J130" s="16" t="inlineStr">
         <is>
-          <t>A026_V_TSERING</t>
+          <t>C001_VIKAS</t>
         </is>
       </c>
       <c r="K130" s="16" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
-          <t>A026_V_TSERING</t>
+          <t>C001_VIKAS</t>
         </is>
       </c>
       <c r="K131" s="16" t="inlineStr"/>
@@ -11536,7 +11536,7 @@
       <c r="I137" s="16" t="inlineStr"/>
       <c r="J137" s="16" t="inlineStr">
         <is>
-          <t>P_A026_SHOES</t>
+          <t>P_SHOES</t>
         </is>
       </c>
       <c r="K137" s="16" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="G140" s="16" t="inlineStr">
         <is>
-          <t>ब्लॉगर नेहा। बोलीं... मैं मेघालय के चेरापूंजी से आई, दुनिया की सबसे ज़्यादा बारिश वाली जगहों में से एक।</t>
+          <t>ब्लॉगर तन्वी। बोले... मैं मेघालय के चेरापूंजी से आई, दुनिया की सबसे ज़्यादा बारिश वाली जगहों में से एक।</t>
         </is>
       </c>
       <c r="H140" s="16" t="inlineStr">
@@ -11741,12 +11741,12 @@
       <c r="I140" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 2/9
-Blogger Neha</t>
+Blogger Tanvi</t>
         </is>
       </c>
       <c r="J140" s="16" t="inlineStr">
         <is>
-          <t>C008_NEHA</t>
+          <t>G_TANVI</t>
         </is>
       </c>
       <c r="K140" s="16" t="inlineStr"/>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="J141" s="16" t="inlineStr">
         <is>
-          <t>G_M_CAMERA_CUT</t>
+          <t>G_M_BROWN_JACKET_CUT</t>
         </is>
       </c>
       <c r="K141" s="16" t="inlineStr"/>
@@ -11879,7 +11879,7 @@
       </c>
       <c r="J142" s="16" t="inlineStr">
         <is>
-          <t>A026_KARMA</t>
+          <t>G_M_BLUE_JACKET_B_CUT</t>
         </is>
       </c>
       <c r="K142" s="16" t="inlineStr"/>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="J143" s="16" t="inlineStr">
         <is>
-          <t>G_M_OLD_GLASSES_CUT</t>
+          <t>C006_GUPTA</t>
         </is>
       </c>
       <c r="K143" s="16" t="inlineStr"/>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="J144" s="16" t="inlineStr">
         <is>
-          <t>C002_RIYA_CUT</t>
+          <t>C001_ANJALI</t>
         </is>
       </c>
       <c r="K144" s="16" t="inlineStr"/>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="J145" s="16" t="inlineStr">
         <is>
-          <t>C16-001_DRMEHTA</t>
+          <t>G_M_OLD_GLASSES_CUT</t>
         </is>
       </c>
       <c r="K145" s="16" t="inlineStr"/>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="J146" s="16" t="inlineStr">
         <is>
-          <t>A026_DORJEE</t>
+          <t>G_M_APRON_CUT</t>
         </is>
       </c>
       <c r="K146" s="16" t="inlineStr"/>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="J147" s="17" t="inlineStr">
         <is>
-          <t>C007_VIKRAM</t>
+          <t>G_CIVIL_BLACK_CUT</t>
         </is>
       </c>
       <c r="K147" s="17" t="inlineStr"/>
@@ -12276,7 +12276,7 @@
       <c r="I148" s="16" t="inlineStr"/>
       <c r="J148" s="16" t="inlineStr">
         <is>
-          <t>A026_DORJEE</t>
+          <t>G_M_APRON_CUT</t>
         </is>
       </c>
       <c r="K148" s="16" t="inlineStr">
@@ -12667,7 +12667,7 @@
       <c r="I154" s="16" t="inlineStr"/>
       <c r="J154" s="16" t="inlineStr">
         <is>
-          <t>A027_V_MOHAPATRA</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="K154" s="16" t="inlineStr"/>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="J155" s="16" t="inlineStr">
         <is>
-          <t>A027_V_MOHAPATRA</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="K155" s="16" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="J163" s="16" t="inlineStr">
         <is>
-          <t>C002_POOJA</t>
+          <t>C019_COWORKER</t>
         </is>
       </c>
       <c r="K163" s="16" t="inlineStr"/>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>C18-003_PRATEEK</t>
+          <t>C10-004_DEEPAK</t>
         </is>
       </c>
       <c r="K165" s="16" t="inlineStr"/>
@@ -13437,7 +13437,7 @@
       </c>
       <c r="J166" s="17" t="inlineStr">
         <is>
-          <t>C17-001_SETH</t>
+          <t>C017_BESTMAN</t>
         </is>
       </c>
       <c r="K166" s="17" t="inlineStr"/>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="J167" s="16" t="inlineStr">
         <is>
-          <t>G_V_WOMAN_SAREE_CUT</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="K167" s="16" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="J168" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C005_VICKY</t>
         </is>
       </c>
       <c r="K168" s="16" t="inlineStr"/>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="J169" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="K169" s="16" t="inlineStr"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="J170" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_GREY_CUT</t>
+          <t>C007_NIKHIL</t>
         </is>
       </c>
       <c r="K170" s="16" t="inlineStr"/>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="G172" s="16" t="inlineStr">
         <is>
-          <t>सफ़ाईवाला रामू। बोले... मैं अमृतसर में जलियाँवाला बाग़ गया था।</t>
+          <t>सफ़ाईवाला गोपी। बोले... मैं अमृतसर में जलियाँवाला बाग़ गया था।</t>
         </is>
       </c>
       <c r="H172" s="16" t="inlineStr">
@@ -13835,12 +13835,12 @@
       <c r="I172" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 10/10
-Safaiwala Ramu</t>
+Safaiwala Gopi</t>
         </is>
       </c>
       <c r="J172" s="16" t="inlineStr">
         <is>
-          <t>G_RAMU</t>
+          <t>G_M_GAMCHHA_CUT</t>
         </is>
       </c>
       <c r="K172" s="16" t="inlineStr"/>
@@ -14292,7 +14292,7 @@
       <c r="I179" s="16" t="inlineStr"/>
       <c r="J179" s="16" t="inlineStr">
         <is>
-          <t>A028_V_GREWAL</t>
+          <t>C08-007_KAPOOR</t>
         </is>
       </c>
       <c r="K179" s="16" t="inlineStr"/>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="J180" s="16" t="inlineStr">
         <is>
-          <t>A028_V_GREWAL</t>
+          <t>C08-007_KAPOOR</t>
         </is>
       </c>
       <c r="K180" s="16" t="inlineStr"/>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="J188" s="16" t="inlineStr">
         <is>
-          <t>C005_VICKY</t>
+          <t>C018_BOYFRIEND</t>
         </is>
       </c>
       <c r="K188" s="16" t="inlineStr"/>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="J195" s="16" t="inlineStr">
         <is>
-          <t>C001_ANJALI</t>
+          <t>A028_ANU</t>
         </is>
       </c>
       <c r="K195" s="16" t="inlineStr"/>
@@ -15783,7 +15783,7 @@
       <c r="I202" s="16" t="inlineStr"/>
       <c r="J202" s="16" t="inlineStr">
         <is>
-          <t>C04-008_GUPTA_SLUMPED</t>
+          <t>C17-001_SETH</t>
         </is>
       </c>
       <c r="K202" s="16" t="inlineStr"/>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="J203" s="16" t="inlineStr">
         <is>
-          <t>C04-008_GUPTA_SLUMPED</t>
+          <t>C17-001_SETH</t>
         </is>
       </c>
       <c r="K203" s="16" t="inlineStr"/>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="J211" s="17" t="inlineStr">
         <is>
-          <t>C006_GUPTA</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="K211" s="17" t="inlineStr"/>
@@ -16424,7 +16424,7 @@
       </c>
       <c r="J212" s="16" t="inlineStr">
         <is>
-          <t>C004_AMIT</t>
+          <t>C003_BHATIJA</t>
         </is>
       </c>
       <c r="K212" s="16" t="inlineStr"/>
@@ -16490,7 +16490,7 @@
       </c>
       <c r="J213" s="16" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="K213" s="16" t="inlineStr"/>
@@ -16557,7 +16557,7 @@
       </c>
       <c r="J214" s="16" t="inlineStr">
         <is>
-          <t>C003_BHATIJA</t>
+          <t>C004_AMIT</t>
         </is>
       </c>
       <c r="K214" s="16" t="inlineStr"/>
@@ -16624,7 +16624,7 @@
       </c>
       <c r="J215" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>G_M_BLUE_JACKET_A_CUT</t>
         </is>
       </c>
       <c r="K215" s="16" t="inlineStr"/>
@@ -16757,7 +16757,7 @@
       </c>
       <c r="J217" s="16" t="inlineStr">
         <is>
-          <t>C08-004_MR_RATHI</t>
+          <t>C004_PADOSI</t>
         </is>
       </c>
       <c r="K217" s="16" t="inlineStr"/>
@@ -16950,7 +16950,7 @@
       <c r="I220" s="16" t="inlineStr"/>
       <c r="J220" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>G_M_BLUE_JACKET_A_CUT</t>
         </is>
       </c>
       <c r="K220" s="16" t="inlineStr">
@@ -17341,7 +17341,7 @@
       <c r="I226" s="16" t="inlineStr"/>
       <c r="J226" s="16" t="inlineStr">
         <is>
-          <t>A030_V_JOSHI</t>
+          <t>C04-010_ARJUN</t>
         </is>
       </c>
       <c r="K226" s="16" t="inlineStr"/>
@@ -17406,7 +17406,7 @@
       </c>
       <c r="J227" s="16" t="inlineStr">
         <is>
-          <t>A030_V_JOSHI</t>
+          <t>C04-010_ARJUN</t>
         </is>
       </c>
       <c r="K227" s="16" t="inlineStr"/>
@@ -17912,7 +17912,7 @@
       </c>
       <c r="J235" s="16" t="inlineStr">
         <is>
-          <t>G_M_GREY_HOODIE_CUT</t>
+          <t>C020_BROTHER</t>
         </is>
       </c>
       <c r="K235" s="16" t="inlineStr"/>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="J236" s="16" t="inlineStr">
         <is>
-          <t>C005_NEHA</t>
+          <t>G_W_PINK_SUIT_CUT</t>
         </is>
       </c>
       <c r="K236" s="16" t="inlineStr"/>
@@ -18044,7 +18044,7 @@
       </c>
       <c r="J237" s="16" t="inlineStr">
         <is>
-          <t>G_M_OLD_NOGLASSES_CUT</t>
+          <t>C011_TOM</t>
         </is>
       </c>
       <c r="K237" s="16" t="inlineStr"/>
@@ -18111,7 +18111,7 @@
       </c>
       <c r="J238" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>C018_SISTER</t>
         </is>
       </c>
       <c r="K238" s="16" t="inlineStr"/>
@@ -18378,7 +18378,7 @@
       </c>
       <c r="J242" s="16" t="inlineStr">
         <is>
-          <t>C10-004_DEEPAK</t>
+          <t>C03-003_VICKY</t>
         </is>
       </c>
       <c r="K242" s="16" t="inlineStr"/>
@@ -18510,7 +18510,7 @@
       </c>
       <c r="J244" s="17" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C008_GUEST</t>
         </is>
       </c>
       <c r="K244" s="17" t="inlineStr"/>
@@ -18575,7 +18575,7 @@
       <c r="I245" s="16" t="inlineStr"/>
       <c r="J245" s="16" t="inlineStr">
         <is>
-          <t>G_M_GREY_HOODIE_CUT</t>
+          <t>C020_BROTHER</t>
         </is>
       </c>
       <c r="K245" s="16" t="inlineStr">
@@ -20396,7 +20396,7 @@
       </c>
       <c r="H18" s="16" t="inlineStr">
         <is>
-          <t>A021_V_KAMLESH</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I18" s="16" t="inlineStr">
@@ -20469,7 +20469,7 @@
       </c>
       <c r="H19" s="16" t="inlineStr">
         <is>
-          <t>A021_V_KAMLESH</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I19" s="16" t="inlineStr">
@@ -20538,7 +20538,7 @@
       </c>
       <c r="H20" s="16" t="inlineStr">
         <is>
-          <t>A021_V_KAMLESH</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I20" s="16" t="inlineStr">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="H21" s="16" t="inlineStr">
         <is>
-          <t>A021_V_KAMLESH</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I21" s="16" t="inlineStr">
@@ -20684,7 +20684,7 @@
       </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>A021_V_KAMLESH</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I22" s="16" t="inlineStr">
@@ -20822,7 +20822,7 @@
       <c r="G24" s="16" t="inlineStr"/>
       <c r="H24" s="16" t="inlineStr">
         <is>
-          <t>P_KAANCH_TUKDE_CUT</t>
+          <t>P_KAANCH_TUKDE</t>
         </is>
       </c>
       <c r="I24" s="16" t="inlineStr">
@@ -22031,7 +22031,7 @@
       </c>
       <c r="H40" s="16" t="inlineStr">
         <is>
-          <t>G_W_MAROON_SAREE_CUT</t>
+          <t>C004_MAA</t>
         </is>
       </c>
       <c r="I40" s="16" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="H41" s="16" t="inlineStr">
         <is>
-          <t>G_W_MAROON_SAREE_CUT</t>
+          <t>C004_MAA</t>
         </is>
       </c>
       <c r="I41" s="16" t="inlineStr">
@@ -22187,7 +22187,7 @@
       </c>
       <c r="H42" s="16" t="inlineStr">
         <is>
-          <t>G_W_MAROON_SAREE_CUT</t>
+          <t>C004_MAA</t>
         </is>
       </c>
       <c r="I42" s="16" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="H43" s="16" t="inlineStr">
         <is>
-          <t>G_M_CAMERA_CUT</t>
+          <t>G_M_YELLOW_KURTA_CUT</t>
         </is>
       </c>
       <c r="I43" s="16" t="inlineStr">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="H44" s="16" t="inlineStr">
         <is>
-          <t>G_M_CAMERA_CUT</t>
+          <t>G_M_YELLOW_KURTA_CUT</t>
         </is>
       </c>
       <c r="I44" s="16" t="inlineStr">
@@ -22415,7 +22415,7 @@
       </c>
       <c r="H45" s="16" t="inlineStr">
         <is>
-          <t>G_M_CAMERA_CUT</t>
+          <t>G_M_YELLOW_KURTA_CUT</t>
         </is>
       </c>
       <c r="I45" s="16" t="inlineStr">
@@ -22488,7 +22488,7 @@
       </c>
       <c r="H46" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_GREY_CUT</t>
+          <t>C005_VICKY_KEY_CUT</t>
         </is>
       </c>
       <c r="I46" s="16" t="inlineStr">
@@ -22571,7 +22571,7 @@
       </c>
       <c r="H47" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_GREY_CUT</t>
+          <t>C005_VICKY_KEY_CUT</t>
         </is>
       </c>
       <c r="I47" s="16" t="inlineStr">
@@ -22644,7 +22644,7 @@
       </c>
       <c r="H48" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_GREY_CUT</t>
+          <t>C005_VICKY_KEY_CUT</t>
         </is>
       </c>
       <c r="I48" s="16" t="inlineStr">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="H49" s="16" t="inlineStr">
         <is>
-          <t>C08-004_MR_RATHI</t>
+          <t>G_TTE</t>
         </is>
       </c>
       <c r="I49" s="16" t="inlineStr">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="H50" s="16" t="inlineStr">
         <is>
-          <t>C08-004_MR_RATHI</t>
+          <t>G_TTE</t>
         </is>
       </c>
       <c r="I50" s="16" t="inlineStr">
@@ -22873,7 +22873,7 @@
       </c>
       <c r="H51" s="16" t="inlineStr">
         <is>
-          <t>C08-004_MR_RATHI</t>
+          <t>G_TTE</t>
         </is>
       </c>
       <c r="I51" s="16" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="H52" s="16" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="I52" s="16" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="H53" s="16" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="I53" s="16" t="inlineStr">
@@ -23708,7 +23708,7 @@
       </c>
       <c r="H62" s="16" t="inlineStr">
         <is>
-          <t>A022_V_RAO</t>
+          <t>C002_ARYAN</t>
         </is>
       </c>
       <c r="I62" s="16" t="inlineStr">
@@ -23781,7 +23781,7 @@
       </c>
       <c r="H63" s="16" t="inlineStr">
         <is>
-          <t>A022_V_RAO</t>
+          <t>C002_ARYAN</t>
         </is>
       </c>
       <c r="I63" s="16" t="inlineStr">
@@ -23850,7 +23850,7 @@
       </c>
       <c r="H64" s="16" t="inlineStr">
         <is>
-          <t>A022_V_RAO</t>
+          <t>C002_ARYAN</t>
         </is>
       </c>
       <c r="I64" s="16" t="inlineStr">
@@ -23927,7 +23927,7 @@
       </c>
       <c r="H65" s="16" t="inlineStr">
         <is>
-          <t>A022_V_RAO</t>
+          <t>C002_ARYAN</t>
         </is>
       </c>
       <c r="I65" s="16" t="inlineStr">
@@ -23996,7 +23996,7 @@
       </c>
       <c r="H66" s="16" t="inlineStr">
         <is>
-          <t>A022_V_RAO</t>
+          <t>C002_ARYAN</t>
         </is>
       </c>
       <c r="I66" s="16" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="H74" s="16" t="inlineStr">
         <is>
-          <t>C08-007_KAPOOR</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="I74" s="16" t="inlineStr">
@@ -24667,7 +24667,7 @@
       </c>
       <c r="H75" s="16" t="inlineStr">
         <is>
-          <t>C08-007_KAPOOR</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="I75" s="16" t="inlineStr">
@@ -24740,7 +24740,7 @@
       </c>
       <c r="H76" s="16" t="inlineStr">
         <is>
-          <t>C08-007_KAPOOR</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="I76" s="16" t="inlineStr">
@@ -24813,7 +24813,7 @@
       </c>
       <c r="H77" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>G_W_PINK_SUIT_CUT</t>
         </is>
       </c>
       <c r="I77" s="16" t="inlineStr">
@@ -24895,7 +24895,7 @@
       </c>
       <c r="H78" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>G_W_PINK_SUIT_CUT</t>
         </is>
       </c>
       <c r="I78" s="16" t="inlineStr">
@@ -24968,7 +24968,7 @@
       </c>
       <c r="H79" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>G_W_PINK_SUIT_CUT</t>
         </is>
       </c>
       <c r="I79" s="16" t="inlineStr">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="H80" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C007_VIKRAM</t>
         </is>
       </c>
       <c r="I80" s="16" t="inlineStr">
@@ -25123,7 +25123,7 @@
       </c>
       <c r="H81" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C007_VIKRAM</t>
         </is>
       </c>
       <c r="I81" s="16" t="inlineStr">
@@ -25196,7 +25196,7 @@
       </c>
       <c r="H82" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C007_VIKRAM</t>
         </is>
       </c>
       <c r="I82" s="16" t="inlineStr">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="H83" s="16" t="inlineStr">
         <is>
-          <t>G_M_APRON_CUT</t>
+          <t>C017_CHEF</t>
         </is>
       </c>
       <c r="I83" s="16" t="inlineStr">
@@ -25352,7 +25352,7 @@
       </c>
       <c r="H84" s="16" t="inlineStr">
         <is>
-          <t>G_M_APRON_CUT</t>
+          <t>C017_CHEF</t>
         </is>
       </c>
       <c r="I84" s="16" t="inlineStr">
@@ -25425,7 +25425,7 @@
       </c>
       <c r="H85" s="16" t="inlineStr">
         <is>
-          <t>G_M_APRON_CUT</t>
+          <t>C017_CHEF</t>
         </is>
       </c>
       <c r="I85" s="16" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H86" s="16" t="inlineStr">
         <is>
-          <t>G_V_WOMAN_SAREE_CUT</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="I86" s="16" t="inlineStr">
@@ -25581,7 +25581,7 @@
       </c>
       <c r="H87" s="16" t="inlineStr">
         <is>
-          <t>G_V_WOMAN_SAREE_CUT</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="I87" s="16" t="inlineStr">
@@ -25654,7 +25654,7 @@
       </c>
       <c r="H88" s="16" t="inlineStr">
         <is>
-          <t>G_V_WOMAN_SAREE_CUT</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="I88" s="16" t="inlineStr">
@@ -25727,7 +25727,7 @@
       </c>
       <c r="H89" s="16" t="inlineStr">
         <is>
-          <t>A022_JOHNNY</t>
+          <t>C015_MARCO</t>
         </is>
       </c>
       <c r="I89" s="16" t="inlineStr">
@@ -25810,7 +25810,7 @@
       </c>
       <c r="H90" s="16" t="inlineStr">
         <is>
-          <t>A022_JOHNNY</t>
+          <t>C015_MARCO</t>
         </is>
       </c>
       <c r="I90" s="16" t="inlineStr">
@@ -25883,7 +25883,7 @@
       </c>
       <c r="H91" s="16" t="inlineStr">
         <is>
-          <t>A022_JOHNNY</t>
+          <t>C015_MARCO</t>
         </is>
       </c>
       <c r="I91" s="16" t="inlineStr">
@@ -25956,7 +25956,7 @@
       </c>
       <c r="H92" s="16" t="inlineStr">
         <is>
-          <t>C04-010_ARJUN</t>
+          <t>G_M_LIGHTMAN_CUT</t>
         </is>
       </c>
       <c r="I92" s="16" t="inlineStr">
@@ -26038,7 +26038,7 @@
       </c>
       <c r="H93" s="16" t="inlineStr">
         <is>
-          <t>C04-010_ARJUN</t>
+          <t>G_M_LIGHTMAN_CUT</t>
         </is>
       </c>
       <c r="I93" s="16" t="inlineStr">
@@ -26340,7 +26340,7 @@
       </c>
       <c r="H97" s="16" t="inlineStr">
         <is>
-          <t>C005_NEHA</t>
+          <t>C018_SISTER</t>
         </is>
       </c>
       <c r="I97" s="16" t="inlineStr">
@@ -26422,7 +26422,7 @@
       </c>
       <c r="H98" s="16" t="inlineStr">
         <is>
-          <t>C005_NEHA</t>
+          <t>C018_SISTER</t>
         </is>
       </c>
       <c r="I98" s="16" t="inlineStr">
@@ -26495,7 +26495,7 @@
       </c>
       <c r="H99" s="16" t="inlineStr">
         <is>
-          <t>C005_NEHA</t>
+          <t>C018_SISTER</t>
         </is>
       </c>
       <c r="I99" s="16" t="inlineStr">
@@ -26568,7 +26568,7 @@
       </c>
       <c r="H100" s="16" t="inlineStr">
         <is>
-          <t>A022_JOHNNY</t>
+          <t>C015_MARCO</t>
         </is>
       </c>
       <c r="I100" s="16" t="inlineStr">
@@ -27175,7 +27175,7 @@
       </c>
       <c r="H108" s="16" t="inlineStr">
         <is>
-          <t>A023_V_DESHMUKH</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="I108" s="16" t="inlineStr">
@@ -27248,7 +27248,7 @@
       </c>
       <c r="H109" s="16" t="inlineStr">
         <is>
-          <t>A023_V_DESHMUKH</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="I109" s="16" t="inlineStr">
@@ -27317,7 +27317,7 @@
       </c>
       <c r="H110" s="16" t="inlineStr">
         <is>
-          <t>A023_V_DESHMUKH</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="I110" s="16" t="inlineStr">
@@ -27394,7 +27394,7 @@
       </c>
       <c r="H111" s="16" t="inlineStr">
         <is>
-          <t>A023_V_DESHMUKH</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="I111" s="16" t="inlineStr">
@@ -27463,7 +27463,7 @@
       </c>
       <c r="H112" s="16" t="inlineStr">
         <is>
-          <t>A023_V_DESHMUKH</t>
+          <t>G_V_MAN_GREY_CUT</t>
         </is>
       </c>
       <c r="I112" s="16" t="inlineStr">
@@ -27893,7 +27893,7 @@
       <c r="G118" s="16" t="inlineStr"/>
       <c r="H118" s="16" t="inlineStr">
         <is>
-          <t>P_A023_BOTTLE</t>
+          <t>P_BOTTLE_CUT</t>
         </is>
       </c>
       <c r="I118" s="16" t="inlineStr">
@@ -28280,7 +28280,7 @@
       </c>
       <c r="H123" s="16" t="inlineStr">
         <is>
-          <t>A023_BALA</t>
+          <t>C18-003_PRATEEK</t>
         </is>
       </c>
       <c r="I123" s="16" t="inlineStr">
@@ -28362,7 +28362,7 @@
       </c>
       <c r="H124" s="16" t="inlineStr">
         <is>
-          <t>A023_BALA</t>
+          <t>C18-003_PRATEEK</t>
         </is>
       </c>
       <c r="I124" s="16" t="inlineStr">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="H125" s="16" t="inlineStr">
         <is>
-          <t>A023_BALA</t>
+          <t>C18-003_PRATEEK</t>
         </is>
       </c>
       <c r="I125" s="16" t="inlineStr">
@@ -28891,7 +28891,7 @@
       </c>
       <c r="H131" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>C020_NOAH</t>
         </is>
       </c>
       <c r="I131" s="16" t="inlineStr">
@@ -28974,7 +28974,7 @@
       </c>
       <c r="H132" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>C020_NOAH</t>
         </is>
       </c>
       <c r="I132" s="16" t="inlineStr">
@@ -29047,7 +29047,7 @@
       </c>
       <c r="H133" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>C020_NOAH</t>
         </is>
       </c>
       <c r="I133" s="16" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="H134" s="16" t="inlineStr">
         <is>
-          <t>A023_ROY</t>
+          <t>G_CIVIL_RED_CUT</t>
         </is>
       </c>
       <c r="I134" s="16" t="inlineStr">
@@ -29202,7 +29202,7 @@
       </c>
       <c r="H135" s="16" t="inlineStr">
         <is>
-          <t>A023_ROY</t>
+          <t>G_CIVIL_RED_CUT</t>
         </is>
       </c>
       <c r="I135" s="16" t="inlineStr">
@@ -29275,7 +29275,7 @@
       </c>
       <c r="H136" s="16" t="inlineStr">
         <is>
-          <t>A023_ROY</t>
+          <t>G_CIVIL_RED_CUT</t>
         </is>
       </c>
       <c r="I136" s="16" t="inlineStr">
@@ -29348,7 +29348,7 @@
       </c>
       <c r="H137" s="16" t="inlineStr">
         <is>
-          <t>G_CR_VIKRAM_CUT</t>
+          <t>G_CR_MANOJ_CUT</t>
         </is>
       </c>
       <c r="I137" s="16" t="inlineStr">
@@ -29374,7 +29374,7 @@
       <c r="M137" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 7/10
-Cricketer Soham
+Cricketer Manoj
 (team se nikala)</t>
         </is>
       </c>
@@ -29431,7 +29431,7 @@
       </c>
       <c r="H138" s="16" t="inlineStr">
         <is>
-          <t>G_CR_VIKRAM_CUT</t>
+          <t>G_CR_MANOJ_CUT</t>
         </is>
       </c>
       <c r="I138" s="16" t="inlineStr">
@@ -29504,7 +29504,7 @@
       </c>
       <c r="H139" s="16" t="inlineStr">
         <is>
-          <t>G_CR_VIKRAM_CUT</t>
+          <t>G_CR_MANOJ_CUT</t>
         </is>
       </c>
       <c r="I139" s="16" t="inlineStr">
@@ -29577,7 +29577,7 @@
       </c>
       <c r="H140" s="16" t="inlineStr">
         <is>
-          <t>A023_AJINKYA</t>
+          <t>G_CIVIL_GREEN_CUT</t>
         </is>
       </c>
       <c r="I140" s="16" t="inlineStr">
@@ -29659,7 +29659,7 @@
       </c>
       <c r="H141" s="16" t="inlineStr">
         <is>
-          <t>A023_AJINKYA</t>
+          <t>G_CIVIL_GREEN_CUT</t>
         </is>
       </c>
       <c r="I141" s="16" t="inlineStr">
@@ -29732,7 +29732,7 @@
       </c>
       <c r="H142" s="16" t="inlineStr">
         <is>
-          <t>A023_AJINKYA</t>
+          <t>G_CIVIL_GREEN_CUT</t>
         </is>
       </c>
       <c r="I142" s="16" t="inlineStr">
@@ -29805,7 +29805,7 @@
       </c>
       <c r="H143" s="16" t="inlineStr">
         <is>
-          <t>G_W_PINK_SUIT_CUT</t>
+          <t>A023_KAPOOR</t>
         </is>
       </c>
       <c r="I143" s="16" t="inlineStr">
@@ -29887,7 +29887,7 @@
       </c>
       <c r="H144" s="16" t="inlineStr">
         <is>
-          <t>G_W_PINK_SUIT_CUT</t>
+          <t>A023_KAPOOR</t>
         </is>
       </c>
       <c r="I144" s="16" t="inlineStr">
@@ -29960,7 +29960,7 @@
       </c>
       <c r="H145" s="16" t="inlineStr">
         <is>
-          <t>C008_NEHA</t>
+          <t>A023_SAINA</t>
         </is>
       </c>
       <c r="I145" s="16" t="inlineStr">
@@ -30042,7 +30042,7 @@
       </c>
       <c r="H146" s="16" t="inlineStr">
         <is>
-          <t>C008_NEHA</t>
+          <t>A023_SAINA</t>
         </is>
       </c>
       <c r="I146" s="16" t="inlineStr">
@@ -30722,7 +30722,7 @@
       </c>
       <c r="H155" s="16" t="inlineStr">
         <is>
-          <t>A024_V_PANDEY</t>
+          <t>C04-008_GUPTA_SLUMPED</t>
         </is>
       </c>
       <c r="I155" s="16" t="inlineStr">
@@ -30795,7 +30795,7 @@
       </c>
       <c r="H156" s="16" t="inlineStr">
         <is>
-          <t>A024_V_PANDEY</t>
+          <t>C04-008_GUPTA_SLUMPED</t>
         </is>
       </c>
       <c r="I156" s="16" t="inlineStr">
@@ -30864,7 +30864,7 @@
       </c>
       <c r="H157" s="16" t="inlineStr">
         <is>
-          <t>A024_V_PANDEY</t>
+          <t>C04-008_GUPTA_SLUMPED</t>
         </is>
       </c>
       <c r="I157" s="16" t="inlineStr">
@@ -30941,7 +30941,7 @@
       </c>
       <c r="H158" s="16" t="inlineStr">
         <is>
-          <t>A024_V_PANDEY</t>
+          <t>C04-008_GUPTA_SLUMPED</t>
         </is>
       </c>
       <c r="I158" s="16" t="inlineStr">
@@ -31010,7 +31010,7 @@
       </c>
       <c r="H159" s="16" t="inlineStr">
         <is>
-          <t>A024_V_PANDEY</t>
+          <t>C04-008_GUPTA_SLUMPED</t>
         </is>
       </c>
       <c r="I159" s="16" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="H167" s="16" t="inlineStr">
         <is>
-          <t>C010_SUNITA</t>
+          <t>G_W_MAROON_SAREE_CUT</t>
         </is>
       </c>
       <c r="I167" s="16" t="inlineStr">
@@ -31681,7 +31681,7 @@
       </c>
       <c r="H168" s="16" t="inlineStr">
         <is>
-          <t>C010_SUNITA</t>
+          <t>G_W_MAROON_SAREE_CUT</t>
         </is>
       </c>
       <c r="I168" s="16" t="inlineStr">
@@ -31754,7 +31754,7 @@
       </c>
       <c r="H169" s="16" t="inlineStr">
         <is>
-          <t>C010_SUNITA</t>
+          <t>G_W_MAROON_SAREE_CUT</t>
         </is>
       </c>
       <c r="I169" s="16" t="inlineStr">
@@ -32056,7 +32056,7 @@
       </c>
       <c r="H173" s="16" t="inlineStr">
         <is>
-          <t>C004_BEHEN</t>
+          <t>C002_RIYA_CUT</t>
         </is>
       </c>
       <c r="I173" s="16" t="inlineStr">
@@ -32138,7 +32138,7 @@
       </c>
       <c r="H174" s="16" t="inlineStr">
         <is>
-          <t>C004_BEHEN</t>
+          <t>C002_RIYA_CUT</t>
         </is>
       </c>
       <c r="I174" s="16" t="inlineStr">
@@ -32211,7 +32211,7 @@
       </c>
       <c r="H175" s="16" t="inlineStr">
         <is>
-          <t>C004_BEHEN</t>
+          <t>C002_RIYA_CUT</t>
         </is>
       </c>
       <c r="I175" s="16" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="H176" s="16" t="inlineStr">
         <is>
-          <t>C004_PADOSI</t>
+          <t>C12-010_MAHESH</t>
         </is>
       </c>
       <c r="I176" s="16" t="inlineStr">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="H177" s="16" t="inlineStr">
         <is>
-          <t>C004_PADOSI</t>
+          <t>C12-010_MAHESH</t>
         </is>
       </c>
       <c r="I177" s="16" t="inlineStr">
@@ -32440,7 +32440,7 @@
       </c>
       <c r="H178" s="16" t="inlineStr">
         <is>
-          <t>C004_PADOSI</t>
+          <t>C12-010_MAHESH</t>
         </is>
       </c>
       <c r="I178" s="16" t="inlineStr">
@@ -32513,7 +32513,7 @@
       </c>
       <c r="H179" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>C003_SURAJ_CUT</t>
         </is>
       </c>
       <c r="I179" s="16" t="inlineStr">
@@ -32595,7 +32595,7 @@
       </c>
       <c r="H180" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>C003_SURAJ_CUT</t>
         </is>
       </c>
       <c r="I180" s="16" t="inlineStr">
@@ -32668,7 +32668,7 @@
       </c>
       <c r="H181" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>C003_SURAJ_CUT</t>
         </is>
       </c>
       <c r="I181" s="16" t="inlineStr">
@@ -32741,7 +32741,7 @@
       </c>
       <c r="H182" s="16" t="inlineStr">
         <is>
-          <t>G_M_YELLOW_KURTA_CUT</t>
+          <t>C001_ROHIT</t>
         </is>
       </c>
       <c r="I182" s="16" t="inlineStr">
@@ -32823,7 +32823,7 @@
       </c>
       <c r="H183" s="16" t="inlineStr">
         <is>
-          <t>G_M_YELLOW_KURTA_CUT</t>
+          <t>C001_ROHIT</t>
         </is>
       </c>
       <c r="I183" s="16" t="inlineStr">
@@ -32896,7 +32896,7 @@
       </c>
       <c r="H184" s="16" t="inlineStr">
         <is>
-          <t>G_M_YELLOW_KURTA_CUT</t>
+          <t>C001_ROHIT</t>
         </is>
       </c>
       <c r="I184" s="16" t="inlineStr">
@@ -33198,7 +33198,7 @@
       </c>
       <c r="H188" s="16" t="inlineStr">
         <is>
-          <t>G_M_LIGHTMAN_CUT</t>
+          <t>G_M_BLUE_SHIRT_CUT</t>
         </is>
       </c>
       <c r="I188" s="16" t="inlineStr">
@@ -33280,7 +33280,7 @@
       </c>
       <c r="H189" s="16" t="inlineStr">
         <is>
-          <t>G_M_LIGHTMAN_CUT</t>
+          <t>G_M_BLUE_SHIRT_CUT</t>
         </is>
       </c>
       <c r="I189" s="16" t="inlineStr">
@@ -33353,7 +33353,7 @@
       </c>
       <c r="H190" s="16" t="inlineStr">
         <is>
-          <t>G_M_LIGHTMAN_CUT</t>
+          <t>G_M_BLUE_SHIRT_CUT</t>
         </is>
       </c>
       <c r="I190" s="16" t="inlineStr">
@@ -34106,7 +34106,7 @@
       </c>
       <c r="H200" s="16" t="inlineStr">
         <is>
-          <t>A025_V_KHAN</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I200" s="16" t="inlineStr">
@@ -34179,7 +34179,7 @@
       </c>
       <c r="H201" s="16" t="inlineStr">
         <is>
-          <t>A025_V_KHAN</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I201" s="16" t="inlineStr">
@@ -34248,7 +34248,7 @@
       </c>
       <c r="H202" s="16" t="inlineStr">
         <is>
-          <t>A025_V_KHAN</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I202" s="16" t="inlineStr">
@@ -34325,7 +34325,7 @@
       </c>
       <c r="H203" s="16" t="inlineStr">
         <is>
-          <t>A025_V_KHAN</t>
+          <t>G_V_MAN_CHECK_CUT</t>
         </is>
       </c>
       <c r="I203" s="16" t="inlineStr">
@@ -34913,7 +34913,7 @@
       </c>
       <c r="H211" s="16" t="inlineStr">
         <is>
-          <t>C001_ROHIT</t>
+          <t>G_CR_ROHIT_CUT</t>
         </is>
       </c>
       <c r="I211" s="16" t="inlineStr">
@@ -34996,7 +34996,7 @@
       </c>
       <c r="H212" s="16" t="inlineStr">
         <is>
-          <t>C001_ROHIT</t>
+          <t>G_CR_ROHIT_CUT</t>
         </is>
       </c>
       <c r="I212" s="16" t="inlineStr">
@@ -35069,7 +35069,7 @@
       </c>
       <c r="H213" s="16" t="inlineStr">
         <is>
-          <t>C001_ROHIT</t>
+          <t>G_CR_ROHIT_CUT</t>
         </is>
       </c>
       <c r="I213" s="16" t="inlineStr">
@@ -35142,7 +35142,7 @@
       </c>
       <c r="H214" s="16" t="inlineStr">
         <is>
-          <t>G_M_BROWN_JACKET_CUT</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I214" s="16" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="H215" s="16" t="inlineStr">
         <is>
-          <t>G_M_BROWN_JACKET_CUT</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I215" s="16" t="inlineStr">
@@ -35297,7 +35297,7 @@
       </c>
       <c r="H216" s="16" t="inlineStr">
         <is>
-          <t>G_M_BROWN_JACKET_CUT</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="I216" s="16" t="inlineStr">
@@ -35370,7 +35370,7 @@
       </c>
       <c r="H217" s="16" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="I217" s="16" t="inlineStr">
@@ -35453,7 +35453,7 @@
       </c>
       <c r="H218" s="16" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="I218" s="16" t="inlineStr">
@@ -35526,7 +35526,7 @@
       </c>
       <c r="H219" s="16" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="I219" s="16" t="inlineStr">
@@ -35599,7 +35599,7 @@
       </c>
       <c r="H220" s="16" t="inlineStr">
         <is>
-          <t>A025_BHUPENDRA</t>
+          <t>G_KALLU_CUT</t>
         </is>
       </c>
       <c r="I220" s="16" t="inlineStr">
@@ -35625,7 +35625,7 @@
       <c r="M220" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 4/9
-Guide Bhupendra</t>
+Guide Kallu</t>
         </is>
       </c>
       <c r="N220" s="16" t="inlineStr">
@@ -35681,7 +35681,7 @@
       </c>
       <c r="H221" s="16" t="inlineStr">
         <is>
-          <t>A025_BHUPENDRA</t>
+          <t>G_KALLU_CUT</t>
         </is>
       </c>
       <c r="I221" s="16" t="inlineStr">
@@ -35754,7 +35754,7 @@
       </c>
       <c r="H222" s="16" t="inlineStr">
         <is>
-          <t>A025_BHUPENDRA</t>
+          <t>G_KALLU_CUT</t>
         </is>
       </c>
       <c r="I222" s="16" t="inlineStr">
@@ -35827,7 +35827,7 @@
       </c>
       <c r="H223" s="16" t="inlineStr">
         <is>
-          <t>C001_ANJALI</t>
+          <t>C011_EMMA</t>
         </is>
       </c>
       <c r="I223" s="16" t="inlineStr">
@@ -35909,7 +35909,7 @@
       </c>
       <c r="H224" s="16" t="inlineStr">
         <is>
-          <t>C001_ANJALI</t>
+          <t>C011_EMMA</t>
         </is>
       </c>
       <c r="I224" s="16" t="inlineStr">
@@ -35982,7 +35982,7 @@
       </c>
       <c r="H225" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_SHERWANI_CUT</t>
+          <t>C013_LAWYER</t>
         </is>
       </c>
       <c r="I225" s="16" t="inlineStr">
@@ -36065,7 +36065,7 @@
       </c>
       <c r="H226" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_SHERWANI_CUT</t>
+          <t>C013_LAWYER</t>
         </is>
       </c>
       <c r="I226" s="16" t="inlineStr">
@@ -36677,7 +36677,7 @@
       </c>
       <c r="H234" s="16" t="inlineStr">
         <is>
-          <t>C001_ROHIT</t>
+          <t>G_CR_ROHIT_CUT</t>
         </is>
       </c>
       <c r="I234" s="16" t="inlineStr">
@@ -37284,7 +37284,7 @@
       </c>
       <c r="H242" s="16" t="inlineStr">
         <is>
-          <t>A026_V_TSERING</t>
+          <t>C001_VIKAS</t>
         </is>
       </c>
       <c r="I242" s="16" t="inlineStr">
@@ -37357,7 +37357,7 @@
       </c>
       <c r="H243" s="16" t="inlineStr">
         <is>
-          <t>A026_V_TSERING</t>
+          <t>C001_VIKAS</t>
         </is>
       </c>
       <c r="I243" s="16" t="inlineStr">
@@ -37426,7 +37426,7 @@
       </c>
       <c r="H244" s="16" t="inlineStr">
         <is>
-          <t>A026_V_TSERING</t>
+          <t>C001_VIKAS</t>
         </is>
       </c>
       <c r="I244" s="16" t="inlineStr">
@@ -37503,7 +37503,7 @@
       </c>
       <c r="H245" s="16" t="inlineStr">
         <is>
-          <t>A026_V_TSERING</t>
+          <t>C001_VIKAS</t>
         </is>
       </c>
       <c r="I245" s="16" t="inlineStr">
@@ -37933,7 +37933,7 @@
       <c r="G251" s="16" t="inlineStr"/>
       <c r="H251" s="16" t="inlineStr">
         <is>
-          <t>P_A026_SHOES</t>
+          <t>P_SHOES</t>
         </is>
       </c>
       <c r="I251" s="16" t="inlineStr">
@@ -38320,7 +38320,7 @@
       </c>
       <c r="H256" s="16" t="inlineStr">
         <is>
-          <t>C008_NEHA</t>
+          <t>G_TANVI</t>
         </is>
       </c>
       <c r="I256" s="16" t="inlineStr">
@@ -38346,7 +38346,7 @@
       <c r="M256" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 2/9
-Blogger Neha</t>
+Blogger Tanvi</t>
         </is>
       </c>
       <c r="N256" s="16" t="inlineStr">
@@ -38402,7 +38402,7 @@
       </c>
       <c r="H257" s="16" t="inlineStr">
         <is>
-          <t>C008_NEHA</t>
+          <t>G_TANVI</t>
         </is>
       </c>
       <c r="I257" s="16" t="inlineStr">
@@ -38475,7 +38475,7 @@
       </c>
       <c r="H258" s="16" t="inlineStr">
         <is>
-          <t>C008_NEHA</t>
+          <t>G_TANVI</t>
         </is>
       </c>
       <c r="I258" s="16" t="inlineStr">
@@ -38548,7 +38548,7 @@
       </c>
       <c r="H259" s="16" t="inlineStr">
         <is>
-          <t>G_M_CAMERA_CUT</t>
+          <t>G_M_BROWN_JACKET_CUT</t>
         </is>
       </c>
       <c r="I259" s="16" t="inlineStr">
@@ -38630,7 +38630,7 @@
       </c>
       <c r="H260" s="16" t="inlineStr">
         <is>
-          <t>G_M_CAMERA_CUT</t>
+          <t>G_M_BROWN_JACKET_CUT</t>
         </is>
       </c>
       <c r="I260" s="16" t="inlineStr">
@@ -38703,7 +38703,7 @@
       </c>
       <c r="H261" s="16" t="inlineStr">
         <is>
-          <t>A026_KARMA</t>
+          <t>G_M_BLUE_JACKET_B_CUT</t>
         </is>
       </c>
       <c r="I261" s="16" t="inlineStr">
@@ -38786,7 +38786,7 @@
       </c>
       <c r="H262" s="16" t="inlineStr">
         <is>
-          <t>A026_KARMA</t>
+          <t>G_M_BLUE_JACKET_B_CUT</t>
         </is>
       </c>
       <c r="I262" s="16" t="inlineStr">
@@ -38859,7 +38859,7 @@
       </c>
       <c r="H263" s="16" t="inlineStr">
         <is>
-          <t>A026_KARMA</t>
+          <t>G_M_BLUE_JACKET_B_CUT</t>
         </is>
       </c>
       <c r="I263" s="16" t="inlineStr">
@@ -38932,7 +38932,7 @@
       </c>
       <c r="H264" s="16" t="inlineStr">
         <is>
-          <t>G_M_OLD_GLASSES_CUT</t>
+          <t>C006_GUPTA</t>
         </is>
       </c>
       <c r="I264" s="16" t="inlineStr">
@@ -39014,7 +39014,7 @@
       </c>
       <c r="H265" s="16" t="inlineStr">
         <is>
-          <t>G_M_OLD_GLASSES_CUT</t>
+          <t>C006_GUPTA</t>
         </is>
       </c>
       <c r="I265" s="16" t="inlineStr">
@@ -39087,7 +39087,7 @@
       </c>
       <c r="H266" s="16" t="inlineStr">
         <is>
-          <t>C002_RIYA_CUT</t>
+          <t>C001_ANJALI</t>
         </is>
       </c>
       <c r="I266" s="16" t="inlineStr">
@@ -39169,7 +39169,7 @@
       </c>
       <c r="H267" s="16" t="inlineStr">
         <is>
-          <t>C002_RIYA_CUT</t>
+          <t>C001_ANJALI</t>
         </is>
       </c>
       <c r="I267" s="16" t="inlineStr">
@@ -39242,7 +39242,7 @@
       </c>
       <c r="H268" s="16" t="inlineStr">
         <is>
-          <t>C002_RIYA_CUT</t>
+          <t>C001_ANJALI</t>
         </is>
       </c>
       <c r="I268" s="16" t="inlineStr">
@@ -39315,7 +39315,7 @@
       </c>
       <c r="H269" s="16" t="inlineStr">
         <is>
-          <t>C16-001_DRMEHTA</t>
+          <t>G_M_OLD_GLASSES_CUT</t>
         </is>
       </c>
       <c r="I269" s="16" t="inlineStr">
@@ -39398,7 +39398,7 @@
       </c>
       <c r="H270" s="16" t="inlineStr">
         <is>
-          <t>C16-001_DRMEHTA</t>
+          <t>G_M_OLD_GLASSES_CUT</t>
         </is>
       </c>
       <c r="I270" s="16" t="inlineStr">
@@ -39471,7 +39471,7 @@
       </c>
       <c r="H271" s="16" t="inlineStr">
         <is>
-          <t>C16-001_DRMEHTA</t>
+          <t>G_M_OLD_GLASSES_CUT</t>
         </is>
       </c>
       <c r="I271" s="16" t="inlineStr">
@@ -39544,7 +39544,7 @@
       </c>
       <c r="H272" s="16" t="inlineStr">
         <is>
-          <t>A026_DORJEE</t>
+          <t>G_M_APRON_CUT</t>
         </is>
       </c>
       <c r="I272" s="16" t="inlineStr">
@@ -39627,7 +39627,7 @@
       </c>
       <c r="H273" s="16" t="inlineStr">
         <is>
-          <t>A026_DORJEE</t>
+          <t>G_M_APRON_CUT</t>
         </is>
       </c>
       <c r="I273" s="16" t="inlineStr">
@@ -39700,7 +39700,7 @@
       </c>
       <c r="H274" s="16" t="inlineStr">
         <is>
-          <t>A026_DORJEE</t>
+          <t>G_M_APRON_CUT</t>
         </is>
       </c>
       <c r="I274" s="16" t="inlineStr">
@@ -39773,7 +39773,7 @@
       </c>
       <c r="H275" s="16" t="inlineStr">
         <is>
-          <t>C007_VIKRAM</t>
+          <t>G_CIVIL_BLACK_CUT</t>
         </is>
       </c>
       <c r="I275" s="16" t="inlineStr">
@@ -39855,7 +39855,7 @@
       </c>
       <c r="H276" s="16" t="inlineStr">
         <is>
-          <t>C007_VIKRAM</t>
+          <t>G_CIVIL_BLACK_CUT</t>
         </is>
       </c>
       <c r="I276" s="16" t="inlineStr">
@@ -39928,7 +39928,7 @@
       </c>
       <c r="H277" s="16" t="inlineStr">
         <is>
-          <t>C007_VIKRAM</t>
+          <t>G_CIVIL_BLACK_CUT</t>
         </is>
       </c>
       <c r="I277" s="16" t="inlineStr">
@@ -40001,7 +40001,7 @@
       </c>
       <c r="H278" s="16" t="inlineStr">
         <is>
-          <t>A026_DORJEE</t>
+          <t>G_M_APRON_CUT</t>
         </is>
       </c>
       <c r="I278" s="16" t="inlineStr">
@@ -40074,7 +40074,7 @@
       </c>
       <c r="H279" s="16" t="inlineStr">
         <is>
-          <t>A026_DORJEE</t>
+          <t>G_M_APRON_CUT</t>
         </is>
       </c>
       <c r="I279" s="16" t="inlineStr">
@@ -40681,7 +40681,7 @@
       </c>
       <c r="H287" s="16" t="inlineStr">
         <is>
-          <t>A027_V_MOHAPATRA</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="I287" s="16" t="inlineStr">
@@ -40754,7 +40754,7 @@
       </c>
       <c r="H288" s="16" t="inlineStr">
         <is>
-          <t>A027_V_MOHAPATRA</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="I288" s="16" t="inlineStr">
@@ -40823,7 +40823,7 @@
       </c>
       <c r="H289" s="16" t="inlineStr">
         <is>
-          <t>A027_V_MOHAPATRA</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="I289" s="16" t="inlineStr">
@@ -40900,7 +40900,7 @@
       </c>
       <c r="H290" s="16" t="inlineStr">
         <is>
-          <t>A027_V_MOHAPATRA</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="I290" s="16" t="inlineStr">
@@ -40969,7 +40969,7 @@
       </c>
       <c r="H291" s="16" t="inlineStr">
         <is>
-          <t>A027_V_MOHAPATRA</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="I291" s="16" t="inlineStr">
@@ -41557,7 +41557,7 @@
       </c>
       <c r="H299" s="16" t="inlineStr">
         <is>
-          <t>C002_POOJA</t>
+          <t>C019_COWORKER</t>
         </is>
       </c>
       <c r="I299" s="16" t="inlineStr">
@@ -41640,7 +41640,7 @@
       </c>
       <c r="H300" s="16" t="inlineStr">
         <is>
-          <t>C002_POOJA</t>
+          <t>C019_COWORKER</t>
         </is>
       </c>
       <c r="I300" s="16" t="inlineStr">
@@ -41713,7 +41713,7 @@
       </c>
       <c r="H301" s="16" t="inlineStr">
         <is>
-          <t>C002_POOJA</t>
+          <t>C019_COWORKER</t>
         </is>
       </c>
       <c r="I301" s="16" t="inlineStr">
@@ -41942,7 +41942,7 @@
       </c>
       <c r="H304" s="16" t="inlineStr">
         <is>
-          <t>C18-003_PRATEEK</t>
+          <t>C10-004_DEEPAK</t>
         </is>
       </c>
       <c r="I304" s="16" t="inlineStr">
@@ -42024,7 +42024,7 @@
       </c>
       <c r="H305" s="16" t="inlineStr">
         <is>
-          <t>C18-003_PRATEEK</t>
+          <t>C10-004_DEEPAK</t>
         </is>
       </c>
       <c r="I305" s="16" t="inlineStr">
@@ -42097,7 +42097,7 @@
       </c>
       <c r="H306" s="16" t="inlineStr">
         <is>
-          <t>C18-003_PRATEEK</t>
+          <t>C10-004_DEEPAK</t>
         </is>
       </c>
       <c r="I306" s="16" t="inlineStr">
@@ -42170,7 +42170,7 @@
       </c>
       <c r="H307" s="16" t="inlineStr">
         <is>
-          <t>C17-001_SETH</t>
+          <t>C017_BESTMAN</t>
         </is>
       </c>
       <c r="I307" s="16" t="inlineStr">
@@ -42252,7 +42252,7 @@
       </c>
       <c r="H308" s="16" t="inlineStr">
         <is>
-          <t>C17-001_SETH</t>
+          <t>C017_BESTMAN</t>
         </is>
       </c>
       <c r="I308" s="16" t="inlineStr">
@@ -42325,7 +42325,7 @@
       </c>
       <c r="H309" s="16" t="inlineStr">
         <is>
-          <t>C17-001_SETH</t>
+          <t>C017_BESTMAN</t>
         </is>
       </c>
       <c r="I309" s="16" t="inlineStr">
@@ -42398,7 +42398,7 @@
       </c>
       <c r="H310" s="16" t="inlineStr">
         <is>
-          <t>G_V_WOMAN_SAREE_CUT</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="I310" s="16" t="inlineStr">
@@ -42481,7 +42481,7 @@
       </c>
       <c r="H311" s="16" t="inlineStr">
         <is>
-          <t>G_V_WOMAN_SAREE_CUT</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="I311" s="16" t="inlineStr">
@@ -42554,7 +42554,7 @@
       </c>
       <c r="H312" s="16" t="inlineStr">
         <is>
-          <t>G_V_WOMAN_SAREE_CUT</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="I312" s="16" t="inlineStr">
@@ -42627,7 +42627,7 @@
       </c>
       <c r="H313" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C005_VICKY</t>
         </is>
       </c>
       <c r="I313" s="16" t="inlineStr">
@@ -42709,7 +42709,7 @@
       </c>
       <c r="H314" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C005_VICKY</t>
         </is>
       </c>
       <c r="I314" s="16" t="inlineStr">
@@ -42782,7 +42782,7 @@
       </c>
       <c r="H315" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C005_VICKY</t>
         </is>
       </c>
       <c r="I315" s="16" t="inlineStr">
@@ -42855,7 +42855,7 @@
       </c>
       <c r="H316" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="I316" s="16" t="inlineStr">
@@ -42938,7 +42938,7 @@
       </c>
       <c r="H317" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="I317" s="16" t="inlineStr">
@@ -43011,7 +43011,7 @@
       </c>
       <c r="H318" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="I318" s="16" t="inlineStr">
@@ -43084,7 +43084,7 @@
       </c>
       <c r="H319" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_GREY_CUT</t>
+          <t>C007_NIKHIL</t>
         </is>
       </c>
       <c r="I319" s="16" t="inlineStr">
@@ -43166,7 +43166,7 @@
       </c>
       <c r="H320" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_GREY_CUT</t>
+          <t>C007_NIKHIL</t>
         </is>
       </c>
       <c r="I320" s="16" t="inlineStr">
@@ -43239,7 +43239,7 @@
       </c>
       <c r="H321" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_GREY_CUT</t>
+          <t>C007_NIKHIL</t>
         </is>
       </c>
       <c r="I321" s="16" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="H325" s="16" t="inlineStr">
         <is>
-          <t>G_RAMU</t>
+          <t>G_M_GAMCHHA_CUT</t>
         </is>
       </c>
       <c r="I325" s="16" t="inlineStr">
@@ -43567,7 +43567,7 @@
       <c r="M325" s="16" t="inlineStr">
         <is>
           <t>SUSPECT 10/10
-Safaiwala Ramu</t>
+Safaiwala Gopi</t>
         </is>
       </c>
       <c r="N325" s="16" t="inlineStr">
@@ -43623,7 +43623,7 @@
       </c>
       <c r="H326" s="16" t="inlineStr">
         <is>
-          <t>G_RAMU</t>
+          <t>G_M_GAMCHHA_CUT</t>
         </is>
       </c>
       <c r="I326" s="16" t="inlineStr">
@@ -44303,7 +44303,7 @@
       </c>
       <c r="H335" s="16" t="inlineStr">
         <is>
-          <t>A028_V_GREWAL</t>
+          <t>C08-007_KAPOOR</t>
         </is>
       </c>
       <c r="I335" s="16" t="inlineStr">
@@ -44376,7 +44376,7 @@
       </c>
       <c r="H336" s="16" t="inlineStr">
         <is>
-          <t>A028_V_GREWAL</t>
+          <t>C08-007_KAPOOR</t>
         </is>
       </c>
       <c r="I336" s="16" t="inlineStr">
@@ -44445,7 +44445,7 @@
       </c>
       <c r="H337" s="16" t="inlineStr">
         <is>
-          <t>A028_V_GREWAL</t>
+          <t>C08-007_KAPOOR</t>
         </is>
       </c>
       <c r="I337" s="16" t="inlineStr">
@@ -44522,7 +44522,7 @@
       </c>
       <c r="H338" s="16" t="inlineStr">
         <is>
-          <t>A028_V_GREWAL</t>
+          <t>C08-007_KAPOOR</t>
         </is>
       </c>
       <c r="I338" s="16" t="inlineStr">
@@ -44591,7 +44591,7 @@
       </c>
       <c r="H339" s="16" t="inlineStr">
         <is>
-          <t>A028_V_GREWAL</t>
+          <t>C08-007_KAPOOR</t>
         </is>
       </c>
       <c r="I339" s="16" t="inlineStr">
@@ -45179,7 +45179,7 @@
       </c>
       <c r="H347" s="16" t="inlineStr">
         <is>
-          <t>C005_VICKY</t>
+          <t>C018_BOYFRIEND</t>
         </is>
       </c>
       <c r="I347" s="16" t="inlineStr">
@@ -45262,7 +45262,7 @@
       </c>
       <c r="H348" s="16" t="inlineStr">
         <is>
-          <t>C005_VICKY</t>
+          <t>C018_BOYFRIEND</t>
         </is>
       </c>
       <c r="I348" s="16" t="inlineStr">
@@ -45335,7 +45335,7 @@
       </c>
       <c r="H349" s="16" t="inlineStr">
         <is>
-          <t>C005_VICKY</t>
+          <t>C018_BOYFRIEND</t>
         </is>
       </c>
       <c r="I349" s="16" t="inlineStr">
@@ -45408,7 +45408,7 @@
       </c>
       <c r="H350" s="16" t="inlineStr">
         <is>
-          <t>C005_VICKY</t>
+          <t>C018_BOYFRIEND</t>
         </is>
       </c>
       <c r="I350" s="16" t="inlineStr">
@@ -46997,7 +46997,7 @@
       </c>
       <c r="H371" s="16" t="inlineStr">
         <is>
-          <t>C001_ANJALI</t>
+          <t>A028_ANU</t>
         </is>
       </c>
       <c r="I371" s="16" t="inlineStr">
@@ -47079,7 +47079,7 @@
       </c>
       <c r="H372" s="16" t="inlineStr">
         <is>
-          <t>C001_ANJALI</t>
+          <t>A028_ANU</t>
         </is>
       </c>
       <c r="I372" s="16" t="inlineStr">
@@ -47152,7 +47152,7 @@
       </c>
       <c r="H373" s="16" t="inlineStr">
         <is>
-          <t>C001_ANJALI</t>
+          <t>A028_ANU</t>
         </is>
       </c>
       <c r="I373" s="16" t="inlineStr">
@@ -47901,7 +47901,7 @@
       </c>
       <c r="H383" s="16" t="inlineStr">
         <is>
-          <t>C04-008_GUPTA_SLUMPED</t>
+          <t>C17-001_SETH</t>
         </is>
       </c>
       <c r="I383" s="16" t="inlineStr">
@@ -47974,7 +47974,7 @@
       </c>
       <c r="H384" s="16" t="inlineStr">
         <is>
-          <t>C04-008_GUPTA_SLUMPED</t>
+          <t>C17-001_SETH</t>
         </is>
       </c>
       <c r="I384" s="16" t="inlineStr">
@@ -48043,7 +48043,7 @@
       </c>
       <c r="H385" s="16" t="inlineStr">
         <is>
-          <t>C04-008_GUPTA_SLUMPED</t>
+          <t>C17-001_SETH</t>
         </is>
       </c>
       <c r="I385" s="16" t="inlineStr">
@@ -48639,7 +48639,7 @@
       </c>
       <c r="H393" s="16" t="inlineStr">
         <is>
-          <t>C006_GUPTA</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="I393" s="16" t="inlineStr">
@@ -48721,7 +48721,7 @@
       </c>
       <c r="H394" s="16" t="inlineStr">
         <is>
-          <t>C006_GUPTA</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="I394" s="16" t="inlineStr">
@@ -48794,7 +48794,7 @@
       </c>
       <c r="H395" s="16" t="inlineStr">
         <is>
-          <t>C006_GUPTA</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="I395" s="16" t="inlineStr">
@@ -48867,7 +48867,7 @@
       </c>
       <c r="H396" s="16" t="inlineStr">
         <is>
-          <t>C006_GUPTA</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="I396" s="16" t="inlineStr">
@@ -48940,7 +48940,7 @@
       </c>
       <c r="H397" s="16" t="inlineStr">
         <is>
-          <t>C004_AMIT</t>
+          <t>C003_BHATIJA</t>
         </is>
       </c>
       <c r="I397" s="16" t="inlineStr">
@@ -49023,7 +49023,7 @@
       </c>
       <c r="H398" s="16" t="inlineStr">
         <is>
-          <t>C004_AMIT</t>
+          <t>C003_BHATIJA</t>
         </is>
       </c>
       <c r="I398" s="16" t="inlineStr">
@@ -49096,7 +49096,7 @@
       </c>
       <c r="H399" s="16" t="inlineStr">
         <is>
-          <t>C004_AMIT</t>
+          <t>C003_BHATIJA</t>
         </is>
       </c>
       <c r="I399" s="16" t="inlineStr">
@@ -49169,7 +49169,7 @@
       </c>
       <c r="H400" s="16" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="I400" s="16" t="inlineStr">
@@ -49251,7 +49251,7 @@
       </c>
       <c r="H401" s="16" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="I401" s="16" t="inlineStr">
@@ -49324,7 +49324,7 @@
       </c>
       <c r="H402" s="16" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="I402" s="16" t="inlineStr">
@@ -49397,7 +49397,7 @@
       </c>
       <c r="H403" s="16" t="inlineStr">
         <is>
-          <t>C003_BHATIJA</t>
+          <t>C004_AMIT</t>
         </is>
       </c>
       <c r="I403" s="16" t="inlineStr">
@@ -49480,7 +49480,7 @@
       </c>
       <c r="H404" s="16" t="inlineStr">
         <is>
-          <t>C003_BHATIJA</t>
+          <t>C004_AMIT</t>
         </is>
       </c>
       <c r="I404" s="16" t="inlineStr">
@@ -49553,7 +49553,7 @@
       </c>
       <c r="H405" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>G_M_BLUE_JACKET_A_CUT</t>
         </is>
       </c>
       <c r="I405" s="16" t="inlineStr">
@@ -49636,7 +49636,7 @@
       </c>
       <c r="H406" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>G_M_BLUE_JACKET_A_CUT</t>
         </is>
       </c>
       <c r="I406" s="16" t="inlineStr">
@@ -49864,7 +49864,7 @@
       </c>
       <c r="H409" s="16" t="inlineStr">
         <is>
-          <t>C08-004_MR_RATHI</t>
+          <t>C004_PADOSI</t>
         </is>
       </c>
       <c r="I409" s="16" t="inlineStr">
@@ -49947,7 +49947,7 @@
       </c>
       <c r="H410" s="16" t="inlineStr">
         <is>
-          <t>C08-004_MR_RATHI</t>
+          <t>C004_PADOSI</t>
         </is>
       </c>
       <c r="I410" s="16" t="inlineStr">
@@ -50020,7 +50020,7 @@
       </c>
       <c r="H411" s="16" t="inlineStr">
         <is>
-          <t>C08-004_MR_RATHI</t>
+          <t>C004_PADOSI</t>
         </is>
       </c>
       <c r="I411" s="16" t="inlineStr">
@@ -50403,7 +50403,7 @@
       </c>
       <c r="H416" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>G_M_BLUE_JACKET_A_CUT</t>
         </is>
       </c>
       <c r="I416" s="16" t="inlineStr">
@@ -51079,7 +51079,7 @@
       </c>
       <c r="H425" s="16" t="inlineStr">
         <is>
-          <t>A030_V_JOSHI</t>
+          <t>C04-010_ARJUN</t>
         </is>
       </c>
       <c r="I425" s="16" t="inlineStr">
@@ -51152,7 +51152,7 @@
       </c>
       <c r="H426" s="16" t="inlineStr">
         <is>
-          <t>A030_V_JOSHI</t>
+          <t>C04-010_ARJUN</t>
         </is>
       </c>
       <c r="I426" s="16" t="inlineStr">
@@ -51221,7 +51221,7 @@
       </c>
       <c r="H427" s="16" t="inlineStr">
         <is>
-          <t>A030_V_JOSHI</t>
+          <t>C04-010_ARJUN</t>
         </is>
       </c>
       <c r="I427" s="16" t="inlineStr">
@@ -51817,7 +51817,7 @@
       </c>
       <c r="H435" s="16" t="inlineStr">
         <is>
-          <t>G_M_GREY_HOODIE_CUT</t>
+          <t>C020_BROTHER</t>
         </is>
       </c>
       <c r="I435" s="16" t="inlineStr">
@@ -51900,7 +51900,7 @@
       </c>
       <c r="H436" s="16" t="inlineStr">
         <is>
-          <t>G_M_GREY_HOODIE_CUT</t>
+          <t>C020_BROTHER</t>
         </is>
       </c>
       <c r="I436" s="16" t="inlineStr">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="H437" s="16" t="inlineStr">
         <is>
-          <t>G_M_GREY_HOODIE_CUT</t>
+          <t>C020_BROTHER</t>
         </is>
       </c>
       <c r="I437" s="16" t="inlineStr">
@@ -52046,7 +52046,7 @@
       </c>
       <c r="H438" s="16" t="inlineStr">
         <is>
-          <t>C005_NEHA</t>
+          <t>G_W_PINK_SUIT_CUT</t>
         </is>
       </c>
       <c r="I438" s="16" t="inlineStr">
@@ -52128,7 +52128,7 @@
       </c>
       <c r="H439" s="16" t="inlineStr">
         <is>
-          <t>C005_NEHA</t>
+          <t>G_W_PINK_SUIT_CUT</t>
         </is>
       </c>
       <c r="I439" s="16" t="inlineStr">
@@ -52201,7 +52201,7 @@
       </c>
       <c r="H440" s="16" t="inlineStr">
         <is>
-          <t>G_M_OLD_NOGLASSES_CUT</t>
+          <t>C011_TOM</t>
         </is>
       </c>
       <c r="I440" s="16" t="inlineStr">
@@ -52283,7 +52283,7 @@
       </c>
       <c r="H441" s="16" t="inlineStr">
         <is>
-          <t>G_M_OLD_NOGLASSES_CUT</t>
+          <t>C011_TOM</t>
         </is>
       </c>
       <c r="I441" s="16" t="inlineStr">
@@ -52356,7 +52356,7 @@
       </c>
       <c r="H442" s="16" t="inlineStr">
         <is>
-          <t>G_M_OLD_NOGLASSES_CUT</t>
+          <t>C011_TOM</t>
         </is>
       </c>
       <c r="I442" s="16" t="inlineStr">
@@ -52429,7 +52429,7 @@
       </c>
       <c r="H443" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>C018_SISTER</t>
         </is>
       </c>
       <c r="I443" s="16" t="inlineStr">
@@ -52512,7 +52512,7 @@
       </c>
       <c r="H444" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>C018_SISTER</t>
         </is>
       </c>
       <c r="I444" s="16" t="inlineStr">
@@ -52585,7 +52585,7 @@
       </c>
       <c r="H445" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>C018_SISTER</t>
         </is>
       </c>
       <c r="I445" s="16" t="inlineStr">
@@ -52658,7 +52658,7 @@
       </c>
       <c r="H446" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>C018_SISTER</t>
         </is>
       </c>
       <c r="I446" s="16" t="inlineStr">
@@ -53417,7 +53417,7 @@
       </c>
       <c r="H456" s="16" t="inlineStr">
         <is>
-          <t>C10-004_DEEPAK</t>
+          <t>C03-003_VICKY</t>
         </is>
       </c>
       <c r="I456" s="16" t="inlineStr">
@@ -53500,7 +53500,7 @@
       </c>
       <c r="H457" s="16" t="inlineStr">
         <is>
-          <t>C10-004_DEEPAK</t>
+          <t>C03-003_VICKY</t>
         </is>
       </c>
       <c r="I457" s="16" t="inlineStr">
@@ -53573,7 +53573,7 @@
       </c>
       <c r="H458" s="16" t="inlineStr">
         <is>
-          <t>C10-004_DEEPAK</t>
+          <t>C03-003_VICKY</t>
         </is>
       </c>
       <c r="I458" s="16" t="inlineStr">
@@ -53874,7 +53874,7 @@
       </c>
       <c r="H462" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C008_GUEST</t>
         </is>
       </c>
       <c r="I462" s="16" t="inlineStr">
@@ -53956,7 +53956,7 @@
       </c>
       <c r="H463" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C008_GUEST</t>
         </is>
       </c>
       <c r="I463" s="16" t="inlineStr">
@@ -54029,7 +54029,7 @@
       </c>
       <c r="H464" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C008_GUEST</t>
         </is>
       </c>
       <c r="I464" s="16" t="inlineStr">
@@ -54102,7 +54102,7 @@
       </c>
       <c r="H465" s="16" t="inlineStr">
         <is>
-          <t>G_M_GREY_HOODIE_CUT</t>
+          <t>C020_BROTHER</t>
         </is>
       </c>
       <c r="I465" s="16" t="inlineStr">
@@ -56443,7 +56443,7 @@
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>A021_V_KAMLESH</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I3" s="16" t="inlineStr">
@@ -56516,7 +56516,7 @@
       </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
-          <t>A021_V_KAMLESH</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I4" s="16" t="inlineStr">
@@ -56585,7 +56585,7 @@
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>A021_V_KAMLESH</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I5" s="16" t="inlineStr">
@@ -56662,7 +56662,7 @@
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>A021_V_KAMLESH</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I6" s="16" t="inlineStr">
@@ -56731,7 +56731,7 @@
       </c>
       <c r="H7" s="16" t="inlineStr">
         <is>
-          <t>A021_V_KAMLESH</t>
+          <t>C08-004_MR_RATHI</t>
         </is>
       </c>
       <c r="I7" s="16" t="inlineStr">
@@ -56873,7 +56873,7 @@
       </c>
       <c r="H9" s="16" t="inlineStr">
         <is>
-          <t>P_KAANCH_TUKDE_CUT ... P_A021_PHOTO</t>
+          <t>P_KAANCH_TUKDE ... P_A021_PHOTO</t>
         </is>
       </c>
       <c r="I9" s="16" t="inlineStr">
@@ -56950,7 +56950,7 @@
       </c>
       <c r="H10" s="16" t="inlineStr">
         <is>
-          <t>P_KAANCH_TUKDE_CUT ... P_A021_PHOTO</t>
+          <t>P_KAANCH_TUKDE ... P_A021_PHOTO</t>
         </is>
       </c>
       <c r="I10" s="16" t="inlineStr">
@@ -57023,7 +57023,7 @@
       </c>
       <c r="H11" s="16" t="inlineStr">
         <is>
-          <t>P_KAANCH_TUKDE_CUT ... P_A021_PHOTO</t>
+          <t>P_KAANCH_TUKDE ... P_A021_PHOTO</t>
         </is>
       </c>
       <c r="I11" s="16" t="inlineStr">
@@ -57481,7 +57481,7 @@
       </c>
       <c r="H17" s="16" t="inlineStr">
         <is>
-          <t>G_M_CAMERA_CUT</t>
+          <t>G_M_YELLOW_KURTA_CUT</t>
         </is>
       </c>
       <c r="I17" s="16" t="inlineStr">
@@ -57563,7 +57563,7 @@
       </c>
       <c r="H18" s="16" t="inlineStr">
         <is>
-          <t>G_M_CAMERA_CUT</t>
+          <t>G_M_YELLOW_KURTA_CUT</t>
         </is>
       </c>
       <c r="I18" s="16" t="inlineStr">
@@ -57636,7 +57636,7 @@
       </c>
       <c r="H19" s="16" t="inlineStr">
         <is>
-          <t>G_M_CAMERA_CUT</t>
+          <t>G_M_YELLOW_KURTA_CUT</t>
         </is>
       </c>
       <c r="I19" s="16" t="inlineStr">
@@ -57709,7 +57709,7 @@
       </c>
       <c r="H20" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_GREY_CUT</t>
+          <t>C005_VICKY_KEY_CUT</t>
         </is>
       </c>
       <c r="I20" s="16" t="inlineStr">
@@ -57792,7 +57792,7 @@
       </c>
       <c r="H21" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_GREY_CUT</t>
+          <t>C005_VICKY_KEY_CUT</t>
         </is>
       </c>
       <c r="I21" s="16" t="inlineStr">
@@ -57865,7 +57865,7 @@
       </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="I22" s="16" t="inlineStr">
@@ -57947,7 +57947,7 @@
       </c>
       <c r="H23" s="16" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="I23" s="16" t="inlineStr">
@@ -58474,7 +58474,7 @@
       </c>
       <c r="H30" s="16" t="inlineStr">
         <is>
-          <t>A022_V_RAO</t>
+          <t>C002_ARYAN</t>
         </is>
       </c>
       <c r="I30" s="16" t="inlineStr">
@@ -58547,7 +58547,7 @@
       </c>
       <c r="H31" s="16" t="inlineStr">
         <is>
-          <t>A022_V_RAO</t>
+          <t>C002_ARYAN</t>
         </is>
       </c>
       <c r="I31" s="16" t="inlineStr">
@@ -58616,7 +58616,7 @@
       </c>
       <c r="H32" s="16" t="inlineStr">
         <is>
-          <t>A022_V_RAO</t>
+          <t>C002_ARYAN</t>
         </is>
       </c>
       <c r="I32" s="16" t="inlineStr">
@@ -58693,7 +58693,7 @@
       </c>
       <c r="H33" s="16" t="inlineStr">
         <is>
-          <t>A022_V_RAO</t>
+          <t>C002_ARYAN</t>
         </is>
       </c>
       <c r="I33" s="16" t="inlineStr">
@@ -59058,7 +59058,7 @@
       </c>
       <c r="H38" s="16" t="inlineStr">
         <is>
-          <t>C08-007_KAPOOR</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="I38" s="16" t="inlineStr">
@@ -59141,7 +59141,7 @@
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>C08-007_KAPOOR</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="I39" s="16" t="inlineStr">
@@ -59214,7 +59214,7 @@
       </c>
       <c r="H40" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C007_VIKRAM</t>
         </is>
       </c>
       <c r="I40" s="16" t="inlineStr">
@@ -59296,7 +59296,7 @@
       </c>
       <c r="H41" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C007_VIKRAM</t>
         </is>
       </c>
       <c r="I41" s="16" t="inlineStr">
@@ -59369,7 +59369,7 @@
       </c>
       <c r="H42" s="16" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C007_VIKRAM</t>
         </is>
       </c>
       <c r="I42" s="16" t="inlineStr">
@@ -59442,7 +59442,7 @@
       </c>
       <c r="H43" s="16" t="inlineStr">
         <is>
-          <t>G_V_WOMAN_SAREE_CUT</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="I43" s="16" t="inlineStr">
@@ -59525,7 +59525,7 @@
       </c>
       <c r="H44" s="16" t="inlineStr">
         <is>
-          <t>G_V_WOMAN_SAREE_CUT</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="I44" s="16" t="inlineStr">
@@ -59598,7 +59598,7 @@
       </c>
       <c r="H45" s="16" t="inlineStr">
         <is>
-          <t>A022_JOHNNY</t>
+          <t>C015_MARCO</t>
         </is>
       </c>
       <c r="I45" s="16" t="inlineStr">
@@ -59681,7 +59681,7 @@
       </c>
       <c r="H46" s="16" t="inlineStr">
         <is>
-          <t>A022_JOHNNY</t>
+          <t>C015_MARCO</t>
         </is>
       </c>
       <c r="I46" s="16" t="inlineStr">
@@ -59754,7 +59754,7 @@
       </c>
       <c r="H47" s="16" t="inlineStr">
         <is>
-          <t>C005_NEHA</t>
+          <t>C018_SISTER</t>
         </is>
       </c>
       <c r="I47" s="16" t="inlineStr">
@@ -59836,7 +59836,7 @@
       </c>
       <c r="H48" s="16" t="inlineStr">
         <is>
-          <t>C005_NEHA</t>
+          <t>C018_SISTER</t>
         </is>
       </c>
       <c r="I48" s="16" t="inlineStr">
@@ -60363,7 +60363,7 @@
       </c>
       <c r="H55" s="16" t="inlineStr">
         <is>
-          <t>A027_V_MOHAPATRA</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="I55" s="16" t="inlineStr">
@@ -60436,7 +60436,7 @@
       </c>
       <c r="H56" s="16" t="inlineStr">
         <is>
-          <t>A027_V_MOHAPATRA</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="I56" s="16" t="inlineStr">
@@ -60505,7 +60505,7 @@
       </c>
       <c r="H57" s="16" t="inlineStr">
         <is>
-          <t>A027_V_MOHAPATRA</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="I57" s="16" t="inlineStr">
@@ -60582,7 +60582,7 @@
       </c>
       <c r="H58" s="16" t="inlineStr">
         <is>
-          <t>A027_V_MOHAPATRA</t>
+          <t>G_V_MAN_SHERWANI_CUT</t>
         </is>
       </c>
       <c r="I58" s="16" t="inlineStr">
@@ -60947,7 +60947,7 @@
       </c>
       <c r="H63" s="16" t="inlineStr">
         <is>
-          <t>C002_POOJA</t>
+          <t>C019_COWORKER</t>
         </is>
       </c>
       <c r="I63" s="16" t="inlineStr">
@@ -61030,7 +61030,7 @@
       </c>
       <c r="H64" s="16" t="inlineStr">
         <is>
-          <t>C002_POOJA</t>
+          <t>C019_COWORKER</t>
         </is>
       </c>
       <c r="I64" s="16" t="inlineStr">
@@ -61186,7 +61186,7 @@
       </c>
       <c r="H66" s="16" t="inlineStr">
         <is>
-          <t>C17-001_SETH</t>
+          <t>C017_BESTMAN</t>
         </is>
       </c>
       <c r="I66" s="16" t="inlineStr">
@@ -61268,7 +61268,7 @@
       </c>
       <c r="H67" s="16" t="inlineStr">
         <is>
-          <t>C17-001_SETH</t>
+          <t>C017_BESTMAN</t>
         </is>
       </c>
       <c r="I67" s="16" t="inlineStr">
@@ -61341,7 +61341,7 @@
       </c>
       <c r="H68" s="16" t="inlineStr">
         <is>
-          <t>C17-001_SETH</t>
+          <t>C017_BESTMAN</t>
         </is>
       </c>
       <c r="I68" s="16" t="inlineStr">
@@ -61414,7 +61414,7 @@
       </c>
       <c r="H69" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="I69" s="16" t="inlineStr">
@@ -61497,7 +61497,7 @@
       </c>
       <c r="H70" s="16" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="I70" s="16" t="inlineStr">
@@ -62309,36 +62309,36 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>A021_V_KAMLESH</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>C08-004_MR_RATHI</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>A021</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Victim</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Indian mill owner Kamlesh Agrawal, about 58, kurta and Nehru jacket, slumped on a leather chair, eyes closed</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian mill owner Kamlesh Agrawal, about 58, kurta and Nehru jacket, slumped on a leather chair, eyes closed. Peaceful pose, YouTube-safe: no blood, no wounds. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>P_KAANCH_TUKDE_CUT</t>
+          <t>P_KAANCH_TUKDE</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
@@ -62554,7 +62554,7 @@
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>G_W_MAROON_SAREE_CUT</t>
+          <t>C004_MAA</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
@@ -62581,7 +62581,7 @@
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>G_M_CAMERA_CUT</t>
+          <t>G_M_YELLOW_KURTA_CUT</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
@@ -62608,7 +62608,7 @@
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>G_V_MAN_GREY_CUT</t>
+          <t>C005_VICKY_KEY_CUT</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
@@ -62635,7 +62635,7 @@
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>C08-004_MR_RATHI</t>
+          <t>G_TTE</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr">
@@ -62662,7 +62662,7 @@
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
@@ -62714,29 +62714,29 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>A022_V_RAO</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>C002_ARYAN</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>A022</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>Victim</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>Indian resort owner Srinivas Rao, about 55, white shirt, slumped on an office chair, eyes closed</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian resort owner Srinivas Rao, about 55, white shirt, slumped on an office chair, eyes closed. Peaceful pose, YouTube-safe: no blood, no wounds. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -62878,7 +62878,7 @@
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>C08-007_KAPOOR</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
@@ -62905,7 +62905,7 @@
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>G_W_PINK_SUIT_CUT</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
@@ -62932,7 +62932,7 @@
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C007_VIKRAM</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
@@ -62959,7 +62959,7 @@
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>G_M_APRON_CUT</t>
+          <t>C017_CHEF</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
@@ -62986,7 +62986,7 @@
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>G_V_WOMAN_SAREE_CUT</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
@@ -63011,36 +63011,36 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>A022_JOHNNY</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>C015_MARCO</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>A022</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Lifeguard Johnny (geele pair isi ke)</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Fit young man about 28, lifeguard vest, wet hair. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>C04-010_ARJUN</t>
+          <t>G_M_LIGHTMAN_CUT</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
@@ -63094,7 +63094,7 @@
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>C005_NEHA</t>
+          <t>C018_SISTER</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
@@ -63146,29 +63146,29 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>A023_V_DESHMUKH</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>G_V_MAN_GREY_CUT</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>A023</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>Victim</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>Indian sports club president Vijay Deshmukh, about 60, track jacket, slumped on a locker room bench, eyes closed</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian sports club president Vijay Deshmukh, about 60, track jacket, slumped on a locker room bench, eyes closed. Peaceful pose, YouTube-safe: no blood, no wounds. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -63281,29 +63281,29 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
-        <is>
-          <t>P_A023_BOTTLE</t>
-        </is>
-      </c>
-      <c r="B45" s="18" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>P_BOTTLE_CUT</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>A023</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D45" s="18" t="inlineStr">
+      <c r="D45" s="19" t="inlineStr">
         <is>
           <t>Spilled sports water bottle</t>
         </is>
       </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Spilled sports water bottle. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -63335,29 +63335,29 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>A023_BALA</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>C18-003_PRATEEK</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>A023</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D47" s="19" t="inlineStr">
         <is>
           <t>Kabaddi khiladi Bala</t>
         </is>
       </c>
-      <c r="E47" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Muscular young man about 25, kabaddi vest. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -63418,7 +63418,7 @@
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>C020_NOAH</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
@@ -63443,36 +63443,36 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>A023_ROY</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>G_CIVIL_RED_CUT</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>A023</t>
         </is>
       </c>
-      <c r="C51" s="16" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>Basketball coach Roy</t>
         </is>
       </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Tall Indian man about 38, basketball jersey. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>G_CR_VIKRAM_CUT</t>
+          <t>G_CR_MANOJ_CUT</t>
         </is>
       </c>
       <c r="B52" s="19" t="inlineStr">
@@ -63487,7 +63487,7 @@
       </c>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>Cricketer Soham (team se nikala)</t>
+          <t>Cricketer Manoj (team se nikala)</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
@@ -63497,83 +63497,83 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>A023_AJINKYA</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>G_CIVIL_GREEN_CUT</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>A023</t>
         </is>
       </c>
-      <c r="C53" s="16" t="inlineStr">
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D53" s="16" t="inlineStr">
+      <c r="D53" s="19" t="inlineStr">
         <is>
           <t>Volleyball captain Ajinkya</t>
         </is>
       </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Tall young man about 26, volleyball jersey, ball, confident. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="19" t="inlineStr">
-        <is>
-          <t>G_W_PINK_SUIT_CUT</t>
-        </is>
-      </c>
-      <c r="B54" s="19" t="inlineStr">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>A023_KAPOOR</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>A023</t>
         </is>
       </c>
-      <c r="C54" s="19" t="inlineStr">
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D54" s="19" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>Golfer Mrs. Kapoor</t>
         </is>
       </c>
-      <c r="E54" s="19" t="inlineStr">
-        <is>
-          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 50, golf cap, golf club. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>C008_NEHA</t>
-        </is>
-      </c>
-      <c r="B55" s="19" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>A023_SAINA</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>A023</t>
         </is>
       </c>
-      <c r="C55" s="19" t="inlineStr">
+      <c r="C55" s="16" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="D55" s="16" t="inlineStr">
         <is>
           <t>Badminton khiladi Saina</t>
         </is>
       </c>
-      <c r="E55" s="19" t="inlineStr">
-        <is>
-          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian young woman about 20, sports wear, racket. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
         </is>
       </c>
     </row>
@@ -63605,29 +63605,29 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>A024_V_PANDEY</t>
-        </is>
-      </c>
-      <c r="B57" s="16" t="inlineStr">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>C04-008_GUPTA_SLUMPED</t>
+        </is>
+      </c>
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t>A024</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>Victim</t>
         </is>
       </c>
-      <c r="D57" s="16" t="inlineStr">
+      <c r="D57" s="19" t="inlineStr">
         <is>
           <t>Indian science teacher Ramesh Pandey, about 55, sweater, spectacles, slumped on a study chair, eyes closed</t>
         </is>
       </c>
-      <c r="E57" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian science teacher Ramesh Pandey, about 55, sweater, spectacles, slumped on a study chair, eyes closed. Peaceful pose, YouTube-safe: no blood, no wounds. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -63769,7 +63769,7 @@
     <row r="63">
       <c r="A63" s="19" t="inlineStr">
         <is>
-          <t>C010_SUNITA</t>
+          <t>G_W_MAROON_SAREE_CUT</t>
         </is>
       </c>
       <c r="B63" s="19" t="inlineStr">
@@ -63823,7 +63823,7 @@
     <row r="65">
       <c r="A65" s="19" t="inlineStr">
         <is>
-          <t>C004_BEHEN</t>
+          <t>C002_RIYA_CUT</t>
         </is>
       </c>
       <c r="B65" s="19" t="inlineStr">
@@ -63850,7 +63850,7 @@
     <row r="66">
       <c r="A66" s="19" t="inlineStr">
         <is>
-          <t>C004_PADOSI</t>
+          <t>C12-010_MAHESH</t>
         </is>
       </c>
       <c r="B66" s="19" t="inlineStr">
@@ -63877,7 +63877,7 @@
     <row r="67">
       <c r="A67" s="19" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>C003_SURAJ_CUT</t>
         </is>
       </c>
       <c r="B67" s="19" t="inlineStr">
@@ -63904,7 +63904,7 @@
     <row r="68">
       <c r="A68" s="19" t="inlineStr">
         <is>
-          <t>G_M_YELLOW_KURTA_CUT</t>
+          <t>C001_ROHIT</t>
         </is>
       </c>
       <c r="B68" s="19" t="inlineStr">
@@ -63958,7 +63958,7 @@
     <row r="70">
       <c r="A70" s="19" t="inlineStr">
         <is>
-          <t>G_M_LIGHTMAN_CUT</t>
+          <t>G_M_BLUE_SHIRT_CUT</t>
         </is>
       </c>
       <c r="B70" s="19" t="inlineStr">
@@ -64010,29 +64010,29 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="inlineStr">
-        <is>
-          <t>A025_V_KHAN</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="inlineStr">
+      <c r="A72" s="19" t="inlineStr">
+        <is>
+          <t>G_V_MAN_CHECK_CUT</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="inlineStr">
         <is>
           <t>A025</t>
         </is>
       </c>
-      <c r="C72" s="16" t="inlineStr">
+      <c r="C72" s="19" t="inlineStr">
         <is>
           <t>Victim</t>
         </is>
       </c>
-      <c r="D72" s="16" t="inlineStr">
+      <c r="D72" s="19" t="inlineStr">
         <is>
           <t>Indian wildlife photographer Imtiaz Khan, about 55, khaki shirt, slumped on a sofa near camera gear, eyes closed</t>
         </is>
       </c>
-      <c r="E72" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian wildlife photographer Imtiaz Khan, about 55, khaki shirt, slumped on a sofa near camera gear, eyes closed. Peaceful pose, YouTube-safe: no blood, no wounds. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E72" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -64174,7 +64174,7 @@
     <row r="78">
       <c r="A78" s="19" t="inlineStr">
         <is>
-          <t>C001_ROHIT</t>
+          <t>G_CR_ROHIT_CUT</t>
         </is>
       </c>
       <c r="B78" s="19" t="inlineStr">
@@ -64201,7 +64201,7 @@
     <row r="79">
       <c r="A79" s="19" t="inlineStr">
         <is>
-          <t>G_M_BROWN_JACKET_CUT</t>
+          <t>G_M_CAMERA_CUT</t>
         </is>
       </c>
       <c r="B79" s="19" t="inlineStr">
@@ -64228,7 +64228,7 @@
     <row r="80">
       <c r="A80" s="19" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="B80" s="19" t="inlineStr">
@@ -64253,36 +64253,36 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="inlineStr">
-        <is>
-          <t>A025_BHUPENDRA</t>
-        </is>
-      </c>
-      <c r="B81" s="16" t="inlineStr">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>G_KALLU_CUT</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
         <is>
           <t>A025</t>
         </is>
       </c>
-      <c r="C81" s="16" t="inlineStr">
+      <c r="C81" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D81" s="16" t="inlineStr">
-        <is>
-          <t>Guide Bhupendra</t>
-        </is>
-      </c>
-      <c r="E81" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Rajasthani guide about 40, safari uniform, turban. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="D81" s="19" t="inlineStr">
+        <is>
+          <t>Guide Kallu</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="19" t="inlineStr">
         <is>
-          <t>C001_ANJALI</t>
+          <t>C011_EMMA</t>
         </is>
       </c>
       <c r="B82" s="19" t="inlineStr">
@@ -64309,7 +64309,7 @@
     <row r="83">
       <c r="A83" s="19" t="inlineStr">
         <is>
-          <t>G_V_MAN_SHERWANI_CUT</t>
+          <t>C013_LAWYER</t>
         </is>
       </c>
       <c r="B83" s="19" t="inlineStr">
@@ -64442,29 +64442,29 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="inlineStr">
-        <is>
-          <t>A026_V_TSERING</t>
-        </is>
-      </c>
-      <c r="B88" s="16" t="inlineStr">
+      <c r="A88" s="19" t="inlineStr">
+        <is>
+          <t>C001_VIKAS</t>
+        </is>
+      </c>
+      <c r="B88" s="19" t="inlineStr">
         <is>
           <t>A026</t>
         </is>
       </c>
-      <c r="C88" s="16" t="inlineStr">
+      <c r="C88" s="19" t="inlineStr">
         <is>
           <t>Victim</t>
         </is>
       </c>
-      <c r="D88" s="16" t="inlineStr">
+      <c r="D88" s="19" t="inlineStr">
         <is>
           <t>Sikkimese homestay owner Tsering Bhutia, about 55, traditional bakhu dress, slumped near a fireplace, eyes closed</t>
         </is>
       </c>
-      <c r="E88" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Sikkimese homestay owner Tsering Bhutia, about 55, traditional bakhu dress, slumped near a fireplace, eyes closed. Peaceful pose, YouTube-safe: no blood, no wounds. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E88" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -64577,29 +64577,29 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="18" t="inlineStr">
-        <is>
-          <t>P_A026_SHOES</t>
-        </is>
-      </c>
-      <c r="B93" s="18" t="inlineStr">
+      <c r="A93" s="19" t="inlineStr">
+        <is>
+          <t>P_SHOES</t>
+        </is>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
         <is>
           <t>A026</t>
         </is>
       </c>
-      <c r="C93" s="18" t="inlineStr">
+      <c r="C93" s="19" t="inlineStr">
         <is>
           <t>Saboot (prop)</t>
         </is>
       </c>
-      <c r="D93" s="18" t="inlineStr">
+      <c r="D93" s="19" t="inlineStr">
         <is>
           <t>Snowy trekking shoes near the door</t>
         </is>
       </c>
-      <c r="E93" s="18" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Snowy trekking shoes near the door. Close-up object, centered. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -64633,7 +64633,7 @@
     <row r="95">
       <c r="A95" s="19" t="inlineStr">
         <is>
-          <t>C008_NEHA</t>
+          <t>G_TANVI</t>
         </is>
       </c>
       <c r="B95" s="19" t="inlineStr">
@@ -64648,7 +64648,7 @@
       </c>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t>Blogger Neha</t>
+          <t>Blogger Tanvi</t>
         </is>
       </c>
       <c r="E95" s="19" t="inlineStr">
@@ -64660,7 +64660,7 @@
     <row r="96">
       <c r="A96" s="19" t="inlineStr">
         <is>
-          <t>G_M_CAMERA_CUT</t>
+          <t>G_M_BROWN_JACKET_CUT</t>
         </is>
       </c>
       <c r="B96" s="19" t="inlineStr">
@@ -64685,36 +64685,36 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="16" t="inlineStr">
-        <is>
-          <t>A026_KARMA</t>
-        </is>
-      </c>
-      <c r="B97" s="16" t="inlineStr">
+      <c r="A97" s="19" t="inlineStr">
+        <is>
+          <t>G_M_BLUE_JACKET_B_CUT</t>
+        </is>
+      </c>
+      <c r="B97" s="19" t="inlineStr">
         <is>
           <t>A026</t>
         </is>
       </c>
-      <c r="C97" s="16" t="inlineStr">
+      <c r="C97" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D97" s="16" t="inlineStr">
+      <c r="D97" s="19" t="inlineStr">
         <is>
           <t>Beta Karma (homestay bechne par jhagda)</t>
         </is>
       </c>
-      <c r="E97" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Sikkimese young man about 27, jacket. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="19" t="inlineStr">
         <is>
-          <t>G_M_OLD_GLASSES_CUT</t>
+          <t>C006_GUPTA</t>
         </is>
       </c>
       <c r="B98" s="19" t="inlineStr">
@@ -64741,7 +64741,7 @@
     <row r="99">
       <c r="A99" s="19" t="inlineStr">
         <is>
-          <t>C002_RIYA_CUT</t>
+          <t>C001_ANJALI</t>
         </is>
       </c>
       <c r="B99" s="19" t="inlineStr">
@@ -64768,7 +64768,7 @@
     <row r="100">
       <c r="A100" s="19" t="inlineStr">
         <is>
-          <t>C16-001_DRMEHTA</t>
+          <t>G_M_OLD_GLASSES_CUT</t>
         </is>
       </c>
       <c r="B100" s="19" t="inlineStr">
@@ -64793,36 +64793,36 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="16" t="inlineStr">
-        <is>
-          <t>A026_DORJEE</t>
-        </is>
-      </c>
-      <c r="B101" s="16" t="inlineStr">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>G_M_APRON_CUT</t>
+        </is>
+      </c>
+      <c r="B101" s="19" t="inlineStr">
         <is>
           <t>A026</t>
         </is>
       </c>
-      <c r="C101" s="16" t="inlineStr">
+      <c r="C101" s="19" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D101" s="16" t="inlineStr">
+      <c r="D101" s="19" t="inlineStr">
         <is>
           <t>Cook Dorjee (daan peti ki chaabi)</t>
         </is>
       </c>
-      <c r="E101" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Sikkimese cook about 45, apron. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E101" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="19" t="inlineStr">
         <is>
-          <t>C007_VIKRAM</t>
+          <t>G_CIVIL_BLACK_CUT</t>
         </is>
       </c>
       <c r="B102" s="19" t="inlineStr">
@@ -64874,29 +64874,29 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="16" t="inlineStr">
-        <is>
-          <t>A027_V_MOHAPATRA</t>
-        </is>
-      </c>
-      <c r="B104" s="16" t="inlineStr">
+      <c r="A104" s="19" t="inlineStr">
+        <is>
+          <t>G_V_MAN_SHERWANI_CUT</t>
+        </is>
+      </c>
+      <c r="B104" s="19" t="inlineStr">
         <is>
           <t>A027</t>
         </is>
       </c>
-      <c r="C104" s="16" t="inlineStr">
+      <c r="C104" s="19" t="inlineStr">
         <is>
           <t>Victim</t>
         </is>
       </c>
-      <c r="D104" s="16" t="inlineStr">
+      <c r="D104" s="19" t="inlineStr">
         <is>
           <t>Indian museum curator Dr. Bijay Mohapatra, about 60, kurta and spectacles, slumped near a glass display case, eyes closed</t>
         </is>
       </c>
-      <c r="E104" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian museum curator Dr. Bijay Mohapatra, about 60, kurta and spectacles, slumped near a glass display case, eyes closed. Peaceful pose, YouTube-safe: no blood, no wounds. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E104" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -65038,7 +65038,7 @@
     <row r="110">
       <c r="A110" s="19" t="inlineStr">
         <is>
-          <t>C002_POOJA</t>
+          <t>C019_COWORKER</t>
         </is>
       </c>
       <c r="B110" s="19" t="inlineStr">
@@ -65092,7 +65092,7 @@
     <row r="112">
       <c r="A112" s="19" t="inlineStr">
         <is>
-          <t>C18-003_PRATEEK</t>
+          <t>C10-004_DEEPAK</t>
         </is>
       </c>
       <c r="B112" s="19" t="inlineStr">
@@ -65119,7 +65119,7 @@
     <row r="113">
       <c r="A113" s="19" t="inlineStr">
         <is>
-          <t>C17-001_SETH</t>
+          <t>C017_BESTMAN</t>
         </is>
       </c>
       <c r="B113" s="19" t="inlineStr">
@@ -65146,7 +65146,7 @@
     <row r="114">
       <c r="A114" s="19" t="inlineStr">
         <is>
-          <t>G_V_WOMAN_SAREE_CUT</t>
+          <t>C010_SUNITA</t>
         </is>
       </c>
       <c r="B114" s="19" t="inlineStr">
@@ -65173,7 +65173,7 @@
     <row r="115">
       <c r="A115" s="19" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C005_VICKY</t>
         </is>
       </c>
       <c r="B115" s="19" t="inlineStr">
@@ -65200,7 +65200,7 @@
     <row r="116">
       <c r="A116" s="19" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>C004_BEHEN</t>
         </is>
       </c>
       <c r="B116" s="19" t="inlineStr">
@@ -65227,7 +65227,7 @@
     <row r="117">
       <c r="A117" s="19" t="inlineStr">
         <is>
-          <t>G_V_MAN_GREY_CUT</t>
+          <t>C007_NIKHIL</t>
         </is>
       </c>
       <c r="B117" s="19" t="inlineStr">
@@ -65281,7 +65281,7 @@
     <row r="119">
       <c r="A119" s="19" t="inlineStr">
         <is>
-          <t>G_RAMU</t>
+          <t>G_M_GAMCHHA_CUT</t>
         </is>
       </c>
       <c r="B119" s="19" t="inlineStr">
@@ -65296,7 +65296,7 @@
       </c>
       <c r="D119" s="19" t="inlineStr">
         <is>
-          <t>Safaiwala Ramu</t>
+          <t>Safaiwala Gopi</t>
         </is>
       </c>
       <c r="E119" s="19" t="inlineStr">
@@ -65333,29 +65333,29 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="16" t="inlineStr">
-        <is>
-          <t>A028_V_GREWAL</t>
-        </is>
-      </c>
-      <c r="B121" s="16" t="inlineStr">
+      <c r="A121" s="19" t="inlineStr">
+        <is>
+          <t>C08-007_KAPOOR</t>
+        </is>
+      </c>
+      <c r="B121" s="19" t="inlineStr">
         <is>
           <t>A028</t>
         </is>
       </c>
-      <c r="C121" s="16" t="inlineStr">
+      <c r="C121" s="19" t="inlineStr">
         <is>
           <t>Victim</t>
         </is>
       </c>
-      <c r="D121" s="16" t="inlineStr">
+      <c r="D121" s="19" t="inlineStr">
         <is>
           <t>Indian hospital owner Dr. Harjeet Grewal, about 60, white coat, slumped on his cabin chair, eyes closed</t>
         </is>
       </c>
-      <c r="E121" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian hospital owner Dr. Harjeet Grewal, about 60, white coat, slumped on his cabin chair, eyes closed. Peaceful pose, YouTube-safe: no blood, no wounds. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E121" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -65497,7 +65497,7 @@
     <row r="127">
       <c r="A127" s="19" t="inlineStr">
         <is>
-          <t>C005_VICKY</t>
+          <t>C018_BOYFRIEND</t>
         </is>
       </c>
       <c r="B127" s="19" t="inlineStr">
@@ -65684,29 +65684,29 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="19" t="inlineStr">
-        <is>
-          <t>C001_ANJALI</t>
-        </is>
-      </c>
-      <c r="B134" s="19" t="inlineStr">
+      <c r="A134" s="16" t="inlineStr">
+        <is>
+          <t>A028_ANU</t>
+        </is>
+      </c>
+      <c r="B134" s="16" t="inlineStr">
         <is>
           <t>A028</t>
         </is>
       </c>
-      <c r="C134" s="19" t="inlineStr">
+      <c r="C134" s="16" t="inlineStr">
         <is>
           <t>Suspect</t>
         </is>
       </c>
-      <c r="D134" s="19" t="inlineStr">
+      <c r="D134" s="16" t="inlineStr">
         <is>
           <t>Yoga teacher Anu</t>
         </is>
       </c>
-      <c r="E134" s="19" t="inlineStr">
-        <is>
-          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
+      <c r="E134" s="16" t="inlineStr">
+        <is>
+          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian woman about 35, yoga wear. Full body, standing, facing camera. Plain bright green (#00FF00) background, no text, no shadow.</t>
         </is>
       </c>
     </row>
@@ -65740,7 +65740,7 @@
     <row r="136">
       <c r="A136" s="19" t="inlineStr">
         <is>
-          <t>C04-008_GUPTA_SLUMPED</t>
+          <t>C17-001_SETH</t>
         </is>
       </c>
       <c r="B136" s="19" t="inlineStr">
@@ -65902,7 +65902,7 @@
     <row r="142">
       <c r="A142" s="19" t="inlineStr">
         <is>
-          <t>C006_GUPTA</t>
+          <t>G_M_OLD_NOGLASSES_CUT</t>
         </is>
       </c>
       <c r="B142" s="19" t="inlineStr">
@@ -65929,7 +65929,7 @@
     <row r="143">
       <c r="A143" s="19" t="inlineStr">
         <is>
-          <t>C004_AMIT</t>
+          <t>C003_BHATIJA</t>
         </is>
       </c>
       <c r="B143" s="19" t="inlineStr">
@@ -65956,7 +65956,7 @@
     <row r="144">
       <c r="A144" s="19" t="inlineStr">
         <is>
-          <t>C004_SNEHA</t>
+          <t>C002_POOJA</t>
         </is>
       </c>
       <c r="B144" s="19" t="inlineStr">
@@ -65983,7 +65983,7 @@
     <row r="145">
       <c r="A145" s="19" t="inlineStr">
         <is>
-          <t>C003_BHATIJA</t>
+          <t>C004_AMIT</t>
         </is>
       </c>
       <c r="B145" s="19" t="inlineStr">
@@ -66010,7 +66010,7 @@
     <row r="146">
       <c r="A146" s="19" t="inlineStr">
         <is>
-          <t>G_V_MAN_BLUE_CUT</t>
+          <t>G_M_BLUE_JACKET_A_CUT</t>
         </is>
       </c>
       <c r="B146" s="19" t="inlineStr">
@@ -66064,7 +66064,7 @@
     <row r="148">
       <c r="A148" s="19" t="inlineStr">
         <is>
-          <t>C08-004_MR_RATHI</t>
+          <t>C004_PADOSI</t>
         </is>
       </c>
       <c r="B148" s="19" t="inlineStr">
@@ -66170,29 +66170,29 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="16" t="inlineStr">
-        <is>
-          <t>A030_V_JOSHI</t>
-        </is>
-      </c>
-      <c r="B152" s="16" t="inlineStr">
+      <c r="A152" s="19" t="inlineStr">
+        <is>
+          <t>C04-010_ARJUN</t>
+        </is>
+      </c>
+      <c r="B152" s="19" t="inlineStr">
         <is>
           <t>A030</t>
         </is>
       </c>
-      <c r="C152" s="16" t="inlineStr">
+      <c r="C152" s="19" t="inlineStr">
         <is>
           <t>Victim</t>
         </is>
       </c>
-      <c r="D152" s="16" t="inlineStr">
+      <c r="D152" s="19" t="inlineStr">
         <is>
           <t>Indian astronomer Dr. Prakash Joshi, about 62, woollen sweater, slumped near a telescope, eyes closed</t>
         </is>
       </c>
-      <c r="E152" s="16" t="inlineStr">
-        <is>
-          <t>Flat 2D cartoon illustration, bold black outlines, same art style as the 'Detective Shivam' series, Indian setting, warm cinematic colours, no watermark. Indian astronomer Dr. Prakash Joshi, about 62, woollen sweater, slumped near a telescope, eyes closed. Peaceful pose, YouTube-safe: no blood, no wounds. Plain bright green (#00FF00) background, no text, no shadow.</t>
+      <c r="E152" s="19" t="inlineStr">
+        <is>
+          <t>PEHLE SE HAI (purani image, nayi mat banao) – ek baar dekh lo look role se mel khaata hai</t>
         </is>
       </c>
     </row>
@@ -66334,7 +66334,7 @@
     <row r="158">
       <c r="A158" s="19" t="inlineStr">
         <is>
-          <t>G_M_GREY_HOODIE_CUT</t>
+          <t>C020_BROTHER</t>
         </is>
       </c>
       <c r="B158" s="19" t="inlineStr">
@@ -66361,7 +66361,7 @@
     <row r="159">
       <c r="A159" s="19" t="inlineStr">
         <is>
-          <t>C005_NEHA</t>
+          <t>G_W_PINK_SUIT_CUT</t>
         </is>
       </c>
       <c r="B159" s="19" t="inlineStr">
@@ -66388,7 +66388,7 @@
     <row r="160">
       <c r="A160" s="19" t="inlineStr">
         <is>
-          <t>G_M_OLD_NOGLASSES_CUT</t>
+          <t>C011_TOM</t>
         </is>
       </c>
       <c r="B160" s="19" t="inlineStr">
@@ -66415,7 +66415,7 @@
     <row r="161">
       <c r="A161" s="19" t="inlineStr">
         <is>
-          <t>C007_KAVYA</t>
+          <t>C018_SISTER</t>
         </is>
       </c>
       <c r="B161" s="19" t="inlineStr">
@@ -66523,7 +66523,7 @@
     <row r="165">
       <c r="A165" s="19" t="inlineStr">
         <is>
-          <t>C10-004_DEEPAK</t>
+          <t>C03-003_VICKY</t>
         </is>
       </c>
       <c r="B165" s="19" t="inlineStr">
@@ -66577,7 +66577,7 @@
     <row r="167">
       <c r="A167" s="19" t="inlineStr">
         <is>
-          <t>G_V_MAN_CHECK_CUT</t>
+          <t>C008_GUEST</t>
         </is>
       </c>
       <c r="B167" s="19" t="inlineStr">
